--- a/ДВР 26.01.02.105 ответы на замечания (итог2).xlsx
+++ b/ДВР 26.01.02.105 ответы на замечания (итог2).xlsx
@@ -23,7 +23,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="U99">
+    <comment authorId="0" ref="U88">
       <text>
         <t xml:space="preserve">======
 ID#AAACGns-JXA
@@ -31,7 +31,7 @@
 по формуле добавлено 12 шт (это для информации на снятие)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="D81">
+    <comment authorId="0" ref="D95">
       <text>
         <t xml:space="preserve">======
 ID#AAACGns-JXE
@@ -3212,15 +3212,15 @@
       <c r="U4" s="17"/>
       <c r="V4" s="9"/>
       <c r="W4" s="9">
-        <f t="shared" ref="W4:Y4" si="1">W3/83</f>
+        <f>W3/83</f>
         <v>13268.81928</v>
       </c>
       <c r="X4" s="9">
-        <f t="shared" si="1"/>
+        <f>X3/83</f>
         <v>12048.19277</v>
       </c>
       <c r="Y4" s="9">
-        <f t="shared" si="1"/>
+        <f>Y3/83</f>
         <v>-1220.626506</v>
       </c>
       <c r="Z4" s="9"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AK10" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Исправлено: в столбце V объём считается формулой (X+AA+AD+AG), объёмы в AD и AG расписаны формулами по позициям РД. В строках 46, 77, 86–88, 99, 100, 155, 156 объём разбит между 2025 и 2026 гг.: в AD — объём, закрытый в 2025 г., в AG — формула по позициям РД за вычетом объёма 2025 г.</t>
+          <t xml:space="preserve">Исправлено: в столбце V объём считается формулой (X+AA+AD+AG), объёмы в AD и AG расписаны формулами по позициям РД. В строках 46, 77, 88, 89, 100–102, 155, 156 объём разбит между 2025 и 2026 гг.: в AD — объём, закрытый в 2025 г., в AG — формула по позициям РД за вычетом объёма 2025 г.</t>
         </is>
       </c>
       <c r="AL10" s="13"/>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="M12" s="64"/>
       <c r="N12" s="65">
-        <f t="shared" ref="N12:N148" si="2">V12</f>
+        <f>V12</f>
         <v>322</v>
       </c>
       <c r="O12" s="64">
@@ -3932,7 +3932,7 @@
         <v>33570110</v>
       </c>
       <c r="Q12" s="65">
-        <f t="shared" ref="Q12:Q170" si="3">N12-G12</f>
+        <f>N12-G12</f>
         <v>322</v>
       </c>
       <c r="R12" s="66">
@@ -4056,13 +4056,13 @@
       </c>
       <c r="M13" s="83"/>
       <c r="N13" s="84">
-        <f t="shared" si="2"/>
+        <f>V13</f>
         <v>60</v>
       </c>
       <c r="O13" s="83"/>
       <c r="P13" s="83"/>
       <c r="Q13" s="84">
-        <f t="shared" si="3"/>
+        <f>N13-G13</f>
         <v>60</v>
       </c>
       <c r="R13" s="85"/>
@@ -4072,7 +4072,7 @@
       <c r="T13" s="86"/>
       <c r="U13" s="87"/>
       <c r="V13" s="88">
-        <f t="shared" ref="V13:V20" si="4">SUM(X13+AA13+AD13+AG13)</f>
+        <f>SUM(X13+AA13+AD13+AG13)</f>
         <v>60</v>
       </c>
       <c r="W13" s="89"/>
@@ -4140,13 +4140,13 @@
       </c>
       <c r="M14" s="83"/>
       <c r="N14" s="84">
-        <f t="shared" si="2"/>
+        <f>V14</f>
         <v>6</v>
       </c>
       <c r="O14" s="83"/>
       <c r="P14" s="83"/>
       <c r="Q14" s="84">
-        <f t="shared" si="3"/>
+        <f>N14-G14</f>
         <v>6</v>
       </c>
       <c r="R14" s="85"/>
@@ -4156,7 +4156,7 @@
       <c r="T14" s="86"/>
       <c r="U14" s="87"/>
       <c r="V14" s="88">
-        <f t="shared" si="4"/>
+        <f>SUM(X14+AA14+AD14+AG14)</f>
         <v>6</v>
       </c>
       <c r="W14" s="89"/>
@@ -4220,13 +4220,13 @@
       </c>
       <c r="M15" s="83"/>
       <c r="N15" s="84">
-        <f t="shared" si="2"/>
+        <f>V15</f>
         <v>94</v>
       </c>
       <c r="O15" s="83"/>
       <c r="P15" s="83"/>
       <c r="Q15" s="84">
-        <f t="shared" si="3"/>
+        <f>N15-G15</f>
         <v>94</v>
       </c>
       <c r="R15" s="85"/>
@@ -4236,7 +4236,7 @@
       <c r="T15" s="86"/>
       <c r="U15" s="87"/>
       <c r="V15" s="88">
-        <f t="shared" si="4"/>
+        <f>SUM(X15+AA15+AD15+AG15)</f>
         <v>94</v>
       </c>
       <c r="W15" s="89"/>
@@ -4300,13 +4300,13 @@
       </c>
       <c r="M16" s="83"/>
       <c r="N16" s="84">
-        <f t="shared" si="2"/>
+        <f>V16</f>
         <v>34</v>
       </c>
       <c r="O16" s="83"/>
       <c r="P16" s="83"/>
       <c r="Q16" s="84">
-        <f t="shared" si="3"/>
+        <f>N16-G16</f>
         <v>34</v>
       </c>
       <c r="R16" s="87"/>
@@ -4316,7 +4316,7 @@
       <c r="T16" s="86"/>
       <c r="U16" s="87"/>
       <c r="V16" s="88">
-        <f t="shared" si="4"/>
+        <f>SUM(X16+AA16+AD16+AG16)</f>
         <v>34</v>
       </c>
       <c r="W16" s="93"/>
@@ -4380,13 +4380,13 @@
       </c>
       <c r="M17" s="83"/>
       <c r="N17" s="84">
-        <f t="shared" si="2"/>
+        <f>V17</f>
         <v>100</v>
       </c>
       <c r="O17" s="83"/>
       <c r="P17" s="83"/>
       <c r="Q17" s="84">
-        <f t="shared" si="3"/>
+        <f>N17-G17</f>
         <v>100</v>
       </c>
       <c r="R17" s="87"/>
@@ -4396,7 +4396,7 @@
       <c r="T17" s="86"/>
       <c r="U17" s="87"/>
       <c r="V17" s="88">
-        <f t="shared" si="4"/>
+        <f>SUM(X17+AA17+AD17+AG17)</f>
         <v>100</v>
       </c>
       <c r="W17" s="93"/>
@@ -4460,13 +4460,13 @@
       </c>
       <c r="M18" s="83"/>
       <c r="N18" s="84">
-        <f t="shared" si="2"/>
+        <f>V18</f>
         <v>25</v>
       </c>
       <c r="O18" s="83"/>
       <c r="P18" s="83"/>
       <c r="Q18" s="84">
-        <f t="shared" si="3"/>
+        <f>N18-G18</f>
         <v>25</v>
       </c>
       <c r="R18" s="85"/>
@@ -4476,7 +4476,7 @@
       <c r="T18" s="86"/>
       <c r="U18" s="87"/>
       <c r="V18" s="88">
-        <f t="shared" si="4"/>
+        <f>SUM(X18+AA18+AD18+AG18)</f>
         <v>25</v>
       </c>
       <c r="W18" s="89"/>
@@ -4540,13 +4540,13 @@
       </c>
       <c r="M19" s="83"/>
       <c r="N19" s="84">
-        <f t="shared" si="2"/>
+        <f>V19</f>
         <v>2</v>
       </c>
       <c r="O19" s="83"/>
       <c r="P19" s="83"/>
       <c r="Q19" s="84">
-        <f t="shared" si="3"/>
+        <f>N19-G19</f>
         <v>2</v>
       </c>
       <c r="R19" s="87"/>
@@ -4556,7 +4556,7 @@
       <c r="T19" s="86"/>
       <c r="U19" s="87"/>
       <c r="V19" s="88">
-        <f t="shared" si="4"/>
+        <f>SUM(X19+AA19+AD19+AG19)</f>
         <v>2</v>
       </c>
       <c r="W19" s="93"/>
@@ -4621,13 +4621,13 @@
       </c>
       <c r="M20" s="83"/>
       <c r="N20" s="84">
-        <f t="shared" si="2"/>
+        <f>V20</f>
         <v>1</v>
       </c>
       <c r="O20" s="83"/>
       <c r="P20" s="83"/>
       <c r="Q20" s="84">
-        <f t="shared" si="3"/>
+        <f>N20-G20</f>
         <v>1</v>
       </c>
       <c r="R20" s="87"/>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="U20" s="87"/>
       <c r="V20" s="88">
-        <f t="shared" si="4"/>
+        <f>SUM(X20+AA20+AD20+AG20)</f>
         <v>1</v>
       </c>
       <c r="W20" s="93"/>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="M21" s="98"/>
       <c r="N21" s="99">
-        <f t="shared" si="2"/>
+        <f>V21</f>
         <v>2313.5</v>
       </c>
       <c r="O21" s="98">
@@ -4742,7 +4742,7 @@
         <v>2146511.57</v>
       </c>
       <c r="Q21" s="99">
-        <f t="shared" si="3"/>
+        <f>N21-G21</f>
         <v>2313.5</v>
       </c>
       <c r="R21" s="100">
@@ -4868,13 +4868,13 @@
       </c>
       <c r="M22" s="83"/>
       <c r="N22" s="84">
-        <f t="shared" si="2"/>
+        <f>V22</f>
         <v>776</v>
       </c>
       <c r="O22" s="83"/>
       <c r="P22" s="83"/>
       <c r="Q22" s="84">
-        <f t="shared" si="3"/>
+        <f>N22-G22</f>
         <v>776</v>
       </c>
       <c r="R22" s="85"/>
@@ -4884,7 +4884,7 @@
       <c r="T22" s="86"/>
       <c r="U22" s="87"/>
       <c r="V22" s="106">
-        <f t="shared" ref="V22:V29" si="5">SUM(X22+AA22+AD22+AG22)</f>
+        <f>SUM(X22+AA22+AD22+AG22)</f>
         <v>776</v>
       </c>
       <c r="W22" s="93"/>
@@ -4948,13 +4948,13 @@
       </c>
       <c r="M23" s="83"/>
       <c r="N23" s="84">
-        <f t="shared" si="2"/>
+        <f>V23</f>
         <v>333.5</v>
       </c>
       <c r="O23" s="83"/>
       <c r="P23" s="83"/>
       <c r="Q23" s="84">
-        <f t="shared" si="3"/>
+        <f>N23-G23</f>
         <v>333.5</v>
       </c>
       <c r="R23" s="85"/>
@@ -4964,7 +4964,7 @@
       <c r="T23" s="86"/>
       <c r="U23" s="87"/>
       <c r="V23" s="106">
-        <f t="shared" si="5"/>
+        <f>SUM(X23+AA23+AD23+AG23)</f>
         <v>333.5</v>
       </c>
       <c r="W23" s="93"/>
@@ -5028,13 +5028,13 @@
       </c>
       <c r="M24" s="83"/>
       <c r="N24" s="84">
-        <f t="shared" si="2"/>
+        <f>V24</f>
         <v>380</v>
       </c>
       <c r="O24" s="83"/>
       <c r="P24" s="83"/>
       <c r="Q24" s="84">
-        <f t="shared" si="3"/>
+        <f>N24-G24</f>
         <v>380</v>
       </c>
       <c r="R24" s="85"/>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="U24" s="87"/>
       <c r="V24" s="106">
-        <f t="shared" si="5"/>
+        <f>SUM(X24+AA24+AD24+AG24)</f>
         <v>380</v>
       </c>
       <c r="W24" s="89"/>
@@ -5110,13 +5110,13 @@
       </c>
       <c r="M25" s="83"/>
       <c r="N25" s="84">
-        <f t="shared" si="2"/>
+        <f>V25</f>
         <v>326</v>
       </c>
       <c r="O25" s="83"/>
       <c r="P25" s="83"/>
       <c r="Q25" s="84">
-        <f t="shared" si="3"/>
+        <f>N25-G25</f>
         <v>326</v>
       </c>
       <c r="R25" s="85"/>
@@ -5126,7 +5126,7 @@
       <c r="T25" s="86"/>
       <c r="U25" s="87"/>
       <c r="V25" s="106">
-        <f t="shared" si="5"/>
+        <f>SUM(X25+AA25+AD25+AG25)</f>
         <v>326</v>
       </c>
       <c r="W25" s="89"/>
@@ -5191,13 +5191,13 @@
       </c>
       <c r="M26" s="83"/>
       <c r="N26" s="84">
-        <f t="shared" si="2"/>
+        <f>V26</f>
         <v>20</v>
       </c>
       <c r="O26" s="83"/>
       <c r="P26" s="83"/>
       <c r="Q26" s="84">
-        <f t="shared" si="3"/>
+        <f>N26-G26</f>
         <v>20</v>
       </c>
       <c r="R26" s="85"/>
@@ -5207,7 +5207,7 @@
       <c r="T26" s="86"/>
       <c r="U26" s="87"/>
       <c r="V26" s="106">
-        <f t="shared" si="5"/>
+        <f>SUM(X26+AA26+AD26+AG26)</f>
         <v>20</v>
       </c>
       <c r="W26" s="89"/>
@@ -5269,13 +5269,13 @@
       <c r="L27" s="83"/>
       <c r="M27" s="83"/>
       <c r="N27" s="84">
-        <f t="shared" si="2"/>
+        <f>V27</f>
         <v>58</v>
       </c>
       <c r="O27" s="83"/>
       <c r="P27" s="83"/>
       <c r="Q27" s="84">
-        <f t="shared" si="3"/>
+        <f>N27-G27</f>
         <v>58</v>
       </c>
       <c r="R27" s="87"/>
@@ -5285,7 +5285,7 @@
       <c r="T27" s="86"/>
       <c r="U27" s="87"/>
       <c r="V27" s="106">
-        <f t="shared" si="5"/>
+        <f>SUM(X27+AA27+AD27+AG27)</f>
         <v>58</v>
       </c>
       <c r="W27" s="93"/>
@@ -5347,13 +5347,13 @@
       <c r="L28" s="83"/>
       <c r="M28" s="83"/>
       <c r="N28" s="84">
-        <f t="shared" si="2"/>
+        <f>V28</f>
         <v>410</v>
       </c>
       <c r="O28" s="83"/>
       <c r="P28" s="83"/>
       <c r="Q28" s="84">
-        <f t="shared" si="3"/>
+        <f>N28-G28</f>
         <v>410</v>
       </c>
       <c r="R28" s="87"/>
@@ -5363,7 +5363,7 @@
       <c r="T28" s="86"/>
       <c r="U28" s="87"/>
       <c r="V28" s="106">
-        <f t="shared" si="5"/>
+        <f>SUM(X28+AA28+AD28+AG28)</f>
         <v>410</v>
       </c>
       <c r="W28" s="93"/>
@@ -5425,13 +5425,13 @@
       <c r="L29" s="83"/>
       <c r="M29" s="83"/>
       <c r="N29" s="84">
-        <f t="shared" si="2"/>
+        <f>V29</f>
         <v>10</v>
       </c>
       <c r="O29" s="83"/>
       <c r="P29" s="83"/>
       <c r="Q29" s="84">
-        <f t="shared" si="3"/>
+        <f>N29-G29</f>
         <v>10</v>
       </c>
       <c r="R29" s="85"/>
@@ -5441,7 +5441,7 @@
       <c r="T29" s="86"/>
       <c r="U29" s="87"/>
       <c r="V29" s="88">
-        <f t="shared" si="5"/>
+        <f>SUM(X29+AA29+AD29+AG29)</f>
         <v>10</v>
       </c>
       <c r="W29" s="89"/>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="M30" s="98"/>
       <c r="N30" s="99">
-        <f t="shared" si="2"/>
+        <f>V30</f>
         <v>2313.5</v>
       </c>
       <c r="O30" s="98">
@@ -5545,7 +5545,7 @@
         <v>2146511.57</v>
       </c>
       <c r="Q30" s="99">
-        <f t="shared" si="3"/>
+        <f>N30-G30</f>
         <v>2313.5</v>
       </c>
       <c r="R30" s="100">
@@ -5666,32 +5666,32 @@
       <c r="J31" s="84"/>
       <c r="K31" s="84"/>
       <c r="L31" s="83" t="str">
-        <f t="shared" ref="L31:L35" si="6">L22</f>
+        <f>L22</f>
         <v>12002-81-020601-АУПТ. СО1; Рев.К; 9л; поз(12.1;)
 12002-81-020601-АУПТ. СО3; Рев.К; 7л; (поз 7.4.10) 14л; поз(14.1)
 </v>
       </c>
       <c r="M31" s="83"/>
       <c r="N31" s="84">
-        <f t="shared" si="2"/>
+        <f>V31</f>
         <v>776</v>
       </c>
       <c r="O31" s="83"/>
       <c r="P31" s="83"/>
       <c r="Q31" s="84">
-        <f t="shared" si="3"/>
+        <f>N31-G31</f>
         <v>776</v>
       </c>
       <c r="R31" s="85"/>
       <c r="S31" s="107" t="str">
-        <f t="shared" ref="S31:S38" si="7">S22</f>
+        <f>S22</f>
         <v>12002-81-020601-АУПТ. СО1; Изм.0; 9л; поз(12.1;)
 12002-81-020601-АУПТ. СО3; Изм.0; 7л; (поз 7.4.10) 14л; поз(14.1)</v>
       </c>
       <c r="T31" s="86"/>
       <c r="U31" s="87"/>
       <c r="V31" s="106">
-        <f t="shared" ref="V31:V38" si="8">SUM(X31+AA31+AD31+AG31)</f>
+        <f>SUM(X31+AA31+AD31+AG31)</f>
         <v>776</v>
       </c>
       <c r="W31" s="93"/>
@@ -5707,7 +5707,7 @@
       <c r="AE31" s="84"/>
       <c r="AF31" s="93"/>
       <c r="AG31" s="86">
-        <f t="shared" ref="AG31:AG38" si="9">AG22</f>
+        <f>AG22</f>
         <v>776</v>
       </c>
       <c r="AH31" s="84"/>
@@ -5751,29 +5751,29 @@
       <c r="J32" s="84"/>
       <c r="K32" s="84"/>
       <c r="L32" s="83" t="str">
-        <f t="shared" si="6"/>
+        <f>L23</f>
         <v>12002-81-020601-АУПТ. СО2; Рев.К п.24.9</v>
       </c>
       <c r="M32" s="83"/>
       <c r="N32" s="84">
-        <f t="shared" si="2"/>
+        <f>V32</f>
         <v>333.5</v>
       </c>
       <c r="O32" s="83"/>
       <c r="P32" s="83"/>
       <c r="Q32" s="84">
-        <f t="shared" si="3"/>
+        <f>N32-G32</f>
         <v>333.5</v>
       </c>
       <c r="R32" s="85"/>
       <c r="S32" s="92" t="str">
-        <f t="shared" si="7"/>
+        <f>S23</f>
         <v>12002-81-020601-АУПТ. СО2; Изм.0 л.56 (поз 24.9)</v>
       </c>
       <c r="T32" s="86"/>
       <c r="U32" s="87"/>
       <c r="V32" s="106">
-        <f t="shared" si="8"/>
+        <f>SUM(X32+AA32+AD32+AG32)</f>
         <v>333.5</v>
       </c>
       <c r="W32" s="89"/>
@@ -5789,7 +5789,7 @@
       <c r="AE32" s="83"/>
       <c r="AF32" s="93"/>
       <c r="AG32" s="86">
-        <f t="shared" si="9"/>
+        <f>AG23</f>
         <v>333.5</v>
       </c>
       <c r="AH32" s="83"/>
@@ -5833,29 +5833,29 @@
       <c r="J33" s="84"/>
       <c r="K33" s="84"/>
       <c r="L33" s="83" t="str">
-        <f t="shared" si="6"/>
+        <f>L24</f>
         <v>12002-81-020601-СПА.СО;Изм.1; 9л; поз(11.46) л.10 (поз 11.48.4)</v>
       </c>
       <c r="M33" s="83"/>
       <c r="N33" s="84">
-        <f t="shared" si="2"/>
+        <f>V33</f>
         <v>380</v>
       </c>
       <c r="O33" s="83"/>
       <c r="P33" s="83"/>
       <c r="Q33" s="84">
-        <f t="shared" si="3"/>
+        <f>N33-G33</f>
         <v>380</v>
       </c>
       <c r="R33" s="85"/>
       <c r="S33" s="92" t="str">
-        <f t="shared" si="7"/>
+        <f>S24</f>
         <v>12002-81-020601-СПА.СО;Изм.1; 9л; поз(11.46) л.10 (поз 11.48.4)</v>
       </c>
       <c r="T33" s="86"/>
       <c r="U33" s="87"/>
       <c r="V33" s="106">
-        <f t="shared" si="8"/>
+        <f>SUM(X33+AA33+AD33+AG33)</f>
         <v>380</v>
       </c>
       <c r="W33" s="93"/>
@@ -5866,13 +5866,13 @@
       <c r="AB33" s="84"/>
       <c r="AC33" s="93"/>
       <c r="AD33" s="86">
-        <f t="shared" ref="AD33:AD35" si="10">AD24</f>
+        <f>AD24</f>
         <v>120</v>
       </c>
       <c r="AE33" s="84"/>
       <c r="AF33" s="93"/>
       <c r="AG33" s="86">
-        <f t="shared" si="9"/>
+        <f>AG24</f>
         <v>260</v>
       </c>
       <c r="AH33" s="84"/>
@@ -5916,24 +5916,24 @@
       <c r="J34" s="84"/>
       <c r="K34" s="84"/>
       <c r="L34" s="83" t="str">
-        <f t="shared" si="6"/>
+        <f>L25</f>
         <v>12002-81-020602-АУПТ.СО1; Изм.0; 10л; поз(10.4.35)
 12002-81-020602-АУПТ.СО2; Изм.0; 20л; поз(4.7)</v>
       </c>
       <c r="M34" s="83"/>
       <c r="N34" s="84">
-        <f t="shared" si="2"/>
+        <f>V34</f>
         <v>326</v>
       </c>
       <c r="O34" s="83"/>
       <c r="P34" s="83"/>
       <c r="Q34" s="84">
-        <f t="shared" si="3"/>
+        <f>N34-G34</f>
         <v>326</v>
       </c>
       <c r="R34" s="85"/>
       <c r="S34" s="92" t="str">
-        <f t="shared" si="7"/>
+        <f>S25</f>
         <v>12002-81-020602-АУПТ.СО1; Изм.0; 10л; поз(10.4.35)
 12002-81-020602-АУПТ.СО2; Изм.0; 20л; поз(4.7)
 12002-81-020602-АУПТ.СО3; Изм.0; 3л; поз(2.7)</v>
@@ -5941,7 +5941,7 @@
       <c r="T34" s="86"/>
       <c r="U34" s="87"/>
       <c r="V34" s="106">
-        <f t="shared" si="8"/>
+        <f>SUM(X34+AA34+AD34+AG34)</f>
         <v>326</v>
       </c>
       <c r="W34" s="93"/>
@@ -5952,13 +5952,13 @@
       <c r="AB34" s="84"/>
       <c r="AC34" s="93"/>
       <c r="AD34" s="86">
-        <f t="shared" si="10"/>
+        <f>AD25</f>
         <v>190</v>
       </c>
       <c r="AE34" s="84"/>
       <c r="AF34" s="93"/>
       <c r="AG34" s="86">
-        <f t="shared" si="9"/>
+        <f>AG25</f>
         <v>136</v>
       </c>
       <c r="AH34" s="84"/>
@@ -6002,31 +6002,31 @@
       <c r="J35" s="84"/>
       <c r="K35" s="84"/>
       <c r="L35" s="83" t="str">
-        <f t="shared" si="6"/>
+        <f>L26</f>
         <v>12002-81-020603-АУПТ.СО; Изм.2; 6л; поз(4.3)
 </v>
       </c>
       <c r="M35" s="83"/>
       <c r="N35" s="84">
-        <f t="shared" si="2"/>
+        <f>V35</f>
         <v>20</v>
       </c>
       <c r="O35" s="83"/>
       <c r="P35" s="83"/>
       <c r="Q35" s="84">
-        <f t="shared" si="3"/>
+        <f>N35-G35</f>
         <v>20</v>
       </c>
       <c r="R35" s="85"/>
       <c r="S35" s="92" t="str">
-        <f t="shared" si="7"/>
+        <f>S26</f>
         <v>12002-81-020603-АУПТ.СО; Изм.2; 6л; поз(4.3)
 </v>
       </c>
       <c r="T35" s="86"/>
       <c r="U35" s="87"/>
       <c r="V35" s="106">
-        <f t="shared" si="8"/>
+        <f>SUM(X35+AA35+AD35+AG35)</f>
         <v>20</v>
       </c>
       <c r="W35" s="89"/>
@@ -6037,13 +6037,13 @@
       <c r="AB35" s="83"/>
       <c r="AC35" s="93"/>
       <c r="AD35" s="86">
-        <f t="shared" si="10"/>
+        <f>AD26</f>
         <v>20</v>
       </c>
       <c r="AE35" s="83"/>
       <c r="AF35" s="93"/>
       <c r="AG35" s="86">
-        <f t="shared" si="9"/>
+        <f>AG26</f>
         <v>0</v>
       </c>
       <c r="AH35" s="83"/>
@@ -6089,18 +6089,18 @@
       <c r="L36" s="83"/>
       <c r="M36" s="83"/>
       <c r="N36" s="84">
-        <f t="shared" si="2"/>
+        <f>V36</f>
         <v>58</v>
       </c>
       <c r="O36" s="83"/>
       <c r="P36" s="83"/>
       <c r="Q36" s="84">
-        <f t="shared" si="3"/>
+        <f>N36-G36</f>
         <v>58</v>
       </c>
       <c r="R36" s="85"/>
       <c r="S36" s="92" t="str">
-        <f t="shared" si="7"/>
+        <f>S27</f>
         <v>12002-81-020601-АУПТ1.1 СО1 Изм.0 л6 поз(11.1)
 12002-81-020601-АУПТ1.1 СО2 Изм.0 л3 поз(6.3)
 12002-81-020601-АУПТ1.1 СО3 Изм.0 л4 поз(5.3.22)л8 поз(12.1)</v>
@@ -6108,7 +6108,7 @@
       <c r="T36" s="86"/>
       <c r="U36" s="87"/>
       <c r="V36" s="92">
-        <f t="shared" si="8"/>
+        <f>SUM(X36+AA36+AD36+AG36)</f>
         <v>58</v>
       </c>
       <c r="W36" s="89"/>
@@ -6124,7 +6124,7 @@
       <c r="AE36" s="83"/>
       <c r="AF36" s="93"/>
       <c r="AG36" s="86">
-        <f t="shared" si="9"/>
+        <f>AG27</f>
         <v>58</v>
       </c>
       <c r="AH36" s="83"/>
@@ -6170,24 +6170,24 @@
       <c r="L37" s="83"/>
       <c r="M37" s="108"/>
       <c r="N37" s="84">
-        <f t="shared" si="2"/>
+        <f>V37</f>
         <v>410</v>
       </c>
       <c r="O37" s="83"/>
       <c r="P37" s="83"/>
       <c r="Q37" s="84">
-        <f t="shared" si="3"/>
+        <f>N37-G37</f>
         <v>410</v>
       </c>
       <c r="R37" s="85"/>
       <c r="S37" s="92" t="str">
-        <f t="shared" si="7"/>
+        <f>S28</f>
         <v>12002-81-020602-СПА.СО Изм.1; л.12 (поз 2.4.57.4)</v>
       </c>
       <c r="T37" s="86"/>
       <c r="U37" s="87"/>
       <c r="V37" s="106">
-        <f t="shared" si="8"/>
+        <f>SUM(X37+AA37+AD37+AG37)</f>
         <v>410</v>
       </c>
       <c r="W37" s="93"/>
@@ -6198,13 +6198,13 @@
       <c r="AB37" s="84"/>
       <c r="AC37" s="93"/>
       <c r="AD37" s="86">
-        <f t="shared" ref="AD37:AD38" si="11">AD28</f>
+        <f>AD28</f>
         <v>410</v>
       </c>
       <c r="AE37" s="84"/>
       <c r="AF37" s="93"/>
       <c r="AG37" s="86">
-        <f t="shared" si="9"/>
+        <f>AG28</f>
         <v>0</v>
       </c>
       <c r="AH37" s="84"/>
@@ -6250,24 +6250,24 @@
       <c r="L38" s="83"/>
       <c r="M38" s="83"/>
       <c r="N38" s="84">
-        <f t="shared" si="2"/>
+        <f>V38</f>
         <v>10</v>
       </c>
       <c r="O38" s="83"/>
       <c r="P38" s="83"/>
       <c r="Q38" s="84">
-        <f t="shared" si="3"/>
+        <f>N38-G38</f>
         <v>10</v>
       </c>
       <c r="R38" s="85"/>
       <c r="S38" s="92" t="str">
-        <f t="shared" si="7"/>
+        <f>S29</f>
         <v>12002-81-020601-СПА.1.1 СО Изм.1; л.3 (поз 49)</v>
       </c>
       <c r="T38" s="86"/>
       <c r="U38" s="78"/>
       <c r="V38" s="88">
-        <f t="shared" si="8"/>
+        <f>SUM(X38+AA38+AD38+AG38)</f>
         <v>10</v>
       </c>
       <c r="W38" s="89"/>
@@ -6278,13 +6278,13 @@
       <c r="AB38" s="83"/>
       <c r="AC38" s="93"/>
       <c r="AD38" s="86">
-        <f t="shared" si="11"/>
+        <f>AD29</f>
         <v>10</v>
       </c>
       <c r="AE38" s="83"/>
       <c r="AF38" s="93"/>
       <c r="AG38" s="86">
-        <f t="shared" si="9"/>
+        <f>AG29</f>
         <v>0</v>
       </c>
       <c r="AH38" s="83"/>
@@ -6347,7 +6347,7 @@
         <v>110514323</v>
       </c>
       <c r="L39" s="98" t="str">
-        <f t="shared" ref="L39:L69" si="12">S39</f>
+        <f>S39</f>
         <v>12002-81-0220-СПА.СО Изм2_, л.1 ( поз 2.1;2.2)
 12002-81-020601-АУПТ. СО1; Изм.0; 2л; поз(4.9; 4.10; 4.11; 4.12; 4.13) 6.л; поз(9.1.1; 9.1.2; 9.2.1; 9.2.2; 9.2.3)
 12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(2.9) 10л; поз(13.1; 13.2; 13.3; 13.4; 13.6; 13.7) 
@@ -6363,7 +6363,7 @@
       </c>
       <c r="M39" s="98"/>
       <c r="N39" s="99">
-        <f t="shared" si="2"/>
+        <f>V39</f>
         <v>116934</v>
       </c>
       <c r="O39" s="98">
@@ -6374,7 +6374,7 @@
         <v>110514323.4</v>
       </c>
       <c r="Q39" s="99">
-        <f t="shared" si="3"/>
+        <f>N39-G39</f>
         <v>116934</v>
       </c>
       <c r="R39" s="100">
@@ -6495,18 +6495,18 @@
       <c r="J40" s="84"/>
       <c r="K40" s="84"/>
       <c r="L40" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S40</f>
         <v>12002-81-0220-СПА.СО Изм2_, л.1 ( поз 2.1;2.2)</v>
       </c>
       <c r="M40" s="83"/>
       <c r="N40" s="84">
-        <f t="shared" si="2"/>
+        <f>V40</f>
         <v>205</v>
       </c>
       <c r="O40" s="83"/>
       <c r="P40" s="83"/>
       <c r="Q40" s="84">
-        <f t="shared" si="3"/>
+        <f>N40-G40</f>
         <v>205</v>
       </c>
       <c r="R40" s="85"/>
@@ -6516,7 +6516,7 @@
       <c r="T40" s="86"/>
       <c r="U40" s="87"/>
       <c r="V40" s="106">
-        <f t="shared" ref="V40:V45" si="13">SUM(X40+AA40+AD40+AG40)</f>
+        <f>SUM(X40+AA40+AD40+AG40)</f>
         <v>205</v>
       </c>
       <c r="W40" s="93"/>
@@ -6576,18 +6576,18 @@
       <c r="J41" s="84"/>
       <c r="K41" s="84"/>
       <c r="L41" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S41</f>
         <v>12002-81-020601-АУПТ. СО1; Изм.0; 2л; поз(4.9; 4.10; 4.11; 4.12; 4.13) 6.л; поз(9.1.1; 9.1.2; 9.2.1; 9.2.2; 9.2.3)</v>
       </c>
       <c r="M41" s="83"/>
       <c r="N41" s="84">
-        <f t="shared" si="2"/>
+        <f>V41</f>
         <v>11631</v>
       </c>
       <c r="O41" s="83"/>
       <c r="P41" s="83"/>
       <c r="Q41" s="84">
-        <f t="shared" si="3"/>
+        <f>N41-G41</f>
         <v>11631</v>
       </c>
       <c r="R41" s="85"/>
@@ -6597,7 +6597,7 @@
       <c r="T41" s="86"/>
       <c r="U41" s="87"/>
       <c r="V41" s="67">
-        <f t="shared" si="13"/>
+        <f>SUM(X41+AA41+AD41+AG41)</f>
         <v>11631</v>
       </c>
       <c r="W41" s="89"/>
@@ -6661,18 +6661,18 @@
       <c r="J42" s="84"/>
       <c r="K42" s="84"/>
       <c r="L42" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S42</f>
         <v>12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(2.9) 10л; поз(13.1; 13.2; 13.3; 13.4; 13.6; 13.7) </v>
       </c>
       <c r="M42" s="83"/>
       <c r="N42" s="84">
-        <f t="shared" si="2"/>
+        <f>V42</f>
         <v>13330</v>
       </c>
       <c r="O42" s="83"/>
       <c r="P42" s="83"/>
       <c r="Q42" s="84">
-        <f t="shared" si="3"/>
+        <f>N42-G42</f>
         <v>13330</v>
       </c>
       <c r="R42" s="85"/>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="U42" s="87"/>
       <c r="V42" s="106">
-        <f t="shared" si="13"/>
+        <f>SUM(X42+AA42+AD42+AG42)</f>
         <v>13330</v>
       </c>
       <c r="W42" s="93"/>
@@ -6744,18 +6744,18 @@
       <c r="J43" s="84"/>
       <c r="K43" s="84"/>
       <c r="L43" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S43</f>
         <v>12002-81-020601-АУПТ. СО4; Изм.0; 4л; поз(8.1; 8.2; 8.3; 8.4)</v>
       </c>
       <c r="M43" s="83"/>
       <c r="N43" s="84">
-        <f t="shared" si="2"/>
+        <f>V43</f>
         <v>3994</v>
       </c>
       <c r="O43" s="83"/>
       <c r="P43" s="83"/>
       <c r="Q43" s="84">
-        <f t="shared" si="3"/>
+        <f>N43-G43</f>
         <v>3994</v>
       </c>
       <c r="R43" s="85"/>
@@ -6765,7 +6765,7 @@
       <c r="T43" s="86"/>
       <c r="U43" s="87"/>
       <c r="V43" s="106">
-        <f t="shared" si="13"/>
+        <f>SUM(X43+AA43+AD43+AG43)</f>
         <v>3994</v>
       </c>
       <c r="W43" s="93"/>
@@ -6825,18 +6825,18 @@
       <c r="J44" s="84"/>
       <c r="K44" s="84"/>
       <c r="L44" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S44</f>
         <v>12002-81-020601-СПА.СО Изм.1 ; 2л; поз(4.5; 4.6; 4.7) 6л; поз(10.1; 10.2; 10.3; 10.4; 10.5; 10.6; 10.7; 10.8)</v>
       </c>
       <c r="M44" s="83"/>
       <c r="N44" s="84">
-        <f t="shared" si="2"/>
+        <f>V44</f>
         <v>26500</v>
       </c>
       <c r="O44" s="83"/>
       <c r="P44" s="83"/>
       <c r="Q44" s="84">
-        <f t="shared" si="3"/>
+        <f>N44-G44</f>
         <v>26500</v>
       </c>
       <c r="R44" s="85"/>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="U44" s="87"/>
       <c r="V44" s="106">
-        <f t="shared" si="13"/>
+        <f>SUM(X44+AA44+AD44+AG44)</f>
         <v>26500</v>
       </c>
       <c r="W44" s="89"/>
@@ -6908,18 +6908,18 @@
       <c r="J45" s="84"/>
       <c r="K45" s="84"/>
       <c r="L45" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S45</f>
         <v>12002-81-020602-АУПТ.СО1_Изм.0, 2л; поз(4.9) л.6 (поз 10.3.1;10.3.2;10.3.3;10.3.4;10.3.5;10.3.6;10.3.7;) л.7 (поз 10.3.19;10.3.20;)</v>
       </c>
       <c r="M45" s="83"/>
       <c r="N45" s="84">
-        <f t="shared" si="2"/>
+        <f>V45</f>
         <v>13281</v>
       </c>
       <c r="O45" s="83"/>
       <c r="P45" s="83"/>
       <c r="Q45" s="84">
-        <f t="shared" si="3"/>
+        <f>N45-G45</f>
         <v>13281</v>
       </c>
       <c r="R45" s="85"/>
@@ -6929,7 +6929,7 @@
       <c r="T45" s="86"/>
       <c r="U45" s="87"/>
       <c r="V45" s="106">
-        <f t="shared" si="13"/>
+        <f>SUM(X45+AA45+AD45+AG45)</f>
         <v>13281</v>
       </c>
       <c r="W45" s="93"/>
@@ -6989,18 +6989,18 @@
       <c r="J46" s="84"/>
       <c r="K46" s="84"/>
       <c r="L46" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S46</f>
         <v>12002-81-020602-СПА.СО.Изм1 л2-л3; (поз 1.4.4) л7; (поз 2.3.1; 2.3.2; 2.3.3; 2.3.4; 2.3.5; 2.3.6; 2.3.7; 2.3.8)</v>
       </c>
       <c r="M46" s="83"/>
       <c r="N46" s="84">
-        <f t="shared" si="2"/>
+        <f>V46</f>
         <v>38880</v>
       </c>
       <c r="O46" s="83"/>
       <c r="P46" s="83"/>
       <c r="Q46" s="84">
-        <f t="shared" si="3"/>
+        <f>N46-G46</f>
         <v>38880</v>
       </c>
       <c r="R46" s="85"/>
@@ -7074,18 +7074,18 @@
       <c r="J47" s="84"/>
       <c r="K47" s="84"/>
       <c r="L47" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S47</f>
         <v>12002-81-020603-СПА.СО_Изм.2_, л.5 (поз 2.3.1 ) л.6 (поз 2.3.2;2.3.3; 2.3.4;2.3.5;2.3.6;2.3.7,2.3.8)</v>
       </c>
       <c r="M47" s="83"/>
       <c r="N47" s="84">
-        <f t="shared" si="2"/>
+        <f>V47</f>
         <v>6084</v>
       </c>
       <c r="O47" s="83"/>
       <c r="P47" s="83"/>
       <c r="Q47" s="84">
-        <f t="shared" si="3"/>
+        <f>N47-G47</f>
         <v>6084</v>
       </c>
       <c r="R47" s="85"/>
@@ -7095,7 +7095,7 @@
       <c r="T47" s="86"/>
       <c r="U47" s="87"/>
       <c r="V47" s="106">
-        <f t="shared" ref="V47:V50" si="14">SUM(X47+AA47+AD47+AG47)</f>
+        <f>SUM(X47+AA47+AD47+AG47)</f>
         <v>6084</v>
       </c>
       <c r="W47" s="93"/>
@@ -7155,19 +7155,19 @@
       <c r="J48" s="83"/>
       <c r="K48" s="84"/>
       <c r="L48" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S48</f>
         <v>12002-81-020601-АУПТ1.1 СО1 Изм.0  л4 поз(8.1.1; 8.1.2; 8.2.1; 8.2.2)
 12002-81-020601-АУПТ1.1 СО3 Изм.0  л6 поз(10.1; 10.2; 10.3; 10.4)</v>
       </c>
       <c r="M48" s="83"/>
       <c r="N48" s="84">
-        <f t="shared" si="2"/>
+        <f>V48</f>
         <v>2361</v>
       </c>
       <c r="O48" s="84"/>
       <c r="P48" s="83"/>
       <c r="Q48" s="83">
-        <f t="shared" si="3"/>
+        <f>N48-G48</f>
         <v>2361</v>
       </c>
       <c r="R48" s="85"/>
@@ -7177,7 +7177,7 @@
       <c r="T48" s="86"/>
       <c r="U48" s="87"/>
       <c r="V48" s="106">
-        <f t="shared" si="14"/>
+        <f>SUM(X48+AA48+AD48+AG48)</f>
         <v>2361</v>
       </c>
       <c r="W48" s="89"/>
@@ -7237,18 +7237,18 @@
       <c r="J49" s="84"/>
       <c r="K49" s="84"/>
       <c r="L49" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S49</f>
         <v>12002-81-0220-СПА.СО; л.1; поз (1.3-чувствительный элемент)</v>
       </c>
       <c r="M49" s="83"/>
       <c r="N49" s="84">
-        <f t="shared" si="2"/>
+        <f>V49</f>
         <v>53</v>
       </c>
       <c r="O49" s="83"/>
       <c r="P49" s="83"/>
       <c r="Q49" s="83">
-        <f t="shared" si="3"/>
+        <f>N49-G49</f>
         <v>53</v>
       </c>
       <c r="R49" s="85"/>
@@ -7258,7 +7258,7 @@
       <c r="T49" s="86"/>
       <c r="U49" s="87"/>
       <c r="V49" s="106">
-        <f t="shared" si="14"/>
+        <f>SUM(X49+AA49+AD49+AG49)</f>
         <v>53</v>
       </c>
       <c r="W49" s="93"/>
@@ -7318,18 +7318,18 @@
       <c r="J50" s="84"/>
       <c r="K50" s="84"/>
       <c r="L50" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S50</f>
         <v>12002-81-020601-СПА.1.1 СО Изм.1; л.2 (поз 31; 32; 33; 34; 35; 36)</v>
       </c>
       <c r="M50" s="83"/>
       <c r="N50" s="84">
-        <f t="shared" si="2"/>
+        <f>V50</f>
         <v>615</v>
       </c>
       <c r="O50" s="83"/>
       <c r="P50" s="83"/>
       <c r="Q50" s="83">
-        <f t="shared" si="3"/>
+        <f>N50-G50</f>
         <v>615</v>
       </c>
       <c r="R50" s="85"/>
@@ -7339,7 +7339,7 @@
       <c r="T50" s="86"/>
       <c r="U50" s="87"/>
       <c r="V50" s="106">
-        <f t="shared" si="14"/>
+        <f>SUM(X50+AA50+AD50+AG50)</f>
         <v>615</v>
       </c>
       <c r="W50" s="93"/>
@@ -7419,7 +7419,7 @@
         <v>5338880</v>
       </c>
       <c r="L51" s="98" t="str">
-        <f t="shared" si="12"/>
+        <f>S51</f>
         <v>12002-81-020601-АУПТ. СО1; Изм.0; 9л; поз(12.1;)
 12002-81-020601-АУПТ. СО3; Изм.0; 7л; (поз 7.4.10) 14л; поз(14.1)
 12002-81-020601-АУПТ. СО2; Изм.0 л.56 (поз 24.9)
@@ -7446,7 +7446,7 @@
       </c>
       <c r="M51" s="98"/>
       <c r="N51" s="99">
-        <f t="shared" si="2"/>
+        <f>V51</f>
         <v>112208.5</v>
       </c>
       <c r="O51" s="98">
@@ -7457,7 +7457,7 @@
         <v>5338880.43</v>
       </c>
       <c r="Q51" s="98">
-        <f t="shared" si="3"/>
+        <f>N51-G51</f>
         <v>112208.5</v>
       </c>
       <c r="R51" s="99">
@@ -7589,31 +7589,31 @@
       <c r="J52" s="84"/>
       <c r="K52" s="84"/>
       <c r="L52" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S52</f>
         <v>12002-81-020601-АУПТ. СО1; Изм.0; 9л; поз(12.1;)
 12002-81-020601-АУПТ. СО3; Изм.0; 7л; (поз 7.4.10) 14л; поз(14.1)</v>
       </c>
       <c r="M52" s="83"/>
       <c r="N52" s="84">
-        <f t="shared" si="2"/>
+        <f>V52</f>
         <v>776</v>
       </c>
       <c r="O52" s="83"/>
       <c r="P52" s="83"/>
       <c r="Q52" s="83">
-        <f t="shared" si="3"/>
+        <f>N52-G52</f>
         <v>776</v>
       </c>
       <c r="R52" s="84"/>
       <c r="S52" s="112" t="str">
-        <f t="shared" ref="S52:S59" si="15">S31</f>
+        <f>S31</f>
         <v>12002-81-020601-АУПТ. СО1; Изм.0; 9л; поз(12.1;)
 12002-81-020601-АУПТ. СО3; Изм.0; 7л; (поз 7.4.10) 14л; поз(14.1)</v>
       </c>
       <c r="T52" s="113"/>
       <c r="U52" s="87"/>
       <c r="V52" s="106">
-        <f t="shared" ref="V52:V69" si="16">SUM(X52+AA52+AD52+AG52)</f>
+        <f>SUM(X52+AA52+AD52+AG52)</f>
         <v>776</v>
       </c>
       <c r="W52" s="93"/>
@@ -7627,7 +7627,7 @@
       <c r="AE52" s="84"/>
       <c r="AF52" s="93"/>
       <c r="AG52" s="110">
-        <f t="shared" ref="AG52:AG59" si="17">V22</f>
+        <f>V22</f>
         <v>776</v>
       </c>
       <c r="AH52" s="84"/>
@@ -7671,29 +7671,29 @@
       <c r="J53" s="84"/>
       <c r="K53" s="84"/>
       <c r="L53" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S53</f>
         <v>12002-81-020601-АУПТ. СО2; Изм.0 л.56 (поз 24.9)</v>
       </c>
       <c r="M53" s="83"/>
       <c r="N53" s="84">
-        <f t="shared" si="2"/>
+        <f>V53</f>
         <v>333.5</v>
       </c>
       <c r="O53" s="83"/>
       <c r="P53" s="83"/>
       <c r="Q53" s="83">
-        <f t="shared" si="3"/>
+        <f>N53-G53</f>
         <v>333.5</v>
       </c>
       <c r="R53" s="84"/>
       <c r="S53" s="112" t="str">
-        <f t="shared" si="15"/>
+        <f>S32</f>
         <v>12002-81-020601-АУПТ. СО2; Изм.0 л.56 (поз 24.9)</v>
       </c>
       <c r="T53" s="113"/>
       <c r="U53" s="87"/>
       <c r="V53" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X53+AA53+AD53+AG53)</f>
         <v>333.5</v>
       </c>
       <c r="W53" s="93"/>
@@ -7707,7 +7707,7 @@
       <c r="AE53" s="84"/>
       <c r="AF53" s="93"/>
       <c r="AG53" s="110">
-        <f t="shared" si="17"/>
+        <f>V23</f>
         <v>333.5</v>
       </c>
       <c r="AH53" s="84"/>
@@ -7751,29 +7751,29 @@
       <c r="J54" s="84"/>
       <c r="K54" s="84"/>
       <c r="L54" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S54</f>
         <v>12002-81-020601-СПА.СО;Изм.1; 9л; поз(11.46) л.10 (поз 11.48.4)</v>
       </c>
       <c r="M54" s="83"/>
       <c r="N54" s="84">
-        <f t="shared" si="2"/>
+        <f>V54</f>
         <v>380</v>
       </c>
       <c r="O54" s="83"/>
       <c r="P54" s="83"/>
       <c r="Q54" s="83">
-        <f t="shared" si="3"/>
+        <f>N54-G54</f>
         <v>380</v>
       </c>
       <c r="R54" s="84"/>
       <c r="S54" s="112" t="str">
-        <f t="shared" si="15"/>
+        <f>S33</f>
         <v>12002-81-020601-СПА.СО;Изм.1; 9л; поз(11.46) л.10 (поз 11.48.4)</v>
       </c>
       <c r="T54" s="113"/>
       <c r="U54" s="87"/>
       <c r="V54" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X54+AA54+AD54+AG54)</f>
         <v>380</v>
       </c>
       <c r="W54" s="93"/>
@@ -7787,7 +7787,7 @@
       <c r="AE54" s="84"/>
       <c r="AF54" s="93"/>
       <c r="AG54" s="110">
-        <f t="shared" si="17"/>
+        <f>V24</f>
         <v>380</v>
       </c>
       <c r="AH54" s="84"/>
@@ -7831,25 +7831,25 @@
       <c r="J55" s="84"/>
       <c r="K55" s="84"/>
       <c r="L55" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S55</f>
         <v>12002-81-020602-АУПТ.СО1; Изм.0; 10л; поз(10.4.35)
 12002-81-020602-АУПТ.СО2; Изм.0; 20л; поз(4.7)
 12002-81-020602-АУПТ.СО3; Изм.0; 3л; поз(2.7)</v>
       </c>
       <c r="M55" s="83"/>
       <c r="N55" s="84">
-        <f t="shared" si="2"/>
+        <f>V55</f>
         <v>326</v>
       </c>
       <c r="O55" s="83"/>
       <c r="P55" s="83"/>
       <c r="Q55" s="83">
-        <f t="shared" si="3"/>
+        <f>N55-G55</f>
         <v>326</v>
       </c>
       <c r="R55" s="84"/>
       <c r="S55" s="112" t="str">
-        <f t="shared" si="15"/>
+        <f>S34</f>
         <v>12002-81-020602-АУПТ.СО1; Изм.0; 10л; поз(10.4.35)
 12002-81-020602-АУПТ.СО2; Изм.0; 20л; поз(4.7)
 12002-81-020602-АУПТ.СО3; Изм.0; 3л; поз(2.7)</v>
@@ -7857,7 +7857,7 @@
       <c r="T55" s="113"/>
       <c r="U55" s="87"/>
       <c r="V55" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X55+AA55+AD55+AG55)</f>
         <v>326</v>
       </c>
       <c r="W55" s="93"/>
@@ -7871,7 +7871,7 @@
       <c r="AE55" s="84"/>
       <c r="AF55" s="93"/>
       <c r="AG55" s="110">
-        <f t="shared" si="17"/>
+        <f>V25</f>
         <v>326</v>
       </c>
       <c r="AH55" s="84"/>
@@ -7915,31 +7915,31 @@
       <c r="J56" s="84"/>
       <c r="K56" s="84"/>
       <c r="L56" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S56</f>
         <v>12002-81-020603-АУПТ.СО; Изм.2; 6л; поз(4.3)
 </v>
       </c>
       <c r="M56" s="83"/>
       <c r="N56" s="84">
-        <f t="shared" si="2"/>
+        <f>V56</f>
         <v>20</v>
       </c>
       <c r="O56" s="83"/>
       <c r="P56" s="83"/>
       <c r="Q56" s="83">
-        <f t="shared" si="3"/>
+        <f>N56-G56</f>
         <v>20</v>
       </c>
       <c r="R56" s="84"/>
       <c r="S56" s="112" t="str">
-        <f t="shared" si="15"/>
+        <f>S35</f>
         <v>12002-81-020603-АУПТ.СО; Изм.2; 6л; поз(4.3)
 </v>
       </c>
       <c r="T56" s="113"/>
       <c r="U56" s="87"/>
       <c r="V56" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X56+AA56+AD56+AG56)</f>
         <v>20</v>
       </c>
       <c r="W56" s="93"/>
@@ -7953,7 +7953,7 @@
       <c r="AE56" s="84"/>
       <c r="AF56" s="93"/>
       <c r="AG56" s="110">
-        <f t="shared" si="17"/>
+        <f>V26</f>
         <v>20</v>
       </c>
       <c r="AH56" s="84"/>
@@ -7997,25 +7997,25 @@
       <c r="J57" s="84"/>
       <c r="K57" s="84"/>
       <c r="L57" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S57</f>
         <v>12002-81-020601-АУПТ1.1 СО1 Изм.0 л6 поз(11.1)
 12002-81-020601-АУПТ1.1 СО2 Изм.0 л3 поз(6.3)
 12002-81-020601-АУПТ1.1 СО3 Изм.0 л4 поз(5.3.22)л8 поз(12.1)</v>
       </c>
       <c r="M57" s="83"/>
       <c r="N57" s="84">
-        <f t="shared" si="2"/>
+        <f>V57</f>
         <v>58</v>
       </c>
       <c r="O57" s="83"/>
       <c r="P57" s="83"/>
       <c r="Q57" s="83">
-        <f t="shared" si="3"/>
+        <f>N57-G57</f>
         <v>58</v>
       </c>
       <c r="R57" s="84"/>
       <c r="S57" s="112" t="str">
-        <f t="shared" si="15"/>
+        <f>S36</f>
         <v>12002-81-020601-АУПТ1.1 СО1 Изм.0 л6 поз(11.1)
 12002-81-020601-АУПТ1.1 СО2 Изм.0 л3 поз(6.3)
 12002-81-020601-АУПТ1.1 СО3 Изм.0 л4 поз(5.3.22)л8 поз(12.1)</v>
@@ -8023,7 +8023,7 @@
       <c r="T57" s="113"/>
       <c r="U57" s="87"/>
       <c r="V57" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X57+AA57+AD57+AG57)</f>
         <v>58</v>
       </c>
       <c r="W57" s="93"/>
@@ -8037,7 +8037,7 @@
       <c r="AE57" s="84"/>
       <c r="AF57" s="93"/>
       <c r="AG57" s="110">
-        <f t="shared" si="17"/>
+        <f>V27</f>
         <v>58</v>
       </c>
       <c r="AH57" s="84"/>
@@ -8081,29 +8081,29 @@
       <c r="J58" s="84"/>
       <c r="K58" s="84"/>
       <c r="L58" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S58</f>
         <v>12002-81-020602-СПА.СО Изм.1; л.12 (поз 2.4.57.4)</v>
       </c>
       <c r="M58" s="83"/>
       <c r="N58" s="84">
-        <f t="shared" si="2"/>
+        <f>V58</f>
         <v>410</v>
       </c>
       <c r="O58" s="83"/>
       <c r="P58" s="83"/>
       <c r="Q58" s="83">
-        <f t="shared" si="3"/>
+        <f>N58-G58</f>
         <v>410</v>
       </c>
       <c r="R58" s="84"/>
       <c r="S58" s="112" t="str">
-        <f t="shared" si="15"/>
+        <f>S37</f>
         <v>12002-81-020602-СПА.СО Изм.1; л.12 (поз 2.4.57.4)</v>
       </c>
       <c r="T58" s="113"/>
       <c r="U58" s="87"/>
       <c r="V58" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X58+AA58+AD58+AG58)</f>
         <v>410</v>
       </c>
       <c r="W58" s="93"/>
@@ -8117,7 +8117,7 @@
       <c r="AE58" s="84"/>
       <c r="AF58" s="93"/>
       <c r="AG58" s="110">
-        <f t="shared" si="17"/>
+        <f>V28</f>
         <v>410</v>
       </c>
       <c r="AH58" s="84"/>
@@ -8161,29 +8161,29 @@
       <c r="J59" s="84"/>
       <c r="K59" s="84"/>
       <c r="L59" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S59</f>
         <v>12002-81-020601-СПА.1.1 СО Изм.1; л.3 (поз 49)</v>
       </c>
       <c r="M59" s="83"/>
       <c r="N59" s="84">
-        <f t="shared" si="2"/>
+        <f>V59</f>
         <v>10</v>
       </c>
       <c r="O59" s="83"/>
       <c r="P59" s="83"/>
       <c r="Q59" s="83">
-        <f t="shared" si="3"/>
+        <f>N59-G59</f>
         <v>10</v>
       </c>
       <c r="R59" s="84"/>
       <c r="S59" s="112" t="str">
-        <f t="shared" si="15"/>
+        <f>S38</f>
         <v>12002-81-020601-СПА.1.1 СО Изм.1; л.3 (поз 49)</v>
       </c>
       <c r="T59" s="113"/>
       <c r="U59" s="87"/>
       <c r="V59" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X59+AA59+AD59+AG59)</f>
         <v>10</v>
       </c>
       <c r="W59" s="93"/>
@@ -8197,7 +8197,7 @@
       <c r="AE59" s="84"/>
       <c r="AF59" s="93"/>
       <c r="AG59" s="110">
-        <f t="shared" si="17"/>
+        <f>V29</f>
         <v>10</v>
       </c>
       <c r="AH59" s="93"/>
@@ -8241,18 +8241,18 @@
       <c r="J60" s="84"/>
       <c r="K60" s="84"/>
       <c r="L60" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S60</f>
         <v>12002-81-0220-СПА.СО Изм2_, л.1 ( поз 2.1;2.2)</v>
       </c>
       <c r="M60" s="83"/>
       <c r="N60" s="84">
-        <f t="shared" si="2"/>
+        <f>V60</f>
         <v>205</v>
       </c>
       <c r="O60" s="83"/>
       <c r="P60" s="83"/>
       <c r="Q60" s="83">
-        <f t="shared" si="3"/>
+        <f>N60-G60</f>
         <v>205</v>
       </c>
       <c r="R60" s="84"/>
@@ -8263,7 +8263,7 @@
       <c r="T60" s="113"/>
       <c r="U60" s="87"/>
       <c r="V60" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X60+AA60+AD60+AG60)</f>
         <v>205</v>
       </c>
       <c r="W60" s="93"/>
@@ -8323,18 +8323,18 @@
       <c r="J61" s="84"/>
       <c r="K61" s="84"/>
       <c r="L61" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S61</f>
         <v>12002-81-020601-АУПТ. СО1; Изм.0; 6.л; поз(9.1.1; 9.1.2; 9.2.1; 9.2.2; 9.2.3)</v>
       </c>
       <c r="M61" s="83"/>
       <c r="N61" s="84">
-        <f t="shared" si="2"/>
+        <f>V61</f>
         <v>11161</v>
       </c>
       <c r="O61" s="83"/>
       <c r="P61" s="83"/>
       <c r="Q61" s="83">
-        <f t="shared" si="3"/>
+        <f>N61-G61</f>
         <v>11161</v>
       </c>
       <c r="R61" s="84"/>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="U61" s="87"/>
       <c r="V61" s="67">
-        <f t="shared" si="16"/>
+        <f>SUM(X61+AA61+AD61+AG61)</f>
         <v>11161</v>
       </c>
       <c r="W61" s="93"/>
@@ -8408,18 +8408,18 @@
       <c r="J62" s="84"/>
       <c r="K62" s="84"/>
       <c r="L62" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S62</f>
         <v>12002-81-020601-АУПТ. СО3; Изм.0; 10л; поз(13.1; 13.2; 13.3; 13.4; 13.6; 13.7) </v>
       </c>
       <c r="M62" s="83"/>
       <c r="N62" s="84">
-        <f t="shared" si="2"/>
+        <f>V62</f>
         <v>13250</v>
       </c>
       <c r="O62" s="83"/>
       <c r="P62" s="83"/>
       <c r="Q62" s="83">
-        <f t="shared" si="3"/>
+        <f>N62-G62</f>
         <v>13250</v>
       </c>
       <c r="R62" s="84"/>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="U62" s="87"/>
       <c r="V62" s="115">
-        <f t="shared" si="16"/>
+        <f>SUM(X62+AA62+AD62+AG62)</f>
         <v>13250</v>
       </c>
       <c r="W62" s="93"/>
@@ -8493,18 +8493,18 @@
       <c r="J63" s="84"/>
       <c r="K63" s="84"/>
       <c r="L63" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S63</f>
         <v>12002-81-020601-АУПТ. СО4; Изм.0; 4л; поз(8.1; 8.2; 8.3; 8.4)</v>
       </c>
       <c r="M63" s="83"/>
       <c r="N63" s="84">
-        <f t="shared" si="2"/>
+        <f>V63</f>
         <v>3994</v>
       </c>
       <c r="O63" s="83"/>
       <c r="P63" s="83"/>
       <c r="Q63" s="83">
-        <f t="shared" si="3"/>
+        <f>N63-G63</f>
         <v>3994</v>
       </c>
       <c r="R63" s="84"/>
@@ -8515,7 +8515,7 @@
       <c r="T63" s="113"/>
       <c r="U63" s="87"/>
       <c r="V63" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X63+AA63+AD63+AG63)</f>
         <v>3994</v>
       </c>
       <c r="W63" s="93"/>
@@ -8573,18 +8573,18 @@
       <c r="J64" s="84"/>
       <c r="K64" s="84"/>
       <c r="L64" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S64</f>
         <v>12002-81-020601-СПА.СО Изм.1; 6л; поз(10.1; 10.2; 10.3; 10.4; 10.5; 10.6; 10.7; 10.8)</v>
       </c>
       <c r="M64" s="83"/>
       <c r="N64" s="84">
-        <f t="shared" si="2"/>
+        <f>V64</f>
         <v>25040</v>
       </c>
       <c r="O64" s="83"/>
       <c r="P64" s="83"/>
       <c r="Q64" s="83">
-        <f t="shared" si="3"/>
+        <f>N64-G64</f>
         <v>25040</v>
       </c>
       <c r="R64" s="84"/>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="U64" s="87"/>
       <c r="V64" s="116">
-        <f t="shared" si="16"/>
+        <f>SUM(X64+AA64+AD64+AG64)</f>
         <v>25040</v>
       </c>
       <c r="W64" s="93"/>
@@ -8658,18 +8658,18 @@
       <c r="J65" s="84"/>
       <c r="K65" s="84"/>
       <c r="L65" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S65</f>
         <v>12002-81-020602-АУПТ.СО1_Изм.0, л.6 (поз 10.3.1;10.3.2;10.3.3;10.3.4;10.3.5;10.3.6;10.3.7;) л.7 (поз 10.3.19;10.3.20;)</v>
       </c>
       <c r="M65" s="83"/>
       <c r="N65" s="84">
-        <f t="shared" si="2"/>
+        <f>V65</f>
         <v>13185</v>
       </c>
       <c r="O65" s="83"/>
       <c r="P65" s="83"/>
       <c r="Q65" s="83">
-        <f t="shared" si="3"/>
+        <f>N65-G65</f>
         <v>13185</v>
       </c>
       <c r="R65" s="84"/>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="U65" s="87"/>
       <c r="V65" s="116">
-        <f t="shared" si="16"/>
+        <f>SUM(X65+AA65+AD65+AG65)</f>
         <v>13185</v>
       </c>
       <c r="W65" s="93"/>
@@ -8743,18 +8743,18 @@
       <c r="J66" s="84"/>
       <c r="K66" s="84"/>
       <c r="L66" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S66</f>
         <v>12002-81-020602-СПА.СО.Изм.0 л6; (поз 2.3.1; 2.3.2; 2.3.3; 2.3.4; 2.3.5; 2.3.6; 2.3.7; 2.3.8)</v>
       </c>
       <c r="M66" s="83"/>
       <c r="N66" s="84">
-        <f t="shared" si="2"/>
+        <f>V66</f>
         <v>34000</v>
       </c>
       <c r="O66" s="83"/>
       <c r="P66" s="83"/>
       <c r="Q66" s="83">
-        <f t="shared" si="3"/>
+        <f>N66-G66</f>
         <v>34000</v>
       </c>
       <c r="R66" s="84"/>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="U66" s="87"/>
       <c r="V66" s="116">
-        <f t="shared" si="16"/>
+        <f>SUM(X66+AA66+AD66+AG66)</f>
         <v>34000</v>
       </c>
       <c r="W66" s="93"/>
@@ -8828,29 +8828,29 @@
       <c r="J67" s="84"/>
       <c r="K67" s="84"/>
       <c r="L67" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S67</f>
         <v>12002-81-020603-СПА.СО_Изм.2_, л.5 (поз 2.3.1 ) л.6 (поз 2.3.2;2.3.3; 2.3.4;2.3.5;2.3.6;2.3.7,2.3.8)</v>
       </c>
       <c r="M67" s="83"/>
       <c r="N67" s="84">
-        <f t="shared" si="2"/>
+        <f>V67</f>
         <v>6084</v>
       </c>
       <c r="O67" s="83"/>
       <c r="P67" s="83"/>
       <c r="Q67" s="83">
-        <f t="shared" si="3"/>
+        <f>N67-G67</f>
         <v>6084</v>
       </c>
       <c r="R67" s="84"/>
       <c r="S67" s="112" t="str">
-        <f t="shared" ref="S67:S68" si="18">S47</f>
+        <f>S47</f>
         <v>12002-81-020603-СПА.СО_Изм.2_, л.5 (поз 2.3.1 ) л.6 (поз 2.3.2;2.3.3; 2.3.4;2.3.5;2.3.6;2.3.7,2.3.8)</v>
       </c>
       <c r="T67" s="113"/>
       <c r="U67" s="87"/>
       <c r="V67" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X67+AA67+AD67+AG67)</f>
         <v>6084</v>
       </c>
       <c r="W67" s="93"/>
@@ -8910,31 +8910,31 @@
       <c r="J68" s="84"/>
       <c r="K68" s="84"/>
       <c r="L68" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S68</f>
         <v>12002-81-020601-АУПТ1.1 СО1 Изм.0  л4 поз(8.1.1; 8.1.2; 8.2.1; 8.2.2)
 12002-81-020601-АУПТ1.1 СО3 Изм.0  л6 поз(10.1; 10.2; 10.3; 10.4)</v>
       </c>
       <c r="M68" s="83"/>
       <c r="N68" s="84">
-        <f t="shared" si="2"/>
+        <f>V68</f>
         <v>2361</v>
       </c>
       <c r="O68" s="83"/>
       <c r="P68" s="83"/>
       <c r="Q68" s="83">
-        <f t="shared" si="3"/>
+        <f>N68-G68</f>
         <v>2361</v>
       </c>
       <c r="R68" s="84"/>
       <c r="S68" s="112" t="str">
-        <f t="shared" si="18"/>
+        <f>S48</f>
         <v>12002-81-020601-АУПТ1.1 СО1 Изм.0  л4 поз(8.1.1; 8.1.2; 8.2.1; 8.2.2)
 12002-81-020601-АУПТ1.1 СО3 Изм.0  л6 поз(10.1; 10.2; 10.3; 10.4)</v>
       </c>
       <c r="T68" s="113"/>
       <c r="U68" s="87"/>
       <c r="V68" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X68+AA68+AD68+AG68)</f>
         <v>2361</v>
       </c>
       <c r="W68" s="93"/>
@@ -8992,18 +8992,18 @@
       <c r="J69" s="84"/>
       <c r="K69" s="84"/>
       <c r="L69" s="83" t="str">
-        <f t="shared" si="12"/>
+        <f>S69</f>
         <v>12002-81-020601-СПА.1.1 СО Изм.1; л.2 (поз 31; 32; 33; 34; 35; 36)</v>
       </c>
       <c r="M69" s="83"/>
       <c r="N69" s="84">
-        <f t="shared" si="2"/>
+        <f>V69</f>
         <v>615</v>
       </c>
       <c r="O69" s="83"/>
       <c r="P69" s="83"/>
       <c r="Q69" s="83">
-        <f t="shared" si="3"/>
+        <f>N69-G69</f>
         <v>615</v>
       </c>
       <c r="R69" s="84"/>
@@ -9014,7 +9014,7 @@
       <c r="T69" s="113"/>
       <c r="U69" s="87"/>
       <c r="V69" s="106">
-        <f t="shared" si="16"/>
+        <f>SUM(X69+AA69+AD69+AG69)</f>
         <v>615</v>
       </c>
       <c r="W69" s="93"/>
@@ -9079,15 +9079,15 @@
         <v>2712.84</v>
       </c>
       <c r="I70" s="83">
-        <f t="shared" ref="I70:I81" si="19">G70*H70</f>
+        <f>G70*H70</f>
         <v>0</v>
       </c>
       <c r="J70" s="84">
-        <f t="shared" ref="J70:J81" si="20">V70-G70</f>
+        <f>V70-G70</f>
         <v>113311.2</v>
       </c>
       <c r="K70" s="84">
-        <f t="shared" ref="K70:K81" si="21">ROUND(P70-I70,0)</f>
+        <f>ROUND(P70-I70,0)</f>
         <v>350799011</v>
       </c>
       <c r="L70" s="83" t="str">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="M70" s="83"/>
       <c r="N70" s="84">
-        <f t="shared" si="2"/>
+        <f>V70</f>
         <v>113311.2</v>
       </c>
       <c r="O70" s="83">
@@ -9117,7 +9117,7 @@
         <v>350799011</v>
       </c>
       <c r="Q70" s="83">
-        <f t="shared" si="3"/>
+        <f>N70-G70</f>
         <v>113311.2</v>
       </c>
       <c r="R70" s="84">
@@ -9235,30 +9235,30 @@
         <v>2712.84</v>
       </c>
       <c r="I71" s="83">
-        <f t="shared" si="19"/>
+        <f>G71*H71</f>
         <v>0</v>
       </c>
       <c r="J71" s="84">
-        <f t="shared" si="20"/>
+        <f>V71-G71</f>
         <v>205</v>
       </c>
       <c r="K71" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P71-I71,0)</f>
         <v>0</v>
       </c>
       <c r="L71" s="83" t="str">
-        <f t="shared" ref="L71:L80" si="22">S71</f>
+        <f>S71</f>
         <v>12002-81-0220-СПА.СО Изм2_, л.1 ( поз 2.3)</v>
       </c>
       <c r="M71" s="83"/>
       <c r="N71" s="84">
-        <f t="shared" si="2"/>
+        <f>V71</f>
         <v>205</v>
       </c>
       <c r="O71" s="83"/>
       <c r="P71" s="83"/>
       <c r="Q71" s="83">
-        <f t="shared" si="3"/>
+        <f>N71-G71</f>
         <v>205</v>
       </c>
       <c r="R71" s="84"/>
@@ -9268,7 +9268,7 @@
       <c r="T71" s="113"/>
       <c r="U71" s="87"/>
       <c r="V71" s="106">
-        <f t="shared" ref="V71:V76" si="23">SUM(X71+AA71+AD71+AG71)</f>
+        <f>SUM(X71+AA71+AD71+AG71)</f>
         <v>205</v>
       </c>
       <c r="W71" s="93"/>
@@ -9331,30 +9331,30 @@
         <v>2712.84</v>
       </c>
       <c r="I72" s="83">
-        <f t="shared" si="19"/>
+        <f>G72*H72</f>
         <v>0</v>
       </c>
       <c r="J72" s="84">
-        <f t="shared" si="20"/>
+        <f>V72-G72</f>
         <v>10420</v>
       </c>
       <c r="K72" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P72-I72,0)</f>
         <v>0</v>
       </c>
       <c r="L72" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S72</f>
         <v>12002-81-020601-АУПТ. СО1_Изм.0,л.6.п(9.3.1, 9.3.2; 9.3.9) 7.п(9.4.3)</v>
       </c>
       <c r="M72" s="83"/>
       <c r="N72" s="84">
-        <f t="shared" si="2"/>
+        <f>V72</f>
         <v>10420</v>
       </c>
       <c r="O72" s="83"/>
       <c r="P72" s="83"/>
       <c r="Q72" s="83">
-        <f t="shared" si="3"/>
+        <f>N72-G72</f>
         <v>10420</v>
       </c>
       <c r="R72" s="84"/>
@@ -9368,7 +9368,7 @@
         <v>124</v>
       </c>
       <c r="V72" s="106">
-        <f t="shared" si="23"/>
+        <f>SUM(X72+AA72+AD72+AG72)</f>
         <v>10420</v>
       </c>
       <c r="W72" s="93"/>
@@ -9427,30 +9427,30 @@
         <v>2712.84</v>
       </c>
       <c r="I73" s="83">
-        <f t="shared" si="19"/>
+        <f>G73*H73</f>
         <v>0</v>
       </c>
       <c r="J73" s="84">
-        <f t="shared" si="20"/>
+        <f>V73-G73</f>
         <v>12017.2</v>
       </c>
       <c r="K73" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P73-I73,0)</f>
         <v>0</v>
       </c>
       <c r="L73" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S73</f>
         <v>12002-81-020601-АУПТ. СО3_Изм.0, л.10 (поз 13.5) л.13 (поз 13.73)</v>
       </c>
       <c r="M73" s="83"/>
       <c r="N73" s="84">
-        <f t="shared" si="2"/>
+        <f>V73</f>
         <v>12017.2</v>
       </c>
       <c r="O73" s="83"/>
       <c r="P73" s="83"/>
       <c r="Q73" s="83">
-        <f t="shared" si="3"/>
+        <f>N73-G73</f>
         <v>12017.2</v>
       </c>
       <c r="R73" s="84"/>
@@ -9464,7 +9464,7 @@
         <v>124</v>
       </c>
       <c r="V73" s="106">
-        <f t="shared" si="23"/>
+        <f>SUM(X73+AA73+AD73+AG73)</f>
         <v>12017.2</v>
       </c>
       <c r="W73" s="93"/>
@@ -9527,30 +9527,30 @@
         <v>2712.84</v>
       </c>
       <c r="I74" s="83">
-        <f t="shared" si="19"/>
+        <f>G74*H74</f>
         <v>0</v>
       </c>
       <c r="J74" s="84">
-        <f t="shared" si="20"/>
+        <f>V74-G74</f>
         <v>3174</v>
       </c>
       <c r="K74" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P74-I74,0)</f>
         <v>0</v>
       </c>
       <c r="L74" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S74</f>
         <v>12002-81-020601-АУПТ. СО4_Изм.0, л.3; (поз7.9) л.4 (поз 8.5) л.5(поз 9.13)</v>
       </c>
       <c r="M74" s="83"/>
       <c r="N74" s="84">
-        <f t="shared" si="2"/>
+        <f>V74</f>
         <v>3174</v>
       </c>
       <c r="O74" s="83"/>
       <c r="P74" s="83"/>
       <c r="Q74" s="83">
-        <f t="shared" si="3"/>
+        <f>N74-G74</f>
         <v>3174</v>
       </c>
       <c r="R74" s="84"/>
@@ -9564,7 +9564,7 @@
         <v>124</v>
       </c>
       <c r="V74" s="106">
-        <f t="shared" si="23"/>
+        <f>SUM(X74+AA74+AD74+AG74)</f>
         <v>3174</v>
       </c>
       <c r="W74" s="93"/>
@@ -9623,30 +9623,30 @@
         <v>2712.84</v>
       </c>
       <c r="I75" s="83">
-        <f t="shared" si="19"/>
+        <f>G75*H75</f>
         <v>0</v>
       </c>
       <c r="J75" s="84">
-        <f t="shared" si="20"/>
+        <f>V75-G75</f>
         <v>23352</v>
       </c>
       <c r="K75" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P75-I75,0)</f>
         <v>0</v>
       </c>
       <c r="L75" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S75</f>
         <v>12002-81-020601-СПА. СО_Изм.1, л.2 (поз 5.3) л.6 (поз 10.9, 10.11;10.12) л.7(поз10.21) л.9 ( поз 11.32)</v>
       </c>
       <c r="M75" s="83"/>
       <c r="N75" s="84">
-        <f t="shared" si="2"/>
+        <f>V75</f>
         <v>23352</v>
       </c>
       <c r="O75" s="83"/>
       <c r="P75" s="83"/>
       <c r="Q75" s="83">
-        <f t="shared" si="3"/>
+        <f>N75-G75</f>
         <v>23352</v>
       </c>
       <c r="R75" s="84"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="U75" s="87"/>
       <c r="V75" s="67">
-        <f t="shared" si="23"/>
+        <f>SUM(X75+AA75+AD75+AG75)</f>
         <v>23352</v>
       </c>
       <c r="W75" s="93"/>
@@ -9722,30 +9722,30 @@
         <v>2712.84</v>
       </c>
       <c r="I76" s="83">
-        <f t="shared" si="19"/>
+        <f>G76*H76</f>
         <v>0</v>
       </c>
       <c r="J76" s="84">
-        <f t="shared" si="20"/>
+        <f>V76-G76</f>
         <v>11578</v>
       </c>
       <c r="K76" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P76-I76,0)</f>
         <v>0</v>
       </c>
       <c r="L76" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S76</f>
         <v>12002-81-020602-АУПТ.СО1_Изм.0, л.2 (поз 5.4)  л.7 (поз 10.3.8;10.3.9) </v>
       </c>
       <c r="M76" s="83"/>
       <c r="N76" s="84">
-        <f t="shared" si="2"/>
+        <f>V76</f>
         <v>11578</v>
       </c>
       <c r="O76" s="83"/>
       <c r="P76" s="83"/>
       <c r="Q76" s="83">
-        <f t="shared" si="3"/>
+        <f>N76-G76</f>
         <v>11578</v>
       </c>
       <c r="R76" s="84"/>
@@ -9755,7 +9755,7 @@
       <c r="T76" s="113"/>
       <c r="U76" s="87"/>
       <c r="V76" s="112">
-        <f t="shared" si="23"/>
+        <f>SUM(X76+AA76+AD76+AG76)</f>
         <v>11578</v>
       </c>
       <c r="W76" s="93"/>
@@ -9814,30 +9814,30 @@
         <v>2712.84</v>
       </c>
       <c r="I77" s="83">
-        <f t="shared" si="19"/>
+        <f>G77*H77</f>
         <v>0</v>
       </c>
       <c r="J77" s="84">
-        <f t="shared" si="20"/>
+        <f>V77-G77</f>
         <v>42750</v>
       </c>
       <c r="K77" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P77-I77,0)</f>
         <v>0</v>
       </c>
       <c r="L77" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S77</f>
         <v>12002-81-020602-СПА.СО.Изм.1, л.3 (п.1.5.4) л.7 (п.2.1.11) л.6 (поз 2.3.9;2.3.11;2.3.12) л.8 (поз 2.3.22)  л.11 (2.4.43)</v>
       </c>
       <c r="M77" s="83"/>
       <c r="N77" s="84">
-        <f t="shared" si="2"/>
+        <f>V77</f>
         <v>42750</v>
       </c>
       <c r="O77" s="83"/>
       <c r="P77" s="83"/>
       <c r="Q77" s="83">
-        <f t="shared" si="3"/>
+        <f>N77-G77</f>
         <v>42750</v>
       </c>
       <c r="R77" s="84"/>
@@ -9914,30 +9914,30 @@
         <v>2712.84</v>
       </c>
       <c r="I78" s="83">
-        <f t="shared" si="19"/>
+        <f>G78*H78</f>
         <v>0</v>
       </c>
       <c r="J78" s="84">
-        <f t="shared" si="20"/>
+        <f>V78-G78</f>
         <v>6886</v>
       </c>
       <c r="K78" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P78-I78,0)</f>
         <v>0</v>
       </c>
       <c r="L78" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S78</f>
         <v>12002-81-020603-СПА.СО_Изм.2,л.6 (поз 2.3.9;2.3.11;2.3.12;2.3.13)</v>
       </c>
       <c r="M78" s="83"/>
       <c r="N78" s="84">
-        <f t="shared" si="2"/>
+        <f>V78</f>
         <v>6886</v>
       </c>
       <c r="O78" s="83"/>
       <c r="P78" s="83"/>
       <c r="Q78" s="83">
-        <f t="shared" si="3"/>
+        <f>N78-G78</f>
         <v>6886</v>
       </c>
       <c r="R78" s="84"/>
@@ -9951,7 +9951,7 @@
         <v>143</v>
       </c>
       <c r="V78" s="112">
-        <f t="shared" ref="V78:V80" si="24">SUM(X78+AA78+AD78+AG78)</f>
+        <f>SUM(X78+AA78+AD78+AG78)</f>
         <v>6886</v>
       </c>
       <c r="W78" s="93"/>
@@ -10010,31 +10010,31 @@
         <v>2712.84</v>
       </c>
       <c r="I79" s="83">
-        <f t="shared" si="19"/>
+        <f>G79*H79</f>
         <v>0</v>
       </c>
       <c r="J79" s="84">
-        <f t="shared" si="20"/>
+        <f>V79-G79</f>
         <v>2329</v>
       </c>
       <c r="K79" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P79-I79,0)</f>
         <v>0</v>
       </c>
       <c r="L79" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S79</f>
         <v>12002-81-020601-АУПТ1.1 СО1 Изм.0  л4 поз(8.3.1; 8.3.2)
 12002-81-020601-АУПТ1.1 СО3 Изм.0  л6 поз(10.5)</v>
       </c>
       <c r="M79" s="83"/>
       <c r="N79" s="84">
-        <f t="shared" si="2"/>
+        <f>V79</f>
         <v>2329</v>
       </c>
       <c r="O79" s="83"/>
       <c r="P79" s="83"/>
       <c r="Q79" s="83">
-        <f t="shared" si="3"/>
+        <f>N79-G79</f>
         <v>2329</v>
       </c>
       <c r="R79" s="84"/>
@@ -10044,7 +10044,7 @@
       <c r="T79" s="113"/>
       <c r="U79" s="87"/>
       <c r="V79" s="106">
-        <f t="shared" si="24"/>
+        <f>SUM(X79+AA79+AD79+AG79)</f>
         <v>2329</v>
       </c>
       <c r="W79" s="93"/>
@@ -10103,30 +10103,30 @@
         <v>2712.84</v>
       </c>
       <c r="I80" s="83">
-        <f t="shared" si="19"/>
+        <f>G80*H80</f>
         <v>0</v>
       </c>
       <c r="J80" s="84">
-        <f t="shared" si="20"/>
+        <f>V80-G80</f>
         <v>600</v>
       </c>
       <c r="K80" s="84">
-        <f t="shared" si="21"/>
+        <f>ROUND(P80-I80,0)</f>
         <v>0</v>
       </c>
       <c r="L80" s="83" t="str">
-        <f t="shared" si="22"/>
+        <f>S80</f>
         <v>12002-81-020601-СПА1.1. Изм.0;  л2 поз(37)</v>
       </c>
       <c r="M80" s="83"/>
       <c r="N80" s="84">
-        <f t="shared" si="2"/>
+        <f>V80</f>
         <v>600</v>
       </c>
       <c r="O80" s="83"/>
       <c r="P80" s="83"/>
       <c r="Q80" s="83">
-        <f t="shared" si="3"/>
+        <f>N80-G80</f>
         <v>600</v>
       </c>
       <c r="R80" s="84"/>
@@ -10136,7 +10136,7 @@
       <c r="T80" s="113"/>
       <c r="U80" s="87"/>
       <c r="V80" s="106">
-        <f t="shared" si="24"/>
+        <f>SUM(X80+AA80+AD80+AG80)</f>
         <v>600</v>
       </c>
       <c r="W80" s="93"/>
@@ -10181,104 +10181,109 @@
       <c r="BE80" s="13"/>
       <c r="BF80" s="13"/>
     </row>
-    <row r="81" ht="197.25" customHeight="1" collapsed="1">
+    <row r="81" ht="372.75" customHeight="1" collapsed="1">
       <c r="A81" s="13"/>
       <c r="B81" s="77"/>
       <c r="C81" s="78" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="D81" s="94">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="E81" s="94" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="F81" s="96" t="s">
         <v>49</v>
       </c>
       <c r="G81" s="82">
-        <f>SUM(G82)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H81" s="83">
+        <v>5534.75</v>
+      </c>
+      <c r="I81" s="83">
+        <f>G81*H81</f>
         <v>0</v>
       </c>
-      <c r="H81" s="83">
-        <v>19181.02</v>
-      </c>
-      <c r="I81" s="83">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
       <c r="J81" s="84">
-        <f t="shared" si="20"/>
-        <v>1007</v>
+        <f>V81-G81</f>
+        <v>3742</v>
       </c>
       <c r="K81" s="84">
-        <f t="shared" si="21"/>
-        <v>23916190</v>
+        <f>ROUND(P81-I81,0)</f>
+        <v>23635445</v>
       </c>
       <c r="L81" s="83" t="str">
         <f>TEXTJOIN("; 
-",FALSE(),L82,L83,L84,L85,L86,L87,L88,L89)</f>
-        <v>12002-81-0220-СПА.СО; л.1; поз (1.1.1; 1.1.2; 1.1.3; 1.1.4; 1.3-блок обработки на 2 шлейфа МИП-2); 
-12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(1.1; 1.2) 2л; поз(3.1; 3.2; 3.3; 3.5;4.6); 
-12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(1.1; 2.8) 2л; поз(3.1,3.2; 3.3; 3.6; 3.7); 
-12002-81-020601-АУПТ. СО4; Изм.0, л.1 (поз 2.2; 2.4); 
-12002-81-020601-СПА. СО; Изм.1; 1л; поз(1.1; 1.2; 1.3; 1.4; 1.5) 2л; поз(3.1; 3.2; 3.3; 3.4; 3.7; 4.2) 4л; поз(7.9); 
-12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(1.1; 3.1 ) 2л; поз( 3.2; 3.3; 3.4; 3.9; 4.8) 4л; поз(9.6;); 
-12002-81-020602-СПА.СО.Изм.1; 1л; поз(1.1.1) 2л; поз(1.3.1; 1.3.2; 1.3.3; 1.3.4; 1.3.7; 1.4.2; 1.4.3; 4; л5 поз (1.7.6); 
-12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.1.1; 1.3.1; 1.3.2; 1.3.3;) 2л; поз(1.3.4; 1.3.7; 1.3.8)</v>
+",FALSE(),L82,L83,L84,L85,L86,L87,L88,L89,L90)</f>
+        <v>12002-81-0220-СПА.СО Изм2_, л.1  (поз1.1.5; 1.2; 1.4;1.5;1.6); 
+12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(2.1; 2.4; 2.5; 2.6; 2.7; 2.8) 2л; поз(3.4; 3.6; 4.1; 4.2; 4.4;) 3л; поз(5.1;5.2,5,3;5,4;5,5;5,6); 
+12002-81-020601-АУПТ. СО2; Изм.0; 1л; поз(1.1.9) 4л; поз(2.1.9) 6л; поз(3.1.9) 8л; поз(4.1.7) 10л; (5.1.7) 11л; поз(6.1.11) 14л; поз(7.1.9) 18л; поз(8.1.9) 21л; поз(9.1.9) 24л; поз(10.1.7) 27л; поз(11.1.9) 29л; поз(12.1.9) 32л; поз(13.1.9) 34л; поз(14.1.9) 37л; поз(15.1.7) 38л; поз(16.1.9) 41л; поз(17.1.9) 45л; поз(18.1.9) 48л; поз(19.1.9) 51л; поз(20.1.9); 
+12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(2.1; 2.5; 2.6) 2л; поз(2.10; 2.11; 2.12; 3.4; 3.5; 4.1; 4.2) 3л; поз(4.4; 4.6; 5.1;5,2; 5,3;5,4; 5.6); 
+12002-81-020601-АУПТ. СО4; Изм.0; л.1; (поз 1.3; 2.5; 3.1;4,1;4,2); 
+12002-81-020601-СПА. СО; Изм.1; 1л; поз(2.1; 2.6; 2.7; 2.9; 2.10; 2.11) 2л; поз(2.14; 3.5; 3.6; 4.1; 4.8; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 6.7; 8.32); 
+12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.1;  2.7; 2.8; 2.9; 2.10) 2л; поз(3.6; 3.7; 3.8; 4.1; 4.2; 4.4; 4.7; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 4л; поз(6.7; 6.8; 6.9; 6.11; 6.12; 6.13)
+12002-81-020602-АУПТ.СО1 ; Изм.0; л. (поз 1.1.11) л.3 (поз 1.3.14)  л.4 (поз 1.5.8)  л.5 (поз 1.7.1.10) л.7 (поз1.8.1.8) л.8 (поз 1.9.10) л.8 (поз 1.9.10) л.11 (поз 1.11.10) л.13 (поз 1.13.8) л.14 (поз1.15.8) л.15 (поз 1.17.10) л.17 (поз 1.19.8) л.18 (поз 1.21.8); 
+12002-81-020602-СПА.СО; Изм.1; 1л; поз(1.2.1; 1.2.6; 1.2.7; 1.2.9; 1.2.10; 1.2.11; ) 2л; поз(1.2.12; 1.3.5; 1.3.6; 1.4.1) 3л; поз( 1.4.12; 1.5.2) 4л; поз(1.6.1; 1.6.2; 1.6.3; 1.6.4; 1.6.5; 1.6.6; 1.6.7; 1.6.8; 1.6.9); 
+12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.2.1; 1.2.5; 1.2.7; 1.2.8; 1.2.10) 2л; поз(1.3.5; 1.3.6; 1.4.1; 1.4.2. 1.5.1; 1.5.2; 1.5.3; 1.5.4; 1.5.5; 1.6.1; 1.6.2;) л.3 (поз 1.6.3; 1.6.4; 1.6.6; 1.6.7; 1.6.9; 1.7.1; 1.7.2; 1.7.3; 1.7.4; 1.7.5; 1.7.6; 1.7.7)</v>
       </c>
       <c r="M81" s="83"/>
       <c r="N81" s="84">
-        <f t="shared" si="2"/>
-        <v>1007</v>
+        <f>V81</f>
+        <v>3742</v>
       </c>
       <c r="O81" s="83">
-        <v>19181.02</v>
+        <v>5534.75</v>
       </c>
       <c r="P81" s="83">
         <f>N81*AE81</f>
-        <v>23916189.58</v>
+        <v>23635444.92</v>
       </c>
       <c r="Q81" s="83">
-        <f t="shared" si="3"/>
-        <v>1007</v>
+        <f>N81-G81</f>
+        <v>3742</v>
       </c>
       <c r="R81" s="84">
         <f>ROUND(P81-I81,0)</f>
-        <v>23916190</v>
-      </c>
-      <c r="S81" s="119" t="str">
+        <v>23635445</v>
+      </c>
+      <c r="S81" s="67" t="str">
         <f>TEXTJOIN("
-",FALSE(),S82:S91)</f>
-        <v>12002-81-0220-СПА.СО; л.1; поз (1.1.1; 1.1.2; 1.1.3; 1.1.4; 1.3-блок обработки на 2 шлейфа МИП-2)
-12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(1.1; 1.2) 2л; поз(3.1; 3.2; 3.3; 3.5;4.6)
-12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(1.1; 2.8) 2л; поз(3.1,3.2; 3.3; 3.6; 3.7)
-12002-81-020601-АУПТ. СО4; Изм.0, л.1 (поз 2.2; 2.4)
-12002-81-020601-СПА. СО; Изм.1; 1л; поз(1.1; 1.2; 1.3; 1.4; 1.5) 2л; поз(3.1; 3.2; 3.3; 3.4; 3.7; 4.2) 4л; поз(7.9)
-12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(1.1; 3.1 ) 2л; поз( 3.2; 3.3; 3.4; 3.9; 4.8) 4л; поз(9.6;)
-12002-81-020602-СПА.СО.Изм.1; 1л; поз(1.1.1) 2л; поз(1.3.1; 1.3.2; 1.3.3; 1.3.4; 1.3.7; 1.4.2; 1.4.3; 4; л5 поз (1.7.6)
-12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.1.1; 1.3.1; 1.3.2; 1.3.3;) 2л; поз(1.3.4; 1.3.7; 1.3.8)
-12002-81-020601-АУПТ1.1 СО1; Изм.0; 1л; поз(2.2; 2.3; 2.5) 
-12002-81-020601-АУПТ1.1 СО3 ; Изм.0; 1л; поз(2.1; 2.2; 2.4; 2.6) 
-12002-81-020601-СПА1.1. Изм.0; Изм.0  л1 поз(1; 3)</v>
+",FALSE(),S82:S94)</f>
+        <v>12002-81-0220-СПА.СО Изм2_, л.1  (поз1.1.5; 1.2; 1.4;1.5;1.6)
+12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(2.1; 2.4; 2.5; 2.6; 2.7; 2.8) 2л; поз(3.4; 3.6; 4.1; 4.2; 4.4;) 3л; поз(5.1;5.2,5,3;5,4;5,5;5,6)
+12002-81-020601-АУПТ. СО2; Изм.0; 1л; поз(1.1.9) 4л; поз(2.1.9) 6л; поз(3.1.9) 8л; поз(4.1.7) 10л; (5.1.7) 11л; поз(6.1.11) 14л; поз(7.1.9) 18л; поз(8.1.9) 21л; поз(9.1.9) 24л; поз(10.1.7) 27л; поз(11.1.9) 29л; поз(12.1.9) 32л; поз(13.1.9) 34л; поз(14.1.9) 37л; поз(15.1.7) 38л; поз(16.1.9) 41л; поз(17.1.9) 45л; поз(18.1.9) 48л; поз(19.1.9) 51л; поз(20.1.9)
+12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(2.1; 2.5; 2.6) 2л; поз(2.10; 2.11; 2.12; 3.4; 3.5; 4.1; 4.2) 3л; поз(4.4; 4.6; 5.1;5,2; 5,3;5,4; 5.6)
+12002-81-020601-АУПТ. СО4; Изм.0; л.1; (поз 1.3; 2.5; 3.1;4,1;4,2)
+12002-81-020601-СПА. СО; Изм.1; 1л; поз(2.1; 2.6; 2.7; 2.9; 2.10; 2.11) 2л; поз(2.14; 3.5; 3.6; 4.1; 4.8; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 6.7; 8.32)
+12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.1;  2.7; 2.8; 2.9; 2.10) 2л; поз(3.6; 3.7; 3.8; 4.1; 4.2; 4.4; 4.7; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 4л; поз(6.7; 6.8; 6.9; 6.11; 6.12; 6.13)
+12002-81-020602-АУПТ.СО1 ; Изм.0; л. (поз 1.1.11) л.3 (поз 1.3.14)  л.4 (поз 1.5.8)  л.5 (поз 1.7.1.10) л.7 (поз1.8.1.8) л.8 (поз 1.9.10) л.8 (поз 1.9.10) л.11 (поз 1.11.10) л.13 (поз 1.13.8) л.14 (поз1.15.8) л.15 (поз 1.17.10) л.17 (поз 1.19.8) л.18 (поз 1.21.8)
+12002-81-020602-СПА.СО; Изм.1; 1л; поз(1.2.1; 1.2.6; 1.2.7; 1.2.9; 1.2.10; 1.2.11; ) 2л; поз(1.2.12; 1.3.5; 1.3.6; 1.4.1) 3л; поз( 1.4.12; 1.5.2) 4л; поз(1.6.1; 1.6.2; 1.6.3; 1.6.4; 1.6.5; 1.6.6; 1.6.7; 1.6.8; 1.6.9)
+12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.2.1; 1.2.5; 1.2.7; 1.2.8; 1.2.10) 2л; поз(1.3.5; 1.3.6; 1.4.1; 1.4.2. 1.5.1; 1.5.2; 1.5.3; 1.5.4; 1.5.5; 1.6.1; 1.6.2;) л.3 (поз 1.6.3; 1.6.4; 1.6.6; 1.6.7; 1.6.9; 1.7.1; 1.7.2; 1.7.3; 1.7.4; 1.7.5; 1.7.6; 1.7.7)
+12002-81-020601-АУПТ1.1 СО1 ; Изм.0; 1л; поз(1.1;1.3;1.4;1.5;1.6;1.7; 2.4) 2л; поз(3.1;3.2; 3.4; 4.1;4.2;4.3;4.4;4.5;4.6)
+ 12002-81-020601-АУПТ1.1 СО3 ; Изм.0; 1л; поз(1.2;1.3;1.5;1.6;2.1;2.3;2.5) 2л по(3.1;3.2;3.4;4.1;4.2;4.3;4.4)
+12002-81-020601-АУПТ1.1 СО2 ; Изм.0; 1л; поз(1.9)
+12002-81-020601-СПА1.1 СО; Изм.0; 1л; (поз2;4;) 2л; (поз30)
+12002-81-020603-АУПТ 1л; поз(1.1.17) л.4(поз 2.1.41)</v>
       </c>
       <c r="T81" s="117"/>
       <c r="U81" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="V81" s="120">
-        <f>SUM(V82:V91)</f>
-        <v>1007</v>
+      <c r="V81" s="67">
+        <f>SUM(V82:V94)</f>
+        <v>3742</v>
       </c>
       <c r="W81" s="103">
         <f>Z81+AC81+AF81+AI81</f>
-        <v>25018427.08</v>
+        <v>24922992.82</v>
       </c>
       <c r="X81" s="97">
         <v>0.0</v>
       </c>
       <c r="Y81" s="99">
-        <v>19181.02</v>
+        <v>5534.75</v>
       </c>
       <c r="Z81" s="103">
         <f>ROUND(X81*Y81,2)</f>
@@ -10288,39 +10293,43 @@
         <v>0.0</v>
       </c>
       <c r="AB81" s="99">
-        <f>ROUND(Y81*$AM$7,2)</f>
-        <v>20811.64</v>
+        <f>ROUND(Y81*$AM$6,2)</f>
+        <v>5534.75</v>
       </c>
       <c r="AC81" s="103">
         <f>ROUND(AB81*AA81,2)</f>
         <v>0</v>
       </c>
       <c r="AD81" s="111">
-        <f>SUM(AD82:AD91)</f>
-        <v>357</v>
-      </c>
-      <c r="AE81" s="121">
-        <f>ROUND(Y81*$AP$7,2)</f>
-        <v>23749.94</v>
+        <f>SUM(AD82:AD94)</f>
+        <v>887</v>
+      </c>
+      <c r="AE81" s="122">
+        <f>ROUND(Y81*$AP$6,2)</f>
+        <v>6316.26</v>
       </c>
       <c r="AF81" s="103">
         <f>ROUND(AE81*AD81,2)</f>
-        <v>8478728.58</v>
+        <v>5602522.62</v>
       </c>
       <c r="AG81" s="111">
-        <f>SUM(AG82:AG91)</f>
-        <v>650</v>
-      </c>
-      <c r="AH81" s="121">
+        <f>SUM(AG82:AG94)</f>
+        <v>2855</v>
+      </c>
+      <c r="AH81" s="122">
         <f>ROUND(AE81*$AS$7,2)</f>
-        <v>25445.69</v>
+        <v>6767.24</v>
       </c>
       <c r="AI81" s="103">
         <f>ROUND(AH81*AG81,2)</f>
-        <v>16539698.5</v>
-      </c>
-      <c r="AJ81" s="76"/>
-      <c r="AK81" s="55"/>
+        <v>19320470.2</v>
+      </c>
+      <c r="AJ81" s="123" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK81" s="55" t="s">
+        <v>162</v>
+      </c>
       <c r="AL81" s="13"/>
       <c r="AM81" s="13"/>
       <c r="AN81" s="13"/>
@@ -10343,7 +10352,7 @@
       <c r="BE81" s="13"/>
       <c r="BF81" s="13"/>
     </row>
-    <row r="82" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="82" ht="129.75" customHeight="1" outlineLevel="1">
       <c r="A82" s="13"/>
       <c r="B82" s="77"/>
       <c r="C82" s="78"/>
@@ -10360,29 +10369,29 @@
       <c r="J82" s="84"/>
       <c r="K82" s="84"/>
       <c r="L82" s="83" t="str">
-        <f t="shared" ref="L82:L91" si="25">S82</f>
-        <v>12002-81-0220-СПА.СО; л.1; поз (1.1.1; 1.1.2; 1.1.3; 1.1.4; 1.3-блок обработки на 2 шлейфа МИП-2)</v>
+        <f>S82</f>
+        <v>12002-81-0220-СПА.СО Изм2_, л.1  (поз1.1.5; 1.2; 1.4;1.5;1.6)</v>
       </c>
       <c r="M82" s="83"/>
       <c r="N82" s="84">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>V82</f>
+        <v>9</v>
       </c>
       <c r="O82" s="83"/>
       <c r="P82" s="83"/>
       <c r="Q82" s="83">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f>N82-G82</f>
+        <v>9</v>
       </c>
       <c r="R82" s="84"/>
-      <c r="S82" s="112" t="s">
-        <v>148</v>
+      <c r="S82" s="67" t="s">
+        <v>163</v>
       </c>
       <c r="T82" s="113"/>
       <c r="U82" s="87"/>
-      <c r="V82" s="106">
-        <f t="shared" ref="V82:V85" si="26">SUM(X82+AA82+AD82+AG82)</f>
-        <v>5</v>
+      <c r="V82" s="67">
+        <f>SUM(X82+AA82+AD82+AG82)</f>
+        <v>9</v>
       </c>
       <c r="W82" s="93"/>
       <c r="X82" s="82"/>
@@ -10392,8 +10401,8 @@
       <c r="AB82" s="84"/>
       <c r="AC82" s="93"/>
       <c r="AD82" s="110">
-        <f>1+1+1+1+1</f>
-        <v>5</v>
+        <f>1+2+3+2+1</f>
+        <v>9</v>
       </c>
       <c r="AE82" s="84"/>
       <c r="AF82" s="93"/>
@@ -10402,8 +10411,12 @@
       </c>
       <c r="AH82" s="84"/>
       <c r="AI82" s="93"/>
-      <c r="AJ82" s="76"/>
-      <c r="AK82" s="55"/>
+      <c r="AJ82" s="124" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK82" s="55" t="s">
+        <v>165</v>
+      </c>
       <c r="AL82" s="13"/>
       <c r="AM82" s="13"/>
       <c r="AN82" s="13"/>
@@ -10426,7 +10439,7 @@
       <c r="BE82" s="13"/>
       <c r="BF82" s="13"/>
     </row>
-    <row r="83" ht="31.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="83" ht="88.5" customHeight="1" outlineLevel="1">
       <c r="A83" s="13"/>
       <c r="B83" s="77"/>
       <c r="C83" s="78"/>
@@ -10441,29 +10454,33 @@
       <c r="J83" s="84"/>
       <c r="K83" s="84"/>
       <c r="L83" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(1.1; 1.2) 2л; поз(3.1; 3.2; 3.3; 3.5;4.6)</v>
+        <f>S83</f>
+        <v>12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(2.1; 2.4; 2.5; 2.6; 2.7; 2.8) 2л; поз(3.4; 3.6; 4.1; 4.2; 4.4;) 3л; поз(5.1;5.2,5,3;5,4;5,5;5,6)</v>
       </c>
       <c r="M83" s="83"/>
       <c r="N83" s="84">
-        <f t="shared" si="2"/>
-        <v>70</v>
+        <f>V83</f>
+        <v>842</v>
       </c>
       <c r="O83" s="83"/>
       <c r="P83" s="83"/>
       <c r="Q83" s="83">
-        <f t="shared" si="3"/>
-        <v>70</v>
+        <f>N83-G83</f>
+        <v>842</v>
       </c>
       <c r="R83" s="84"/>
-      <c r="S83" s="112" t="s">
-        <v>149</v>
-      </c>
-      <c r="T83" s="113"/>
-      <c r="U83" s="87"/>
-      <c r="V83" s="106">
-        <f t="shared" si="26"/>
-        <v>70</v>
+      <c r="S83" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="T83" s="113" t="s">
+        <v>167</v>
+      </c>
+      <c r="U83" s="87" t="s">
+        <v>124</v>
+      </c>
+      <c r="V83" s="67">
+        <f>SUM(X83+AA83+AD83+AG83)</f>
+        <v>842</v>
       </c>
       <c r="W83" s="93"/>
       <c r="X83" s="82"/>
@@ -10478,13 +10495,17 @@
       <c r="AE83" s="84"/>
       <c r="AF83" s="93"/>
       <c r="AG83" s="110">
-        <f>2+18+1+13+2+26+8</f>
-        <v>70</v>
+        <f>(484+5+22+6+6+1)+(9+32+26+46+48)+(34+8+41+33+33+8)</f>
+        <v>842</v>
       </c>
       <c r="AH83" s="84"/>
       <c r="AI83" s="93"/>
-      <c r="AJ83" s="76"/>
-      <c r="AK83" s="55"/>
+      <c r="AJ83" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK83" s="55" t="s">
+        <v>169</v>
+      </c>
       <c r="AL83" s="13"/>
       <c r="AM83" s="13"/>
       <c r="AN83" s="13"/>
@@ -10507,7 +10528,7 @@
       <c r="BE83" s="13"/>
       <c r="BF83" s="13"/>
     </row>
-    <row r="84" ht="31.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="84" ht="157.5" customHeight="1" outlineLevel="1">
       <c r="A84" s="13"/>
       <c r="B84" s="77"/>
       <c r="C84" s="78"/>
@@ -10522,29 +10543,33 @@
       <c r="J84" s="84"/>
       <c r="K84" s="84"/>
       <c r="L84" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(1.1; 2.8) 2л; поз(3.1,3.2; 3.3; 3.6; 3.7)</v>
+        <f>S84</f>
+        <v>12002-81-020601-АУПТ. СО2; Изм.0; 1л; поз(1.1.9) 4л; поз(2.1.9) 6л; поз(3.1.9) 8л; поз(4.1.7) 10л; (5.1.7) 11л; поз(6.1.11) 14л; поз(7.1.9) 18л; поз(8.1.9) 21л; поз(9.1.9) 24л; поз(10.1.7) 27л; поз(11.1.9) 29л; поз(12.1.9) 32л; поз(13.1.9) 34л; поз(14.1.9) 37л; поз(15.1.7) 38л; поз(16.1.9) 41л; поз(17.1.9) 45л; поз(18.1.9) 48л; поз(19.1.9) 51л; поз(20.1.9)</v>
       </c>
       <c r="M84" s="83"/>
       <c r="N84" s="84">
-        <f t="shared" si="2"/>
-        <v>117</v>
+        <f>V84</f>
+        <v>21</v>
       </c>
       <c r="O84" s="83"/>
       <c r="P84" s="83"/>
       <c r="Q84" s="83">
-        <f t="shared" si="3"/>
-        <v>117</v>
+        <f>N84-G84</f>
+        <v>21</v>
       </c>
       <c r="R84" s="84"/>
-      <c r="S84" s="112" t="s">
-        <v>150</v>
-      </c>
-      <c r="T84" s="113"/>
-      <c r="U84" s="87"/>
-      <c r="V84" s="106">
-        <f t="shared" si="26"/>
-        <v>117</v>
+      <c r="S84" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="T84" s="113" t="s">
+        <v>171</v>
+      </c>
+      <c r="U84" s="87" t="s">
+        <v>172</v>
+      </c>
+      <c r="V84" s="67">
+        <f>SUM(X84+AA84+AD84+AG84)</f>
+        <v>21</v>
       </c>
       <c r="W84" s="93"/>
       <c r="X84" s="82"/>
@@ -10559,13 +10584,17 @@
       <c r="AE84" s="84"/>
       <c r="AF84" s="93"/>
       <c r="AG84" s="110">
-        <f>(2+2)+6+2+59+39+7</f>
-        <v>117</v>
+        <f>1+1+1+1+1+2+1+1+1+1+1+1+1+1+1+1+1+1+1+1</f>
+        <v>21</v>
       </c>
       <c r="AH84" s="84"/>
       <c r="AI84" s="93"/>
-      <c r="AJ84" s="76"/>
-      <c r="AK84" s="55"/>
+      <c r="AJ84" s="76" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK84" s="55" t="s">
+        <v>174</v>
+      </c>
       <c r="AL84" s="13"/>
       <c r="AM84" s="13"/>
       <c r="AN84" s="13"/>
@@ -10588,7 +10617,7 @@
       <c r="BE84" s="13"/>
       <c r="BF84" s="13"/>
     </row>
-    <row r="85" ht="31.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="85" ht="88.5" customHeight="1" outlineLevel="1">
       <c r="A85" s="13"/>
       <c r="B85" s="77"/>
       <c r="C85" s="78"/>
@@ -10603,29 +10632,29 @@
       <c r="J85" s="84"/>
       <c r="K85" s="84"/>
       <c r="L85" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020601-АУПТ. СО4; Изм.0, л.1 (поз 2.2; 2.4)</v>
+        <f>S85</f>
+        <v>12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(2.1; 2.5; 2.6) 2л; поз(2.10; 2.11; 2.12; 3.4; 3.5; 4.1; 4.2) 3л; поз(4.4; 4.6; 5.1;5,2; 5,3;5,4; 5.6)</v>
       </c>
       <c r="M85" s="83"/>
       <c r="N85" s="84">
-        <f t="shared" si="2"/>
-        <v>14</v>
+        <f>V85</f>
+        <v>388</v>
       </c>
       <c r="O85" s="83"/>
       <c r="P85" s="83"/>
       <c r="Q85" s="83">
-        <f t="shared" si="3"/>
-        <v>14</v>
+        <f>N85-G85</f>
+        <v>388</v>
       </c>
       <c r="R85" s="84"/>
-      <c r="S85" s="112" t="s">
-        <v>151</v>
+      <c r="S85" s="67" t="s">
+        <v>175</v>
       </c>
       <c r="T85" s="113"/>
       <c r="U85" s="87"/>
-      <c r="V85" s="106">
-        <f t="shared" si="26"/>
-        <v>14</v>
+      <c r="V85" s="67">
+        <f>SUM(X85+AA85+AD85+AG85)</f>
+        <v>388</v>
       </c>
       <c r="W85" s="93"/>
       <c r="X85" s="82"/>
@@ -10640,13 +10669,17 @@
       <c r="AE85" s="84"/>
       <c r="AF85" s="93"/>
       <c r="AG85" s="110">
-        <f>6+8</f>
-        <v>14</v>
+        <f>(4+20+4)+(8+16+60+27+5+30+20)+(6+5+12+11+68+68+24)</f>
+        <v>388</v>
       </c>
       <c r="AH85" s="84"/>
       <c r="AI85" s="93"/>
-      <c r="AJ85" s="76"/>
-      <c r="AK85" s="55"/>
+      <c r="AJ85" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK85" s="55" t="s">
+        <v>169</v>
+      </c>
       <c r="AL85" s="13"/>
       <c r="AM85" s="13"/>
       <c r="AN85" s="13"/>
@@ -10669,7 +10702,7 @@
       <c r="BE85" s="13"/>
       <c r="BF85" s="13"/>
     </row>
-    <row r="86" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="86" ht="88.5" customHeight="1" outlineLevel="1">
       <c r="A86" s="13"/>
       <c r="B86" s="77"/>
       <c r="C86" s="78"/>
@@ -10684,29 +10717,31 @@
       <c r="J86" s="84"/>
       <c r="K86" s="84"/>
       <c r="L86" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020601-СПА. СО; Изм.1; 1л; поз(1.1; 1.2; 1.3; 1.4; 1.5) 2л; поз(3.1; 3.2; 3.3; 3.4; 3.7; 4.2) 4л; поз(7.9)</v>
+        <f>S86</f>
+        <v>12002-81-020601-АУПТ. СО4; Изм.0; л.1; (поз 1.3; 2.5; 3.1;4,1;4,2)</v>
       </c>
       <c r="M86" s="83"/>
       <c r="N86" s="84">
-        <f t="shared" si="2"/>
-        <v>300</v>
+        <f>V86</f>
+        <v>62</v>
       </c>
       <c r="O86" s="83"/>
       <c r="P86" s="83"/>
       <c r="Q86" s="83">
-        <f t="shared" si="3"/>
-        <v>300</v>
+        <f>N86-G86</f>
+        <v>62</v>
       </c>
       <c r="R86" s="84"/>
-      <c r="S86" s="112" t="s">
-        <v>152</v>
+      <c r="S86" s="67" t="s">
+        <v>177</v>
       </c>
       <c r="T86" s="113"/>
-      <c r="U86" s="87"/>
-      <c r="V86" s="106">
+      <c r="U86" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="V86" s="67">
         <f>SUM(X86+AA86+AD86+AG86)</f>
-        <v>300</v>
+        <v>62</v>
       </c>
       <c r="W86" s="93"/>
       <c r="X86" s="82"/>
@@ -10716,18 +10751,22 @@
       <c r="AB86" s="84"/>
       <c r="AC86" s="93"/>
       <c r="AD86" s="110">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE86" s="84"/>
       <c r="AF86" s="93"/>
       <c r="AG86" s="110">
-        <f>((5+4+1+1+1)+(13+9+27+46+181+3)+(9))-AD86</f>
-        <v>200</v>
+        <f>16+4+4+14+24</f>
+        <v>62</v>
       </c>
       <c r="AH86" s="84"/>
       <c r="AI86" s="93"/>
-      <c r="AJ86" s="76"/>
-      <c r="AK86" s="55"/>
+      <c r="AJ86" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="AK86" s="55" t="s">
+        <v>169</v>
+      </c>
       <c r="AL86" s="13"/>
       <c r="AM86" s="13"/>
       <c r="AN86" s="13"/>
@@ -10750,7 +10789,7 @@
       <c r="BE86" s="13"/>
       <c r="BF86" s="13"/>
     </row>
-    <row r="87" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="87" ht="171.0" customHeight="1" outlineLevel="1">
       <c r="A87" s="13"/>
       <c r="B87" s="77"/>
       <c r="C87" s="78"/>
@@ -10765,29 +10804,31 @@
       <c r="J87" s="84"/>
       <c r="K87" s="84"/>
       <c r="L87" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(1.1; 3.1 ) 2л; поз( 3.2; 3.3; 3.4; 3.9; 4.8) 4л; поз(9.6;)</v>
+        <f>S87</f>
+        <v>12002-81-020601-СПА. СО; Изм.1; 1л; поз(2.1; 2.6; 2.7; 2.9; 2.10; 2.11) 2л; поз(2.14; 3.5; 3.6; 4.1; 4.8; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 6.7; 8.32)</v>
       </c>
       <c r="M87" s="83"/>
       <c r="N87" s="84">
-        <f t="shared" si="2"/>
-        <v>70</v>
+        <f>V87</f>
+        <v>747</v>
       </c>
       <c r="O87" s="83"/>
       <c r="P87" s="83"/>
       <c r="Q87" s="83">
-        <f t="shared" si="3"/>
-        <v>70</v>
+        <f>N87-G87</f>
+        <v>747</v>
       </c>
       <c r="R87" s="84"/>
-      <c r="S87" s="112" t="s">
-        <v>153</v>
-      </c>
-      <c r="T87" s="113"/>
+      <c r="S87" s="67" t="s">
+        <v>180</v>
+      </c>
+      <c r="T87" s="125" t="s">
+        <v>181</v>
+      </c>
       <c r="U87" s="87"/>
-      <c r="V87" s="106">
+      <c r="V87" s="67">
         <f>SUM(X87+AA87+AD87+AG87)</f>
-        <v>70</v>
+        <v>747</v>
       </c>
       <c r="W87" s="93"/>
       <c r="X87" s="82"/>
@@ -10797,18 +10838,25 @@
       <c r="AB87" s="84"/>
       <c r="AC87" s="93"/>
       <c r="AD87" s="110">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE87" s="84"/>
       <c r="AF87" s="93"/>
       <c r="AG87" s="110">
-        <f>(3+7+7+19+6+24+1+3)-AD87</f>
-        <v>35</v>
+        <f>(137+16+53+4+4+57)+(1+38+54+97+28)+(12+22+37+7+8+9+13)+(99)+(51)</f>
+        <v>747</v>
       </c>
       <c r="AH87" s="84"/>
       <c r="AI87" s="93"/>
-      <c r="AJ87" s="76"/>
-      <c r="AK87" s="55"/>
+      <c r="AJ87" s="76" t="s">
+        <v>182</v>
+      </c>
+      <c r="AK87" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По меткам: По паспорту изготовителя АМ-4-R3 — адресный модуль (в техописании «Рубежа»: «габаритные размеры модуля АМ-4 прот.R3»), а модули прямо входят в наименование БЕР №7. Критерия «конечный исполнительный элемент» в БЕР №7 нет: датчики и извещатели из того же перечня тоже не исполнительные элементы. Работы по метке — монтаж, расключение АЛС и шлейфов, прозвонка — соответствуют составу БЕР №7. Позицию оставляем.
+По фильтру: Аспирационный извещатель вынесен в отдельную расценку только из-за стоимости: в БЕР №7 входит приобретение оборудования, а «Оптисенс» в десятки раз дороже остальных устройств позиции. Фильтр Ф-10 по цене сопоставим с обычными извещателями, поэтому учтён в БЕР №7. В расценку БЕР №17 фильтр не входит, двойного учёта нет; если исключить п. 5.2, монтаж фильтров не будет учтён нигде. Позицию оставляем.</t>
+        </is>
+      </c>
       <c r="AL87" s="13"/>
       <c r="AM87" s="13"/>
       <c r="AN87" s="13"/>
@@ -10831,7 +10879,7 @@
       <c r="BE87" s="13"/>
       <c r="BF87" s="13"/>
     </row>
-    <row r="88" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="88" ht="253.5" customHeight="1" outlineLevel="1">
       <c r="A88" s="13"/>
       <c r="B88" s="77"/>
       <c r="C88" s="78"/>
@@ -10846,29 +10894,37 @@
       <c r="J88" s="84"/>
       <c r="K88" s="84"/>
       <c r="L88" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020602-СПА.СО.Изм.1; 1л; поз(1.1.1) 2л; поз(1.3.1; 1.3.2; 1.3.3; 1.3.4; 1.3.7; 1.4.2; 1.4.3; 4; л5 поз (1.7.6)</v>
+        <f>S88</f>
+        <v>12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.1;  2.7; 2.8; 2.9; 2.10) 2л; поз(3.6; 3.7; 3.8; 4.1; 4.2; 4.4; 4.7; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 4л; поз(6.7; 6.8; 6.9; 6.11; 6.12; 6.13)
+12002-81-020602-АУПТ.СО1 ; Изм.0; л. (поз 1.1.11) л.3 (поз 1.3.14)  л.4 (поз 1.5.8)  л.5 (поз 1.7.1.10) л.7 (поз1.8.1.8) л.8 (поз 1.9.10) л.8 (поз 1.9.10) л.11 (поз 1.11.10) л.13 (поз 1.13.8) л.14 (поз1.15.8) л.15 (поз 1.17.10) л.17 (поз 1.19.8) л.18 (поз 1.21.8)</v>
       </c>
       <c r="M88" s="83"/>
       <c r="N88" s="84">
-        <f t="shared" si="2"/>
-        <v>346</v>
+        <f>V88</f>
+        <v>453</v>
       </c>
       <c r="O88" s="83"/>
       <c r="P88" s="83"/>
       <c r="Q88" s="83">
-        <f t="shared" si="3"/>
-        <v>346</v>
+        <f>N88-G88</f>
+        <v>453</v>
       </c>
       <c r="R88" s="84"/>
-      <c r="S88" s="112" t="s">
-        <v>154</v>
-      </c>
-      <c r="T88" s="113"/>
-      <c r="U88" s="87"/>
-      <c r="V88" s="106">
+      <c r="S88" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.1;  2.7; 2.8; 2.9; 2.10) 2л; поз(3.6; 3.7; 3.8; 4.1; 4.2; 4.4; 4.7; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6) 4л; поз(6.7; 6.8; 6.9; 6.11; 6.12; 6.13)
+12002-81-020602-АУПТ.СО2 ; Изм.0; л. (поз 1.1.11) л.3 (поз 1.3.14)  л.4 (поз 1.5.8)  л.5 (поз 1.7.1.10) л.7 (поз1.8.1.8) л.8 (поз 1.9.10) л.11 (поз 1.11.10) л.13 (поз 1.13.8) л.14 (поз1.15.8) л.15 (поз 1.17.10) л.17 (поз 1.19.8) л.18 (поз 1.21.8)</t>
+        </is>
+      </c>
+      <c r="T88" s="125" t="s">
+        <v>185</v>
+      </c>
+      <c r="U88" s="87" t="s">
+        <v>186</v>
+      </c>
+      <c r="V88" s="67">
         <f>SUM(X88+AA88+AD88+AG88)</f>
-        <v>346</v>
+        <v>453</v>
       </c>
       <c r="W88" s="93"/>
       <c r="X88" s="82"/>
@@ -10878,18 +10934,26 @@
       <c r="AB88" s="84"/>
       <c r="AC88" s="93"/>
       <c r="AD88" s="110">
-        <v>146.0</v>
+        <v>226.0</v>
       </c>
       <c r="AE88" s="84"/>
       <c r="AF88" s="93"/>
       <c r="AG88" s="110">
-        <f>((6)+(7+23+38+79+169+12+1)+(11))-AD88</f>
-        <v>200</v>
+        <f>((78+6+22+5+3)+(33+18+3+33+34+12+8+6)+(21+4+15+12+40+2)+(55+25+3+1+1+1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1))-AD88</f>
+        <v>227</v>
       </c>
       <c r="AH88" s="84"/>
       <c r="AI88" s="93"/>
-      <c r="AJ88" s="76"/>
-      <c r="AK88" s="55"/>
+      <c r="AJ88" s="76" t="s">
+        <v>187</v>
+      </c>
+      <c r="AK88" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По меткам: По паспорту изготовителя АМ-4-R3 — адресный модуль (в техописании «Рубежа»: «габаритные размеры модуля АМ-4 прот.R3»), а модули прямо входят в наименование БЕР №7. Критерия «конечный исполнительный элемент» в БЕР №7 нет: датчики и извещатели из того же перечня тоже не исполнительные элементы. Работы по метке — монтаж, расключение АЛС и шлейфов, прозвонка — соответствуют составу БЕР №7. Позицию оставляем.
+По сигнализаторам: СДУ-М по паспорту — сигнальное устройство: при изменении давления замыкает/размыкает контакт, то есть по принципу работы это датчик, а датчики прямо указаны в БЕР №7. «Оконечное» в наименовании позиции — устройство на конце линии, а не элемент, завершающий шлейф: громкоговорители, световые указатели и извещатели из того же перечня линию тоже не завершают. Монтаж на трубопроводе, расключение и прозвонка соответствуют составу БЕР №7. Позицию оставляем.
+По фильтру: Аспирационный извещатель вынесен в отдельную расценку только из-за стоимости: в БЕР №7 входит приобретение оборудования, а «Оптисенс» в десятки раз дороже остальных устройств позиции. Фильтр Ф-10 по цене сопоставим с обычными извещателями, поэтому учтён в БЕР №7. В расценку БЕР №17 фильтр не входит, двойного учёта нет; если исключить п. 5.2, монтаж фильтров не будет учтён нигде. Позицию оставляем.</t>
+        </is>
+      </c>
       <c r="AL88" s="13"/>
       <c r="AM88" s="13"/>
       <c r="AN88" s="13"/>
@@ -10912,7 +10976,7 @@
       <c r="BE88" s="13"/>
       <c r="BF88" s="13"/>
     </row>
-    <row r="89" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="89" ht="171.0" customHeight="1" outlineLevel="1">
       <c r="A89" s="13"/>
       <c r="B89" s="77"/>
       <c r="C89" s="78"/>
@@ -10927,29 +10991,33 @@
       <c r="J89" s="84"/>
       <c r="K89" s="84"/>
       <c r="L89" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.1.1; 1.3.1; 1.3.2; 1.3.3;) 2л; поз(1.3.4; 1.3.7; 1.3.8)</v>
+        <f>S89</f>
+        <v>12002-81-020602-СПА.СО; Изм.1; 1л; поз(1.2.1; 1.2.6; 1.2.7; 1.2.9; 1.2.10; 1.2.11; ) 2л; поз(1.2.12; 1.3.5; 1.3.6; 1.4.1) 3л; поз( 1.4.12; 1.5.2) 4л; поз(1.6.1; 1.6.2; 1.6.3; 1.6.4; 1.6.5; 1.6.6; 1.6.7; 1.6.8; 1.6.9)</v>
       </c>
       <c r="M89" s="83"/>
       <c r="N89" s="84">
-        <f t="shared" si="2"/>
-        <v>71</v>
+        <f>V89</f>
+        <v>905</v>
       </c>
       <c r="O89" s="83"/>
       <c r="P89" s="83"/>
       <c r="Q89" s="83">
-        <f t="shared" si="3"/>
-        <v>71</v>
+        <f>N89-G89</f>
+        <v>905</v>
       </c>
       <c r="R89" s="84"/>
-      <c r="S89" s="112" t="s">
-        <v>155</v>
-      </c>
-      <c r="T89" s="113"/>
-      <c r="U89" s="87"/>
-      <c r="V89" s="106">
-        <f t="shared" ref="V89:V91" si="27">SUM(X89+AA89+AD89+AG89)</f>
-        <v>71</v>
+      <c r="S89" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="T89" s="125" t="s">
+        <v>190</v>
+      </c>
+      <c r="U89" s="87" t="s">
+        <v>191</v>
+      </c>
+      <c r="V89" s="67">
+        <f>SUM(X89+AA89+AD89+AG89)</f>
+        <v>905</v>
       </c>
       <c r="W89" s="93"/>
       <c r="X89" s="82"/>
@@ -10959,18 +11027,25 @@
       <c r="AB89" s="84"/>
       <c r="AC89" s="93"/>
       <c r="AD89" s="110">
-        <f>1+3+6+1+20+38+2</f>
-        <v>71</v>
+        <v>455.0</v>
       </c>
       <c r="AE89" s="84"/>
       <c r="AF89" s="93"/>
       <c r="AG89" s="110">
-        <v>0.0</v>
+        <f>((152+12+33+4+1+7)+(55+46+87+76)+(105+20)+(76+25+76+16+16+19+7+1+71))-AD89</f>
+        <v>450</v>
       </c>
       <c r="AH89" s="84"/>
       <c r="AI89" s="93"/>
-      <c r="AJ89" s="76"/>
-      <c r="AK89" s="55"/>
+      <c r="AJ89" s="76" t="s">
+        <v>192</v>
+      </c>
+      <c r="AK89" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По меткам: По паспорту изготовителя АМ-4-R3 — адресный модуль (в техописании «Рубежа»: «габаритные размеры модуля АМ-4 прот.R3»), а модули прямо входят в наименование БЕР №7. Критерия «конечный исполнительный элемент» в БЕР №7 нет: датчики и извещатели из того же перечня тоже не исполнительные элементы. Работы по метке — монтаж, расключение АЛС и шлейфов, прозвонка — соответствуют составу БЕР №7. Позицию оставляем.
+По фильтру: Аспирационный извещатель вынесен в отдельную расценку только из-за стоимости: в БЕР №7 входит приобретение оборудования, а «Оптисенс» в десятки раз дороже остальных устройств позиции. Фильтр Ф-10 по цене сопоставим с обычными извещателями, поэтому учтён в БЕР №7. В расценку БЕР №17 фильтр не входит, двойного учёта нет; если исключить п. 1.5.2, монтаж фильтров не будет учтён нигде. Позицию оставляем.</t>
+        </is>
+      </c>
       <c r="AL89" s="13"/>
       <c r="AM89" s="13"/>
       <c r="AN89" s="13"/>
@@ -10993,7 +11068,7 @@
       <c r="BE89" s="13"/>
       <c r="BF89" s="13"/>
     </row>
-    <row r="90" ht="63.0" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="90" ht="94.5" customHeight="1" outlineLevel="1">
       <c r="A90" s="13"/>
       <c r="B90" s="77"/>
       <c r="C90" s="78"/>
@@ -11008,34 +11083,29 @@
       <c r="J90" s="84"/>
       <c r="K90" s="84"/>
       <c r="L90" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020601-АУПТ1.1 СО1; Изм.0; 1л; поз(2.2; 2.3; 2.5) 
-12002-81-020601-АУПТ1.1 СО3 ; Изм.0; 1л; поз(2.1; 2.2; 2.4; 2.6) </v>
+        <f>S90</f>
+        <v>12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.2.1; 1.2.5; 1.2.7; 1.2.8; 1.2.10) 2л; поз(1.3.5; 1.3.6; 1.4.1; 1.4.2. 1.5.1; 1.5.2; 1.5.3; 1.5.4; 1.5.5; 1.6.1; 1.6.2;) л.3 (поз 1.6.3; 1.6.4; 1.6.6; 1.6.7; 1.6.9; 1.7.1; 1.7.2; 1.7.3; 1.7.4; 1.7.5; 1.7.6; 1.7.7)</v>
       </c>
       <c r="M90" s="83"/>
       <c r="N90" s="84">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <f>V90</f>
+        <v>197</v>
       </c>
       <c r="O90" s="83"/>
       <c r="P90" s="83"/>
       <c r="Q90" s="83">
-        <f t="shared" si="3"/>
-        <v>10</v>
+        <f>N90-G90</f>
+        <v>197</v>
       </c>
       <c r="R90" s="84"/>
-      <c r="S90" s="112" t="s">
-        <v>156</v>
-      </c>
-      <c r="T90" s="113" t="s">
-        <v>157</v>
-      </c>
-      <c r="U90" s="87" t="s">
-        <v>124</v>
-      </c>
-      <c r="V90" s="106">
-        <f t="shared" si="27"/>
-        <v>10</v>
+      <c r="S90" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="T90" s="113"/>
+      <c r="U90" s="87"/>
+      <c r="V90" s="67">
+        <f>SUM(X90+AA90+AD90+AG90)</f>
+        <v>197</v>
       </c>
       <c r="W90" s="93"/>
       <c r="X90" s="82"/>
@@ -11045,18 +11115,22 @@
       <c r="AB90" s="84"/>
       <c r="AC90" s="93"/>
       <c r="AD90" s="110">
-        <v>0.0</v>
+        <f>(31+6+18+4+1)+(23+5+19+22+1+1+1+1+1+2+1)+(1+1+1+2+2+10+4+2+5+4+4+24)</f>
+        <v>197</v>
       </c>
       <c r="AE90" s="84"/>
       <c r="AF90" s="93"/>
       <c r="AG90" s="110">
-        <f>1+1+1+1+2+2+2</f>
-        <v>10</v>
+        <v>0.0</v>
       </c>
       <c r="AH90" s="84"/>
       <c r="AI90" s="93"/>
-      <c r="AJ90" s="76"/>
-      <c r="AK90" s="55"/>
+      <c r="AJ90" s="76" t="s">
+        <v>195</v>
+      </c>
+      <c r="AK90" s="55" t="s">
+        <v>169</v>
+      </c>
       <c r="AL90" s="13"/>
       <c r="AM90" s="13"/>
       <c r="AN90" s="13"/>
@@ -11079,7 +11153,7 @@
       <c r="BE90" s="13"/>
       <c r="BF90" s="13"/>
     </row>
-    <row r="91" ht="31.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="91" ht="105.0" customHeight="1" outlineLevel="1">
       <c r="A91" s="13"/>
       <c r="B91" s="77"/>
       <c r="C91" s="78"/>
@@ -11094,29 +11168,34 @@
       <c r="J91" s="84"/>
       <c r="K91" s="84"/>
       <c r="L91" s="83" t="str">
-        <f t="shared" si="25"/>
-        <v>12002-81-020601-СПА1.1. Изм.0; Изм.0  л1 поз(1; 3)</v>
+        <f>S91</f>
+        <v>12002-81-020601-АУПТ1.1 СО1 ; Изм.0; 1л; поз(1.1;1.3;1.4;1.5;1.6;1.7; 2.4) 2л; поз(3.1;3.2; 3.4; 4.1;4.2;4.3;4.4;4.5;4.6)
+ 12002-81-020601-АУПТ1.1 СО3 ; Изм.0; 1л; поз(1.2;1.3;1.5;1.6;2.1;2.3;2.5) 2л по(3.1;3.2;3.4;4.1;4.2;4.3;4.4)</v>
       </c>
       <c r="M91" s="83"/>
       <c r="N91" s="84">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>V91</f>
+        <v>106</v>
       </c>
       <c r="O91" s="83"/>
       <c r="P91" s="83"/>
       <c r="Q91" s="83">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f>N91-G91</f>
+        <v>106</v>
       </c>
       <c r="R91" s="84"/>
-      <c r="S91" s="112" t="s">
-        <v>158</v>
-      </c>
-      <c r="T91" s="113"/>
-      <c r="U91" s="87"/>
-      <c r="V91" s="106">
-        <f t="shared" si="27"/>
-        <v>4</v>
+      <c r="S91" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="T91" s="113" t="s">
+        <v>197</v>
+      </c>
+      <c r="U91" s="87" t="s">
+        <v>198</v>
+      </c>
+      <c r="V91" s="67">
+        <f>SUM(X91+AA91+AD91+AG91)</f>
+        <v>106</v>
       </c>
       <c r="W91" s="93"/>
       <c r="X91" s="82"/>
@@ -11131,13 +11210,17 @@
       <c r="AE91" s="84"/>
       <c r="AF91" s="93"/>
       <c r="AG91" s="110">
-        <f>2+2</f>
-        <v>4</v>
+        <f>(26+2+2+2+4+4+1)+(1+4+2+3+2+4+3+3+1)+(5+5+1+3+3+1)+(1+7+2+1+1+6+6)</f>
+        <v>106</v>
       </c>
       <c r="AH91" s="84"/>
       <c r="AI91" s="93"/>
-      <c r="AJ91" s="76"/>
-      <c r="AK91" s="55"/>
+      <c r="AJ91" s="76" t="s">
+        <v>199</v>
+      </c>
+      <c r="AK91" s="55" t="s">
+        <v>200</v>
+      </c>
       <c r="AL91" s="13"/>
       <c r="AM91" s="13"/>
       <c r="AN91" s="13"/>
@@ -11160,154 +11243,72 @@
       <c r="BE91" s="13"/>
       <c r="BF91" s="13"/>
     </row>
-    <row r="92" ht="372.75" customHeight="1" collapsed="1">
+    <row r="92" ht="88.5" customHeight="1" outlineLevel="1">
       <c r="A92" s="13"/>
       <c r="B92" s="77"/>
-      <c r="C92" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="D92" s="94">
-        <v>7.0</v>
-      </c>
-      <c r="E92" s="94" t="s">
-        <v>160</v>
-      </c>
-      <c r="F92" s="96" t="s">
-        <v>49</v>
-      </c>
+      <c r="C92" s="78"/>
+      <c r="D92" s="79"/>
+      <c r="E92" s="79"/>
+      <c r="F92" s="81"/>
       <c r="G92" s="82">
         <v>0.0</v>
       </c>
-      <c r="H92" s="83">
-        <v>5534.75</v>
-      </c>
-      <c r="I92" s="83">
-        <f>G92*H92</f>
-        <v>0</v>
-      </c>
-      <c r="J92" s="84">
-        <f>V92-G92</f>
-        <v>3742</v>
-      </c>
-      <c r="K92" s="84">
-        <f>ROUND(P92-I92,0)</f>
-        <v>23635445</v>
-      </c>
+      <c r="H92" s="83"/>
+      <c r="I92" s="83"/>
+      <c r="J92" s="84"/>
+      <c r="K92" s="84"/>
       <c r="L92" s="83" t="str">
-        <f>TEXTJOIN("; 
-",FALSE(),L93,L94,L95,L96,L97,L98,L99,L100,L101)</f>
-        <v>12002-81-0220-СПА.СО Изм2_, л.1  (поз1.1.5; 1.2; 1.4;1.5;1.6); 
-12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(2.1; 2.4; 2.5; 2.6; 2.7; 2.8) 2л; поз(3.4; 3.6; 4.1; 4.2; 4.4;) 3л; поз(5.1;5.2,5,3;5,4;5,5;5,6); 
-12002-81-020601-АУПТ. СО2; Изм.0; 1л; поз(1.1.9) 4л; поз(2.1.9) 6л; поз(3.1.9) 8л; поз(4.1.7) 10л; (5.1.7) 11л; поз(6.1.11) 14л; поз(7.1.9) 18л; поз(8.1.9) 21л; поз(9.1.9) 24л; поз(10.1.7) 27л; поз(11.1.9) 29л; поз(12.1.9) 32л; поз(13.1.9) 34л; поз(14.1.9) 37л; поз(15.1.7) 38л; поз(16.1.9) 41л; поз(17.1.9) 45л; поз(18.1.9) 48л; поз(19.1.9) 51л; поз(20.1.9); 
-12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(2.1; 2.5; 2.6) 2л; поз(2.10; 2.11; 2.12; 3.4; 3.5; 4.1; 4.2) 3л; поз(4.4; 4.6; 5.1;5,2; 5,3;5,4; 5.6); 
-12002-81-020601-АУПТ. СО4; Изм.0; л.1; (поз 1.3; 2.5; 3.1;4,1;4,2); 
-12002-81-020601-СПА. СО; Изм.1; 1л; поз(2.1; 2.6; 2.7; 2.9; 2.10; 2.11) 2л; поз(2.14; 3.5; 3.6; 4.1; 4.8; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 6.7; 8.32); 
-12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.1;  2.7; 2.8; 2.9; 2.10) 2л; поз(3.6; 3.7; 3.8; 4.1; 4.2; 4.4; 4.7; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 4л; поз(6.7; 6.8; 6.9; 6.11; 6.12; 6.13)
-12002-81-020602-АУПТ.СО1 ; Изм.0; л. (поз 1.1.11) л.3 (поз 1.3.14)  л.4 (поз 1.5.8)  л.5 (поз 1.7.1.10) л.7 (поз1.8.1.8) л.8 (поз 1.9.10) л.8 (поз 1.9.10) л.11 (поз 1.11.10) л.13 (поз 1.13.8) л.14 (поз1.15.8) л.15 (поз 1.17.10) л.17 (поз 1.19.8) л.18 (поз 1.21.8); 
-12002-81-020602-СПА.СО; Изм.1; 1л; поз(1.2.1; 1.2.6; 1.2.7; 1.2.9; 1.2.10; 1.2.11; ) 2л; поз(1.2.12; 1.3.5; 1.3.6; 1.4.1) 3л; поз( 1.4.12; 1.5.2) 4л; поз(1.6.1; 1.6.2; 1.6.3; 1.6.4; 1.6.5; 1.6.6; 1.6.7; 1.6.8; 1.6.9); 
-12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.2.1; 1.2.5; 1.2.7; 1.2.8; 1.2.10) 2л; поз(1.3.5; 1.3.6; 1.4.1; 1.4.2. 1.5.1; 1.5.2; 1.5.3; 1.5.4; 1.5.5; 1.6.1; 1.6.2;) л.3 (поз 1.6.3; 1.6.4; 1.6.6; 1.6.7; 1.6.9; 1.7.1; 1.7.2; 1.7.3; 1.7.4; 1.7.5; 1.7.6; 1.7.7)</v>
+        <f>S92</f>
+        <v>12002-81-020601-АУПТ1.1 СО2 ; Изм.0; 1л; поз(1.9)</v>
       </c>
       <c r="M92" s="83"/>
       <c r="N92" s="84">
-        <f t="shared" si="2"/>
-        <v>3742</v>
-      </c>
-      <c r="O92" s="83">
-        <v>5534.75</v>
-      </c>
-      <c r="P92" s="83">
-        <f>N92*AE92</f>
-        <v>23635444.92</v>
-      </c>
+        <f>V92</f>
+        <v>1</v>
+      </c>
+      <c r="O92" s="83"/>
+      <c r="P92" s="83"/>
       <c r="Q92" s="83">
-        <f t="shared" si="3"/>
-        <v>3742</v>
-      </c>
-      <c r="R92" s="84">
-        <f>ROUND(P92-I92,0)</f>
-        <v>23635445</v>
-      </c>
-      <c r="S92" s="67" t="str">
-        <f>TEXTJOIN("
-",FALSE(),S93:S105)</f>
-        <v>12002-81-0220-СПА.СО Изм2_, л.1  (поз1.1.5; 1.2; 1.4;1.5;1.6)
-12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(2.1; 2.4; 2.5; 2.6; 2.7; 2.8) 2л; поз(3.4; 3.6; 4.1; 4.2; 4.4;) 3л; поз(5.1;5.2,5,3;5,4;5,5;5,6)
-12002-81-020601-АУПТ. СО2; Изм.0; 1л; поз(1.1.9) 4л; поз(2.1.9) 6л; поз(3.1.9) 8л; поз(4.1.7) 10л; (5.1.7) 11л; поз(6.1.11) 14л; поз(7.1.9) 18л; поз(8.1.9) 21л; поз(9.1.9) 24л; поз(10.1.7) 27л; поз(11.1.9) 29л; поз(12.1.9) 32л; поз(13.1.9) 34л; поз(14.1.9) 37л; поз(15.1.7) 38л; поз(16.1.9) 41л; поз(17.1.9) 45л; поз(18.1.9) 48л; поз(19.1.9) 51л; поз(20.1.9)
-12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(2.1; 2.5; 2.6) 2л; поз(2.10; 2.11; 2.12; 3.4; 3.5; 4.1; 4.2) 3л; поз(4.4; 4.6; 5.1;5,2; 5,3;5,4; 5.6)
-12002-81-020601-АУПТ. СО4; Изм.0; л.1; (поз 1.3; 2.5; 3.1;4,1;4,2)
-12002-81-020601-СПА. СО; Изм.1; 1л; поз(2.1; 2.6; 2.7; 2.9; 2.10; 2.11) 2л; поз(2.14; 3.5; 3.6; 4.1; 4.8; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 6.7; 8.32)
-12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.1;  2.7; 2.8; 2.9; 2.10) 2л; поз(3.6; 3.7; 3.8; 4.1; 4.2; 4.4; 4.7; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 4л; поз(6.7; 6.8; 6.9; 6.11; 6.12; 6.13)
-12002-81-020602-АУПТ.СО1 ; Изм.0; л. (поз 1.1.11) л.3 (поз 1.3.14)  л.4 (поз 1.5.8)  л.5 (поз 1.7.1.10) л.7 (поз1.8.1.8) л.8 (поз 1.9.10) л.8 (поз 1.9.10) л.11 (поз 1.11.10) л.13 (поз 1.13.8) л.14 (поз1.15.8) л.15 (поз 1.17.10) л.17 (поз 1.19.8) л.18 (поз 1.21.8)
-12002-81-020602-СПА.СО; Изм.1; 1л; поз(1.2.1; 1.2.6; 1.2.7; 1.2.9; 1.2.10; 1.2.11; ) 2л; поз(1.2.12; 1.3.5; 1.3.6; 1.4.1) 3л; поз( 1.4.12; 1.5.2) 4л; поз(1.6.1; 1.6.2; 1.6.3; 1.6.4; 1.6.5; 1.6.6; 1.6.7; 1.6.8; 1.6.9)
-12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.2.1; 1.2.5; 1.2.7; 1.2.8; 1.2.10) 2л; поз(1.3.5; 1.3.6; 1.4.1; 1.4.2. 1.5.1; 1.5.2; 1.5.3; 1.5.4; 1.5.5; 1.6.1; 1.6.2;) л.3 (поз 1.6.3; 1.6.4; 1.6.6; 1.6.7; 1.6.9; 1.7.1; 1.7.2; 1.7.3; 1.7.4; 1.7.5; 1.7.6; 1.7.7)
-12002-81-020601-АУПТ1.1 СО1 ; Изм.0; 1л; поз(1.1;1.3;1.4;1.5;1.6;1.7; 2.4) 2л; поз(3.1;3.2; 3.4; 4.1;4.2;4.3;4.4;4.5;4.6)
- 12002-81-020601-АУПТ1.1 СО3 ; Изм.0; 1л; поз(1.2;1.3;1.5;1.6;2.1;2.3;2.5) 2л по(3.1;3.2;3.4;4.1;4.2;4.3;4.4)
-12002-81-020601-АУПТ1.1 СО2 ; Изм.0; 1л; поз(1.9)
-12002-81-020601-СПА1.1 СО; Изм.0; 1л; (поз2;4;) 2л; (поз30)
-12002-81-020603-АУПТ 1л; поз(1.1.17) л.4(поз 2.1.41)</v>
-      </c>
-      <c r="T92" s="117"/>
-      <c r="U92" s="102" t="s">
-        <v>50</v>
+        <f>N92-G92</f>
+        <v>1</v>
+      </c>
+      <c r="R92" s="84"/>
+      <c r="S92" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="T92" s="113" t="s">
+        <v>202</v>
+      </c>
+      <c r="U92" s="87" t="s">
+        <v>203</v>
       </c>
       <c r="V92" s="67">
-        <f>SUM(V93:V105)</f>
-        <v>3742</v>
-      </c>
-      <c r="W92" s="103">
-        <f>Z92+AC92+AF92+AI92</f>
-        <v>24922992.82</v>
-      </c>
-      <c r="X92" s="97">
+        <f>SUM(X92+AA92+AD92+AG92)</f>
+        <v>1</v>
+      </c>
+      <c r="W92" s="93"/>
+      <c r="X92" s="82"/>
+      <c r="Y92" s="84"/>
+      <c r="Z92" s="93"/>
+      <c r="AA92" s="110"/>
+      <c r="AB92" s="84"/>
+      <c r="AC92" s="93"/>
+      <c r="AD92" s="110">
         <v>0.0</v>
       </c>
-      <c r="Y92" s="99">
-        <v>5534.75</v>
-      </c>
-      <c r="Z92" s="103">
-        <f>ROUND(X92*Y92,2)</f>
-        <v>0</v>
-      </c>
-      <c r="AA92" s="111">
-        <v>0.0</v>
-      </c>
-      <c r="AB92" s="99">
-        <f>ROUND(Y92*$AM$6,2)</f>
-        <v>5534.75</v>
-      </c>
-      <c r="AC92" s="103">
-        <f>ROUND(AB92*AA92,2)</f>
-        <v>0</v>
-      </c>
-      <c r="AD92" s="111">
-        <f>SUM(AD93:AD105)</f>
-        <v>887</v>
-      </c>
-      <c r="AE92" s="122">
-        <f>ROUND(Y92*$AP$6,2)</f>
-        <v>6316.26</v>
-      </c>
-      <c r="AF92" s="103">
-        <f>ROUND(AE92*AD92,2)</f>
-        <v>5602522.62</v>
-      </c>
-      <c r="AG92" s="111">
-        <f>SUM(AG93:AG105)</f>
-        <v>2855</v>
-      </c>
-      <c r="AH92" s="122">
-        <f>ROUND(AE92*$AS$7,2)</f>
-        <v>6767.24</v>
-      </c>
-      <c r="AI92" s="103">
-        <f>ROUND(AH92*AG92,2)</f>
-        <v>19320470.2</v>
-      </c>
-      <c r="AJ92" s="123" t="s">
-        <v>161</v>
+      <c r="AE92" s="84"/>
+      <c r="AF92" s="93"/>
+      <c r="AG92" s="110">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="AH92" s="84"/>
+      <c r="AI92" s="93"/>
+      <c r="AJ92" s="76" t="s">
+        <v>204</v>
       </c>
       <c r="AK92" s="55" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="AL92" s="13"/>
       <c r="AM92" s="13"/>
@@ -11331,14 +11332,12 @@
       <c r="BE92" s="13"/>
       <c r="BF92" s="13"/>
     </row>
-    <row r="93" ht="129.75" customHeight="1" outlineLevel="1">
+    <row r="93" ht="88.5" customHeight="1" outlineLevel="1">
       <c r="A93" s="13"/>
       <c r="B93" s="77"/>
       <c r="C93" s="78"/>
       <c r="D93" s="79"/>
-      <c r="E93" s="79" t="s">
-        <v>51</v>
-      </c>
+      <c r="E93" s="79"/>
       <c r="F93" s="81"/>
       <c r="G93" s="82">
         <v>0.0</v>
@@ -11348,28 +11347,30 @@
       <c r="J93" s="84"/>
       <c r="K93" s="84"/>
       <c r="L93" s="83" t="str">
-        <f t="shared" ref="L93:L104" si="28">S93</f>
-        <v>12002-81-0220-СПА.СО Изм2_, л.1  (поз1.1.5; 1.2; 1.4;1.5;1.6)</v>
+        <f>S93</f>
+        <v>12002-81-020601-СПА1.1 СО; Изм.0; 1л; (поз2;4;) 2л; (поз30)</v>
       </c>
       <c r="M93" s="83"/>
       <c r="N93" s="84">
-        <f t="shared" si="2"/>
+        <f>V93</f>
         <v>9</v>
       </c>
       <c r="O93" s="83"/>
       <c r="P93" s="83"/>
       <c r="Q93" s="83">
-        <f t="shared" si="3"/>
+        <f>N93-G93</f>
         <v>9</v>
       </c>
       <c r="R93" s="84"/>
       <c r="S93" s="67" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="T93" s="113"/>
-      <c r="U93" s="87"/>
+      <c r="U93" s="87" t="s">
+        <v>143</v>
+      </c>
       <c r="V93" s="67">
-        <f t="shared" ref="V93:V98" si="29">SUM(X93+AA93+AD93+AG93)</f>
+        <f>SUM(X93+AA93+AD93+AG93)</f>
         <v>9</v>
       </c>
       <c r="W93" s="93"/>
@@ -11380,21 +11381,21 @@
       <c r="AB93" s="84"/>
       <c r="AC93" s="93"/>
       <c r="AD93" s="110">
-        <f>1+2+3+2+1</f>
-        <v>9</v>
+        <v>0.0</v>
       </c>
       <c r="AE93" s="84"/>
       <c r="AF93" s="93"/>
       <c r="AG93" s="110">
-        <v>0.0</v>
+        <f>1+7+1</f>
+        <v>9</v>
       </c>
       <c r="AH93" s="84"/>
       <c r="AI93" s="93"/>
-      <c r="AJ93" s="124" t="s">
-        <v>164</v>
+      <c r="AJ93" s="76" t="s">
+        <v>206</v>
       </c>
       <c r="AK93" s="55" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AL93" s="13"/>
       <c r="AM93" s="13"/>
@@ -11432,34 +11433,31 @@
       <c r="I94" s="83"/>
       <c r="J94" s="84"/>
       <c r="K94" s="84"/>
-      <c r="L94" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(2.1; 2.4; 2.5; 2.6; 2.7; 2.8) 2л; поз(3.4; 3.6; 4.1; 4.2; 4.4;) 3л; поз(5.1;5.2,5,3;5,4;5,5;5,6)</v>
-      </c>
+      <c r="L94" s="83"/>
       <c r="M94" s="83"/>
       <c r="N94" s="84">
-        <f t="shared" si="2"/>
-        <v>842</v>
+        <f>V94</f>
+        <v>2</v>
       </c>
       <c r="O94" s="83"/>
       <c r="P94" s="83"/>
       <c r="Q94" s="83">
-        <f t="shared" si="3"/>
-        <v>842</v>
+        <f>N94-G94</f>
+        <v>2</v>
       </c>
       <c r="R94" s="84"/>
       <c r="S94" s="67" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="T94" s="113" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="U94" s="87" t="s">
-        <v>124</v>
+        <v>203</v>
       </c>
       <c r="V94" s="67">
-        <f t="shared" si="29"/>
-        <v>842</v>
+        <f>SUM(X94+AA94+AD94+AG94)</f>
+        <v>2</v>
       </c>
       <c r="W94" s="93"/>
       <c r="X94" s="82"/>
@@ -11474,16 +11472,16 @@
       <c r="AE94" s="84"/>
       <c r="AF94" s="93"/>
       <c r="AG94" s="110">
-        <f>(484+5+22+6+6+1)+(9+32+26+46+48)+(34+8+41+33+33+8)</f>
-        <v>842</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="AH94" s="84"/>
       <c r="AI94" s="93"/>
       <c r="AJ94" s="76" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="AK94" s="55" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AL94" s="13"/>
       <c r="AM94" s="13"/>
@@ -11507,72 +11505,149 @@
       <c r="BE94" s="13"/>
       <c r="BF94" s="13"/>
     </row>
-    <row r="95" ht="157.5" customHeight="1" outlineLevel="1">
+    <row r="95" ht="197.25" customHeight="1" collapsed="1">
       <c r="A95" s="13"/>
       <c r="B95" s="77"/>
-      <c r="C95" s="78"/>
-      <c r="D95" s="79"/>
-      <c r="E95" s="79"/>
-      <c r="F95" s="81"/>
+      <c r="C95" s="78" t="s">
+        <v>146</v>
+      </c>
+      <c r="D95" s="94">
+        <v>8.0</v>
+      </c>
+      <c r="E95" s="94" t="s">
+        <v>147</v>
+      </c>
+      <c r="F95" s="96" t="s">
+        <v>49</v>
+      </c>
       <c r="G95" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="H95" s="83"/>
-      <c r="I95" s="83"/>
-      <c r="J95" s="84"/>
-      <c r="K95" s="84"/>
+        <f>SUM(G96)</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="83">
+        <v>19181.02</v>
+      </c>
+      <c r="I95" s="83">
+        <f>G95*H95</f>
+        <v>0</v>
+      </c>
+      <c r="J95" s="84">
+        <f>V95-G95</f>
+        <v>1007</v>
+      </c>
+      <c r="K95" s="84">
+        <f>ROUND(P95-I95,0)</f>
+        <v>23916190</v>
+      </c>
       <c r="L95" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020601-АУПТ. СО2; Изм.0; 1л; поз(1.1.9) 4л; поз(2.1.9) 6л; поз(3.1.9) 8л; поз(4.1.7) 10л; (5.1.7) 11л; поз(6.1.11) 14л; поз(7.1.9) 18л; поз(8.1.9) 21л; поз(9.1.9) 24л; поз(10.1.7) 27л; поз(11.1.9) 29л; поз(12.1.9) 32л; поз(13.1.9) 34л; поз(14.1.9) 37л; поз(15.1.7) 38л; поз(16.1.9) 41л; поз(17.1.9) 45л; поз(18.1.9) 48л; поз(19.1.9) 51л; поз(20.1.9)</v>
+        <f>TEXTJOIN("; 
+",FALSE(),L96,L97,L98,L99,L100,L101,L102,L103)</f>
+        <v>12002-81-0220-СПА.СО; л.1; поз (1.1.1; 1.1.2; 1.1.3; 1.1.4; 1.3-блок обработки на 2 шлейфа МИП-2); 
+12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(1.1; 1.2) 2л; поз(3.1; 3.2; 3.3; 3.5;4.6); 
+12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(1.1; 2.8) 2л; поз(3.1,3.2; 3.3; 3.6; 3.7); 
+12002-81-020601-АУПТ. СО4; Изм.0, л.1 (поз 2.2; 2.4); 
+12002-81-020601-СПА. СО; Изм.1; 1л; поз(1.1; 1.2; 1.3; 1.4; 1.5) 2л; поз(3.1; 3.2; 3.3; 3.4; 3.7; 4.2) 4л; поз(7.9); 
+12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(1.1; 3.1 ) 2л; поз( 3.2; 3.3; 3.4; 3.9; 4.8) 4л; поз(9.6;); 
+12002-81-020602-СПА.СО.Изм.1; 1л; поз(1.1.1) 2л; поз(1.3.1; 1.3.2; 1.3.3; 1.3.4; 1.3.7; 1.4.2; 1.4.3; 4; л5 поз (1.7.6); 
+12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.1.1; 1.3.1; 1.3.2; 1.3.3;) 2л; поз(1.3.4; 1.3.7; 1.3.8)</v>
       </c>
       <c r="M95" s="83"/>
       <c r="N95" s="84">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-      <c r="O95" s="83"/>
-      <c r="P95" s="83"/>
+        <f>V95</f>
+        <v>1007</v>
+      </c>
+      <c r="O95" s="83">
+        <v>19181.02</v>
+      </c>
+      <c r="P95" s="83">
+        <f>N95*AE95</f>
+        <v>23916189.58</v>
+      </c>
       <c r="Q95" s="83">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-      <c r="R95" s="84"/>
-      <c r="S95" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="T95" s="113" t="s">
-        <v>171</v>
-      </c>
-      <c r="U95" s="87" t="s">
-        <v>172</v>
-      </c>
-      <c r="V95" s="67">
-        <f t="shared" si="29"/>
-        <v>21</v>
-      </c>
-      <c r="W95" s="93"/>
-      <c r="X95" s="82"/>
-      <c r="Y95" s="84"/>
-      <c r="Z95" s="93"/>
-      <c r="AA95" s="110"/>
-      <c r="AB95" s="84"/>
-      <c r="AC95" s="93"/>
-      <c r="AD95" s="110">
+        <f>N95-G95</f>
+        <v>1007</v>
+      </c>
+      <c r="R95" s="84">
+        <f>ROUND(P95-I95,0)</f>
+        <v>23916190</v>
+      </c>
+      <c r="S95" s="119" t="str">
+        <f>TEXTJOIN("
+",FALSE(),S96:S105)</f>
+        <v>12002-81-0220-СПА.СО; л.1; поз (1.1.1; 1.1.2; 1.1.3; 1.1.4; 1.3-блок обработки на 2 шлейфа МИП-2)
+12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(1.1; 1.2) 2л; поз(3.1; 3.2; 3.3; 3.5;4.6)
+12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(1.1; 2.8) 2л; поз(3.1,3.2; 3.3; 3.6; 3.7)
+12002-81-020601-АУПТ. СО4; Изм.0, л.1 (поз 2.2; 2.4)
+12002-81-020601-СПА. СО; Изм.1; 1л; поз(1.1; 1.2; 1.3; 1.4; 1.5) 2л; поз(3.1; 3.2; 3.3; 3.4; 3.7; 4.2) 4л; поз(7.9)
+12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(1.1; 3.1 ) 2л; поз( 3.2; 3.3; 3.4; 3.9; 4.8) 4л; поз(9.6;)
+12002-81-020602-СПА.СО.Изм.1; 1л; поз(1.1.1) 2л; поз(1.3.1; 1.3.2; 1.3.3; 1.3.4; 1.3.7; 1.4.2; 1.4.3; 4; л5 поз (1.7.6)
+12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.1.1; 1.3.1; 1.3.2; 1.3.3;) 2л; поз(1.3.4; 1.3.7; 1.3.8)
+12002-81-020601-АУПТ1.1 СО1; Изм.0; 1л; поз(2.2; 2.3; 2.5) 
+12002-81-020601-АУПТ1.1 СО3 ; Изм.0; 1л; поз(2.1; 2.2; 2.4; 2.6) 
+12002-81-020601-СПА1.1. Изм.0; Изм.0  л1 поз(1; 3)</v>
+      </c>
+      <c r="T95" s="117"/>
+      <c r="U95" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="V95" s="120">
+        <f>SUM(V96:V105)</f>
+        <v>1007</v>
+      </c>
+      <c r="W95" s="103">
+        <f>Z95+AC95+AF95+AI95</f>
+        <v>25018427.08</v>
+      </c>
+      <c r="X95" s="97">
         <v>0.0</v>
       </c>
-      <c r="AE95" s="84"/>
-      <c r="AF95" s="93"/>
-      <c r="AG95" s="110">
-        <f>1+1+1+1+1+2+1+1+1+1+1+1+1+1+1+1+1+1+1+1</f>
-        <v>21</v>
-      </c>
-      <c r="AH95" s="84"/>
-      <c r="AI95" s="93"/>
-      <c r="AJ95" s="76" t="s">
-        <v>173</v>
-      </c>
-      <c r="AK95" s="55" t="s">
-        <v>174</v>
+      <c r="Y95" s="99">
+        <v>19181.02</v>
+      </c>
+      <c r="Z95" s="103">
+        <f>ROUND(X95*Y95,2)</f>
+        <v>0</v>
+      </c>
+      <c r="AA95" s="111">
+        <v>0.0</v>
+      </c>
+      <c r="AB95" s="99">
+        <f>ROUND(Y95*$AM$7,2)</f>
+        <v>20811.64</v>
+      </c>
+      <c r="AC95" s="103">
+        <f>ROUND(AB95*AA95,2)</f>
+        <v>0</v>
+      </c>
+      <c r="AD95" s="111">
+        <f>SUM(AD96:AD105)</f>
+        <v>357</v>
+      </c>
+      <c r="AE95" s="121">
+        <f>ROUND(Y95*$AP$7,2)</f>
+        <v>23749.94</v>
+      </c>
+      <c r="AF95" s="103">
+        <f>ROUND(AE95*AD95,2)</f>
+        <v>8478728.58</v>
+      </c>
+      <c r="AG95" s="111">
+        <f>SUM(AG96:AG105)</f>
+        <v>650</v>
+      </c>
+      <c r="AH95" s="121">
+        <f>ROUND(AE95*$AS$7,2)</f>
+        <v>25445.69</v>
+      </c>
+      <c r="AI95" s="103">
+        <f>ROUND(AH95*AG95,2)</f>
+        <v>16539698.5</v>
+      </c>
+      <c r="AJ95" s="76"/>
+      <c r="AK95" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Исправлено: порядок строк приведён в соответствие с нумерацией (БЕР №7, затем БЕР №8), нумерация БЕР сплошная 1–17.</t>
+        </is>
       </c>
       <c r="AL95" s="13"/>
       <c r="AM95" s="13"/>
@@ -11596,12 +11671,14 @@
       <c r="BE95" s="13"/>
       <c r="BF95" s="13"/>
     </row>
-    <row r="96" ht="88.5" customHeight="1" outlineLevel="1">
+    <row r="96" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A96" s="13"/>
       <c r="B96" s="77"/>
       <c r="C96" s="78"/>
       <c r="D96" s="79"/>
-      <c r="E96" s="79"/>
+      <c r="E96" s="79" t="s">
+        <v>51</v>
+      </c>
       <c r="F96" s="81"/>
       <c r="G96" s="82">
         <v>0.0</v>
@@ -11611,29 +11688,29 @@
       <c r="J96" s="84"/>
       <c r="K96" s="84"/>
       <c r="L96" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(2.1; 2.5; 2.6) 2л; поз(2.10; 2.11; 2.12; 3.4; 3.5; 4.1; 4.2) 3л; поз(4.4; 4.6; 5.1;5,2; 5,3;5,4; 5.6)</v>
+        <f>S96</f>
+        <v>12002-81-0220-СПА.СО; л.1; поз (1.1.1; 1.1.2; 1.1.3; 1.1.4; 1.3-блок обработки на 2 шлейфа МИП-2)</v>
       </c>
       <c r="M96" s="83"/>
       <c r="N96" s="84">
-        <f t="shared" si="2"/>
-        <v>388</v>
+        <f>V96</f>
+        <v>5</v>
       </c>
       <c r="O96" s="83"/>
       <c r="P96" s="83"/>
       <c r="Q96" s="83">
-        <f t="shared" si="3"/>
-        <v>388</v>
+        <f>N96-G96</f>
+        <v>5</v>
       </c>
       <c r="R96" s="84"/>
-      <c r="S96" s="67" t="s">
-        <v>175</v>
+      <c r="S96" s="112" t="s">
+        <v>148</v>
       </c>
       <c r="T96" s="113"/>
       <c r="U96" s="87"/>
-      <c r="V96" s="67">
-        <f t="shared" si="29"/>
-        <v>388</v>
+      <c r="V96" s="106">
+        <f>SUM(X96+AA96+AD96+AG96)</f>
+        <v>5</v>
       </c>
       <c r="W96" s="93"/>
       <c r="X96" s="82"/>
@@ -11643,22 +11720,18 @@
       <c r="AB96" s="84"/>
       <c r="AC96" s="93"/>
       <c r="AD96" s="110">
-        <v>0.0</v>
+        <f>1+1+1+1+1</f>
+        <v>5</v>
       </c>
       <c r="AE96" s="84"/>
       <c r="AF96" s="93"/>
       <c r="AG96" s="110">
-        <f>(4+20+4)+(8+16+60+27+5+30+20)+(6+5+12+11+68+68+24)</f>
-        <v>388</v>
+        <v>0.0</v>
       </c>
       <c r="AH96" s="84"/>
       <c r="AI96" s="93"/>
-      <c r="AJ96" s="76" t="s">
-        <v>176</v>
-      </c>
-      <c r="AK96" s="55" t="s">
-        <v>169</v>
-      </c>
+      <c r="AJ96" s="76"/>
+      <c r="AK96" s="55"/>
       <c r="AL96" s="13"/>
       <c r="AM96" s="13"/>
       <c r="AN96" s="13"/>
@@ -11681,7 +11754,7 @@
       <c r="BE96" s="13"/>
       <c r="BF96" s="13"/>
     </row>
-    <row r="97" ht="88.5" customHeight="1" outlineLevel="1">
+    <row r="97" ht="31.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A97" s="13"/>
       <c r="B97" s="77"/>
       <c r="C97" s="78"/>
@@ -11696,31 +11769,29 @@
       <c r="J97" s="84"/>
       <c r="K97" s="84"/>
       <c r="L97" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020601-АУПТ. СО4; Изм.0; л.1; (поз 1.3; 2.5; 3.1;4,1;4,2)</v>
+        <f>S97</f>
+        <v>12002-81-020601-АУПТ. СО1; Изм.0; 1л; поз(1.1; 1.2) 2л; поз(3.1; 3.2; 3.3; 3.5;4.6)</v>
       </c>
       <c r="M97" s="83"/>
       <c r="N97" s="84">
-        <f t="shared" si="2"/>
-        <v>62</v>
+        <f>V97</f>
+        <v>70</v>
       </c>
       <c r="O97" s="83"/>
       <c r="P97" s="83"/>
       <c r="Q97" s="83">
-        <f t="shared" si="3"/>
-        <v>62</v>
+        <f>N97-G97</f>
+        <v>70</v>
       </c>
       <c r="R97" s="84"/>
-      <c r="S97" s="67" t="s">
-        <v>177</v>
+      <c r="S97" s="112" t="s">
+        <v>149</v>
       </c>
       <c r="T97" s="113"/>
-      <c r="U97" s="118" t="s">
-        <v>178</v>
-      </c>
-      <c r="V97" s="67">
-        <f t="shared" si="29"/>
-        <v>62</v>
+      <c r="U97" s="87"/>
+      <c r="V97" s="106">
+        <f>SUM(X97+AA97+AD97+AG97)</f>
+        <v>70</v>
       </c>
       <c r="W97" s="93"/>
       <c r="X97" s="82"/>
@@ -11735,17 +11806,13 @@
       <c r="AE97" s="84"/>
       <c r="AF97" s="93"/>
       <c r="AG97" s="110">
-        <f>16+4+4+14+24</f>
-        <v>62</v>
+        <f>2+18+1+13+2+26+8</f>
+        <v>70</v>
       </c>
       <c r="AH97" s="84"/>
       <c r="AI97" s="93"/>
-      <c r="AJ97" s="76" t="s">
-        <v>179</v>
-      </c>
-      <c r="AK97" s="55" t="s">
-        <v>169</v>
-      </c>
+      <c r="AJ97" s="76"/>
+      <c r="AK97" s="55"/>
       <c r="AL97" s="13"/>
       <c r="AM97" s="13"/>
       <c r="AN97" s="13"/>
@@ -11768,7 +11835,7 @@
       <c r="BE97" s="13"/>
       <c r="BF97" s="13"/>
     </row>
-    <row r="98" ht="171.0" customHeight="1" outlineLevel="1">
+    <row r="98" ht="31.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A98" s="13"/>
       <c r="B98" s="77"/>
       <c r="C98" s="78"/>
@@ -11783,31 +11850,29 @@
       <c r="J98" s="84"/>
       <c r="K98" s="84"/>
       <c r="L98" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020601-СПА. СО; Изм.1; 1л; поз(2.1; 2.6; 2.7; 2.9; 2.10; 2.11) 2л; поз(2.14; 3.5; 3.6; 4.1; 4.8; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 6.7; 8.32)</v>
+        <f>S98</f>
+        <v>12002-81-020601-АУПТ. СО3; Изм.0; 1л; поз(1.1; 2.8) 2л; поз(3.1,3.2; 3.3; 3.6; 3.7)</v>
       </c>
       <c r="M98" s="83"/>
       <c r="N98" s="84">
-        <f t="shared" si="2"/>
-        <v>747</v>
+        <f>V98</f>
+        <v>117</v>
       </c>
       <c r="O98" s="83"/>
       <c r="P98" s="83"/>
       <c r="Q98" s="83">
-        <f t="shared" si="3"/>
-        <v>747</v>
+        <f>N98-G98</f>
+        <v>117</v>
       </c>
       <c r="R98" s="84"/>
-      <c r="S98" s="67" t="s">
-        <v>180</v>
-      </c>
-      <c r="T98" s="125" t="s">
-        <v>181</v>
-      </c>
+      <c r="S98" s="112" t="s">
+        <v>150</v>
+      </c>
+      <c r="T98" s="113"/>
       <c r="U98" s="87"/>
-      <c r="V98" s="67">
-        <f t="shared" si="29"/>
-        <v>747</v>
+      <c r="V98" s="106">
+        <f>SUM(X98+AA98+AD98+AG98)</f>
+        <v>117</v>
       </c>
       <c r="W98" s="93"/>
       <c r="X98" s="82"/>
@@ -11822,17 +11887,13 @@
       <c r="AE98" s="84"/>
       <c r="AF98" s="93"/>
       <c r="AG98" s="110">
-        <f>(137+16+53+4+4+57)+(1+38+54+97+28)+(12+22+37+7+8+9+13)+(99)+(51)</f>
-        <v>747</v>
+        <f>(2+2)+6+2+59+39+7</f>
+        <v>117</v>
       </c>
       <c r="AH98" s="84"/>
       <c r="AI98" s="93"/>
-      <c r="AJ98" s="76" t="s">
-        <v>182</v>
-      </c>
-      <c r="AK98" s="55" t="s">
-        <v>183</v>
-      </c>
+      <c r="AJ98" s="76"/>
+      <c r="AK98" s="55"/>
       <c r="AL98" s="13"/>
       <c r="AM98" s="13"/>
       <c r="AN98" s="13"/>
@@ -11855,7 +11916,7 @@
       <c r="BE98" s="13"/>
       <c r="BF98" s="13"/>
     </row>
-    <row r="99" ht="253.5" customHeight="1" outlineLevel="1">
+    <row r="99" ht="31.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A99" s="13"/>
       <c r="B99" s="77"/>
       <c r="C99" s="78"/>
@@ -11870,34 +11931,29 @@
       <c r="J99" s="84"/>
       <c r="K99" s="84"/>
       <c r="L99" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.1;  2.7; 2.8; 2.9; 2.10) 2л; поз(3.6; 3.7; 3.8; 4.1; 4.2; 4.4; 4.7; 5.2) 3л; поз(6.1; 6.2; 6.3; 6.4; 6.5; 6.6; 4л; поз(6.7; 6.8; 6.9; 6.11; 6.12; 6.13)
-12002-81-020602-АУПТ.СО1 ; Изм.0; л. (поз 1.1.11) л.3 (поз 1.3.14)  л.4 (поз 1.5.8)  л.5 (поз 1.7.1.10) л.7 (поз1.8.1.8) л.8 (поз 1.9.10) л.8 (поз 1.9.10) л.11 (поз 1.11.10) л.13 (поз 1.13.8) л.14 (поз1.15.8) л.15 (поз 1.17.10) л.17 (поз 1.19.8) л.18 (поз 1.21.8)</v>
+        <f>S99</f>
+        <v>12002-81-020601-АУПТ. СО4; Изм.0, л.1 (поз 2.2; 2.4)</v>
       </c>
       <c r="M99" s="83"/>
       <c r="N99" s="84">
-        <f t="shared" si="2"/>
-        <v>453</v>
+        <f>V99</f>
+        <v>14</v>
       </c>
       <c r="O99" s="83"/>
       <c r="P99" s="83"/>
       <c r="Q99" s="83">
-        <f t="shared" si="3"/>
-        <v>453</v>
+        <f>N99-G99</f>
+        <v>14</v>
       </c>
       <c r="R99" s="84"/>
-      <c r="S99" s="67" t="s">
-        <v>184</v>
-      </c>
-      <c r="T99" s="125" t="s">
-        <v>185</v>
-      </c>
-      <c r="U99" s="87" t="s">
-        <v>186</v>
-      </c>
-      <c r="V99" s="67">
+      <c r="S99" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="T99" s="113"/>
+      <c r="U99" s="87"/>
+      <c r="V99" s="106">
         <f>SUM(X99+AA99+AD99+AG99)</f>
-        <v>453</v>
+        <v>14</v>
       </c>
       <c r="W99" s="93"/>
       <c r="X99" s="82"/>
@@ -11907,22 +11963,18 @@
       <c r="AB99" s="84"/>
       <c r="AC99" s="93"/>
       <c r="AD99" s="110">
-        <v>226.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE99" s="84"/>
       <c r="AF99" s="93"/>
       <c r="AG99" s="110">
-        <f>((78+6+22+5+3)+(33+18+3+33+34+12+8+6)+(21+4+15+12+40+2)+(55+25+3+1+1+1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1)+(1))-AD99</f>
-        <v>227</v>
+        <f>6+8</f>
+        <v>14</v>
       </c>
       <c r="AH99" s="84"/>
       <c r="AI99" s="93"/>
-      <c r="AJ99" s="76" t="s">
-        <v>187</v>
-      </c>
-      <c r="AK99" s="55" t="s">
-        <v>188</v>
-      </c>
+      <c r="AJ99" s="76"/>
+      <c r="AK99" s="55"/>
       <c r="AL99" s="13"/>
       <c r="AM99" s="13"/>
       <c r="AN99" s="13"/>
@@ -11945,7 +11997,7 @@
       <c r="BE99" s="13"/>
       <c r="BF99" s="13"/>
     </row>
-    <row r="100" ht="171.0" customHeight="1" outlineLevel="1">
+    <row r="100" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A100" s="13"/>
       <c r="B100" s="77"/>
       <c r="C100" s="78"/>
@@ -11960,33 +12012,29 @@
       <c r="J100" s="84"/>
       <c r="K100" s="84"/>
       <c r="L100" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020602-СПА.СО; Изм.1; 1л; поз(1.2.1; 1.2.6; 1.2.7; 1.2.9; 1.2.10; 1.2.11; ) 2л; поз(1.2.12; 1.3.5; 1.3.6; 1.4.1) 3л; поз( 1.4.12; 1.5.2) 4л; поз(1.6.1; 1.6.2; 1.6.3; 1.6.4; 1.6.5; 1.6.6; 1.6.7; 1.6.8; 1.6.9)</v>
+        <f>S100</f>
+        <v>12002-81-020601-СПА. СО; Изм.1; 1л; поз(1.1; 1.2; 1.3; 1.4; 1.5) 2л; поз(3.1; 3.2; 3.3; 3.4; 3.7; 4.2) 4л; поз(7.9)</v>
       </c>
       <c r="M100" s="83"/>
       <c r="N100" s="84">
-        <f t="shared" si="2"/>
-        <v>905</v>
+        <f>V100</f>
+        <v>300</v>
       </c>
       <c r="O100" s="83"/>
       <c r="P100" s="83"/>
       <c r="Q100" s="83">
-        <f t="shared" si="3"/>
-        <v>905</v>
+        <f>N100-G100</f>
+        <v>300</v>
       </c>
       <c r="R100" s="84"/>
-      <c r="S100" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="T100" s="125" t="s">
-        <v>190</v>
-      </c>
-      <c r="U100" s="87" t="s">
-        <v>191</v>
-      </c>
-      <c r="V100" s="67">
+      <c r="S100" s="112" t="s">
+        <v>152</v>
+      </c>
+      <c r="T100" s="113"/>
+      <c r="U100" s="87"/>
+      <c r="V100" s="106">
         <f>SUM(X100+AA100+AD100+AG100)</f>
-        <v>905</v>
+        <v>300</v>
       </c>
       <c r="W100" s="93"/>
       <c r="X100" s="82"/>
@@ -11996,22 +12044,18 @@
       <c r="AB100" s="84"/>
       <c r="AC100" s="93"/>
       <c r="AD100" s="110">
-        <v>455.0</v>
+        <v>100.0</v>
       </c>
       <c r="AE100" s="84"/>
       <c r="AF100" s="93"/>
       <c r="AG100" s="110">
-        <f>((152+12+33+4+1+7)+(55+46+87+76)+(105+20)+(76+25+76+16+16+19+7+1+71))-AD100</f>
-        <v>450</v>
+        <f>((5+4+1+1+1)+(13+9+27+46+181+3)+(9))-AD100</f>
+        <v>200</v>
       </c>
       <c r="AH100" s="84"/>
       <c r="AI100" s="93"/>
-      <c r="AJ100" s="76" t="s">
-        <v>192</v>
-      </c>
-      <c r="AK100" s="55" t="s">
-        <v>193</v>
-      </c>
+      <c r="AJ100" s="76"/>
+      <c r="AK100" s="55"/>
       <c r="AL100" s="13"/>
       <c r="AM100" s="13"/>
       <c r="AN100" s="13"/>
@@ -12034,7 +12078,7 @@
       <c r="BE100" s="13"/>
       <c r="BF100" s="13"/>
     </row>
-    <row r="101" ht="94.5" customHeight="1" outlineLevel="1">
+    <row r="101" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A101" s="13"/>
       <c r="B101" s="77"/>
       <c r="C101" s="78"/>
@@ -12049,29 +12093,29 @@
       <c r="J101" s="84"/>
       <c r="K101" s="84"/>
       <c r="L101" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.2.1; 1.2.5; 1.2.7; 1.2.8; 1.2.10) 2л; поз(1.3.5; 1.3.6; 1.4.1; 1.4.2. 1.5.1; 1.5.2; 1.5.3; 1.5.4; 1.5.5; 1.6.1; 1.6.2;) л.3 (поз 1.6.3; 1.6.4; 1.6.6; 1.6.7; 1.6.9; 1.7.1; 1.7.2; 1.7.3; 1.7.4; 1.7.5; 1.7.6; 1.7.7)</v>
+        <f>S101</f>
+        <v>12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(1.1; 3.1 ) 2л; поз( 3.2; 3.3; 3.4; 3.9; 4.8) 4л; поз(9.6;)</v>
       </c>
       <c r="M101" s="83"/>
       <c r="N101" s="84">
-        <f t="shared" si="2"/>
-        <v>197</v>
+        <f>V101</f>
+        <v>70</v>
       </c>
       <c r="O101" s="83"/>
       <c r="P101" s="83"/>
       <c r="Q101" s="83">
-        <f t="shared" si="3"/>
-        <v>197</v>
+        <f>N101-G101</f>
+        <v>70</v>
       </c>
       <c r="R101" s="84"/>
-      <c r="S101" s="67" t="s">
-        <v>194</v>
+      <c r="S101" s="112" t="s">
+        <v>153</v>
       </c>
       <c r="T101" s="113"/>
       <c r="U101" s="87"/>
-      <c r="V101" s="67">
-        <f t="shared" ref="V101:V105" si="30">SUM(X101+AA101+AD101+AG101)</f>
-        <v>197</v>
+      <c r="V101" s="106">
+        <f>SUM(X101+AA101+AD101+AG101)</f>
+        <v>70</v>
       </c>
       <c r="W101" s="93"/>
       <c r="X101" s="82"/>
@@ -12081,22 +12125,18 @@
       <c r="AB101" s="84"/>
       <c r="AC101" s="93"/>
       <c r="AD101" s="110">
-        <f>(31+6+18+4+1)+(23+5+19+22+1+1+1+1+1+2+1)+(1+1+1+2+2+10+4+2+5+4+4+24)</f>
-        <v>197</v>
+        <v>35.0</v>
       </c>
       <c r="AE101" s="84"/>
       <c r="AF101" s="93"/>
       <c r="AG101" s="110">
-        <v>0.0</v>
+        <f>(3+7+7+19+6+24+1+3)-AD101</f>
+        <v>35</v>
       </c>
       <c r="AH101" s="84"/>
       <c r="AI101" s="93"/>
-      <c r="AJ101" s="76" t="s">
-        <v>195</v>
-      </c>
-      <c r="AK101" s="55" t="s">
-        <v>169</v>
-      </c>
+      <c r="AJ101" s="76"/>
+      <c r="AK101" s="55"/>
       <c r="AL101" s="13"/>
       <c r="AM101" s="13"/>
       <c r="AN101" s="13"/>
@@ -12119,7 +12159,7 @@
       <c r="BE101" s="13"/>
       <c r="BF101" s="13"/>
     </row>
-    <row r="102" ht="105.0" customHeight="1" outlineLevel="1">
+    <row r="102" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A102" s="13"/>
       <c r="B102" s="77"/>
       <c r="C102" s="78"/>
@@ -12134,34 +12174,29 @@
       <c r="J102" s="84"/>
       <c r="K102" s="84"/>
       <c r="L102" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020601-АУПТ1.1 СО1 ; Изм.0; 1л; поз(1.1;1.3;1.4;1.5;1.6;1.7; 2.4) 2л; поз(3.1;3.2; 3.4; 4.1;4.2;4.3;4.4;4.5;4.6)
- 12002-81-020601-АУПТ1.1 СО3 ; Изм.0; 1л; поз(1.2;1.3;1.5;1.6;2.1;2.3;2.5) 2л по(3.1;3.2;3.4;4.1;4.2;4.3;4.4)</v>
+        <f>S102</f>
+        <v>12002-81-020602-СПА.СО.Изм.1; 1л; поз(1.1.1) 2л; поз(1.3.1; 1.3.2; 1.3.3; 1.3.4; 1.3.7; 1.4.2; 1.4.3; 4; л5 поз (1.7.6)</v>
       </c>
       <c r="M102" s="83"/>
       <c r="N102" s="84">
-        <f t="shared" si="2"/>
-        <v>106</v>
+        <f>V102</f>
+        <v>346</v>
       </c>
       <c r="O102" s="83"/>
       <c r="P102" s="83"/>
       <c r="Q102" s="83">
-        <f t="shared" si="3"/>
-        <v>106</v>
+        <f>N102-G102</f>
+        <v>346</v>
       </c>
       <c r="R102" s="84"/>
-      <c r="S102" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="T102" s="113" t="s">
-        <v>197</v>
-      </c>
-      <c r="U102" s="87" t="s">
-        <v>198</v>
-      </c>
-      <c r="V102" s="67">
-        <f t="shared" si="30"/>
-        <v>106</v>
+      <c r="S102" s="112" t="s">
+        <v>154</v>
+      </c>
+      <c r="T102" s="113"/>
+      <c r="U102" s="87"/>
+      <c r="V102" s="106">
+        <f>SUM(X102+AA102+AD102+AG102)</f>
+        <v>346</v>
       </c>
       <c r="W102" s="93"/>
       <c r="X102" s="82"/>
@@ -12171,22 +12206,18 @@
       <c r="AB102" s="84"/>
       <c r="AC102" s="93"/>
       <c r="AD102" s="110">
-        <v>0.0</v>
+        <v>146.0</v>
       </c>
       <c r="AE102" s="84"/>
       <c r="AF102" s="93"/>
       <c r="AG102" s="110">
-        <f>(26+2+2+2+4+4+1)+(1+4+2+3+2+4+3+3+1)+(5+5+1+3+3+1)+(1+7+2+1+1+6+6)</f>
-        <v>106</v>
+        <f>((6)+(7+23+38+79+169+12+1)+(11))-AD102</f>
+        <v>200</v>
       </c>
       <c r="AH102" s="84"/>
       <c r="AI102" s="93"/>
-      <c r="AJ102" s="76" t="s">
-        <v>199</v>
-      </c>
-      <c r="AK102" s="55" t="s">
-        <v>200</v>
-      </c>
+      <c r="AJ102" s="76"/>
+      <c r="AK102" s="55"/>
       <c r="AL102" s="13"/>
       <c r="AM102" s="13"/>
       <c r="AN102" s="13"/>
@@ -12209,7 +12240,7 @@
       <c r="BE102" s="13"/>
       <c r="BF102" s="13"/>
     </row>
-    <row r="103" ht="88.5" customHeight="1" outlineLevel="1">
+    <row r="103" ht="47.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A103" s="13"/>
       <c r="B103" s="77"/>
       <c r="C103" s="78"/>
@@ -12224,33 +12255,29 @@
       <c r="J103" s="84"/>
       <c r="K103" s="84"/>
       <c r="L103" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020601-АУПТ1.1 СО2 ; Изм.0; 1л; поз(1.9)</v>
+        <f>S103</f>
+        <v>12002-81-020603-СПА.СО ; Изм.2; 1л; поз(1.1.1; 1.3.1; 1.3.2; 1.3.3;) 2л; поз(1.3.4; 1.3.7; 1.3.8)</v>
       </c>
       <c r="M103" s="83"/>
       <c r="N103" s="84">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>V103</f>
+        <v>71</v>
       </c>
       <c r="O103" s="83"/>
       <c r="P103" s="83"/>
       <c r="Q103" s="83">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f>N103-G103</f>
+        <v>71</v>
       </c>
       <c r="R103" s="84"/>
-      <c r="S103" s="67" t="s">
-        <v>201</v>
-      </c>
-      <c r="T103" s="113" t="s">
-        <v>202</v>
-      </c>
-      <c r="U103" s="87" t="s">
-        <v>203</v>
-      </c>
-      <c r="V103" s="67">
-        <f t="shared" si="30"/>
-        <v>1</v>
+      <c r="S103" s="112" t="s">
+        <v>155</v>
+      </c>
+      <c r="T103" s="113"/>
+      <c r="U103" s="87"/>
+      <c r="V103" s="106">
+        <f>SUM(X103+AA103+AD103+AG103)</f>
+        <v>71</v>
       </c>
       <c r="W103" s="93"/>
       <c r="X103" s="82"/>
@@ -12260,22 +12287,18 @@
       <c r="AB103" s="84"/>
       <c r="AC103" s="93"/>
       <c r="AD103" s="110">
-        <v>0.0</v>
+        <f>1+3+6+1+20+38+2</f>
+        <v>71</v>
       </c>
       <c r="AE103" s="84"/>
       <c r="AF103" s="93"/>
       <c r="AG103" s="110">
-        <f>1</f>
-        <v>1</v>
+        <v>0.0</v>
       </c>
       <c r="AH103" s="84"/>
       <c r="AI103" s="93"/>
-      <c r="AJ103" s="76" t="s">
-        <v>204</v>
-      </c>
-      <c r="AK103" s="55" t="s">
-        <v>174</v>
-      </c>
+      <c r="AJ103" s="76"/>
+      <c r="AK103" s="55"/>
       <c r="AL103" s="13"/>
       <c r="AM103" s="13"/>
       <c r="AN103" s="13"/>
@@ -12298,7 +12321,7 @@
       <c r="BE103" s="13"/>
       <c r="BF103" s="13"/>
     </row>
-    <row r="104" ht="88.5" customHeight="1" outlineLevel="1">
+    <row r="104" ht="63.0" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A104" s="13"/>
       <c r="B104" s="77"/>
       <c r="C104" s="78"/>
@@ -12313,31 +12336,34 @@
       <c r="J104" s="84"/>
       <c r="K104" s="84"/>
       <c r="L104" s="83" t="str">
-        <f t="shared" si="28"/>
-        <v>12002-81-020601-СПА1.1 СО; Изм.0; 1л; (поз2;4;) 2л; (поз30)</v>
+        <f>S104</f>
+        <v>12002-81-020601-АУПТ1.1 СО1; Изм.0; 1л; поз(2.2; 2.3; 2.5) 
+12002-81-020601-АУПТ1.1 СО3 ; Изм.0; 1л; поз(2.1; 2.2; 2.4; 2.6) </v>
       </c>
       <c r="M104" s="83"/>
       <c r="N104" s="84">
-        <f t="shared" si="2"/>
-        <v>9</v>
+        <f>V104</f>
+        <v>10</v>
       </c>
       <c r="O104" s="83"/>
       <c r="P104" s="83"/>
       <c r="Q104" s="83">
-        <f t="shared" si="3"/>
-        <v>9</v>
+        <f>N104-G104</f>
+        <v>10</v>
       </c>
       <c r="R104" s="84"/>
-      <c r="S104" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="T104" s="113"/>
+      <c r="S104" s="112" t="s">
+        <v>156</v>
+      </c>
+      <c r="T104" s="113" t="s">
+        <v>157</v>
+      </c>
       <c r="U104" s="87" t="s">
-        <v>143</v>
-      </c>
-      <c r="V104" s="67">
-        <f t="shared" si="30"/>
-        <v>9</v>
+        <v>124</v>
+      </c>
+      <c r="V104" s="106">
+        <f>SUM(X104+AA104+AD104+AG104)</f>
+        <v>10</v>
       </c>
       <c r="W104" s="93"/>
       <c r="X104" s="82"/>
@@ -12352,17 +12378,13 @@
       <c r="AE104" s="84"/>
       <c r="AF104" s="93"/>
       <c r="AG104" s="110">
-        <f>1+7+1</f>
-        <v>9</v>
+        <f>1+1+1+1+2+2+2</f>
+        <v>10</v>
       </c>
       <c r="AH104" s="84"/>
       <c r="AI104" s="93"/>
-      <c r="AJ104" s="76" t="s">
-        <v>206</v>
-      </c>
-      <c r="AK104" s="55" t="s">
-        <v>169</v>
-      </c>
+      <c r="AJ104" s="76"/>
+      <c r="AK104" s="55"/>
       <c r="AL104" s="13"/>
       <c r="AM104" s="13"/>
       <c r="AN104" s="13"/>
@@ -12385,7 +12407,7 @@
       <c r="BE104" s="13"/>
       <c r="BF104" s="13"/>
     </row>
-    <row r="105" ht="88.5" customHeight="1" outlineLevel="1">
+    <row r="105" ht="31.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A105" s="13"/>
       <c r="B105" s="77"/>
       <c r="C105" s="78"/>
@@ -12399,31 +12421,30 @@
       <c r="I105" s="83"/>
       <c r="J105" s="84"/>
       <c r="K105" s="84"/>
-      <c r="L105" s="83"/>
+      <c r="L105" s="83" t="str">
+        <f>S105</f>
+        <v>12002-81-020601-СПА1.1. Изм.0; Изм.0  л1 поз(1; 3)</v>
+      </c>
       <c r="M105" s="83"/>
       <c r="N105" s="84">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f>V105</f>
+        <v>4</v>
       </c>
       <c r="O105" s="83"/>
       <c r="P105" s="83"/>
       <c r="Q105" s="83">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f>N105-G105</f>
+        <v>4</v>
       </c>
       <c r="R105" s="84"/>
-      <c r="S105" s="67" t="s">
-        <v>207</v>
-      </c>
-      <c r="T105" s="113" t="s">
-        <v>202</v>
-      </c>
-      <c r="U105" s="87" t="s">
-        <v>203</v>
-      </c>
-      <c r="V105" s="67">
-        <f t="shared" si="30"/>
-        <v>2</v>
+      <c r="S105" s="112" t="s">
+        <v>158</v>
+      </c>
+      <c r="T105" s="113"/>
+      <c r="U105" s="87"/>
+      <c r="V105" s="106">
+        <f>SUM(X105+AA105+AD105+AG105)</f>
+        <v>4</v>
       </c>
       <c r="W105" s="93"/>
       <c r="X105" s="82"/>
@@ -12438,17 +12459,13 @@
       <c r="AE105" s="84"/>
       <c r="AF105" s="93"/>
       <c r="AG105" s="110">
-        <f>1+1</f>
-        <v>2</v>
+        <f>2+2</f>
+        <v>4</v>
       </c>
       <c r="AH105" s="84"/>
       <c r="AI105" s="93"/>
-      <c r="AJ105" s="76" t="s">
-        <v>204</v>
-      </c>
-      <c r="AK105" s="55" t="s">
-        <v>174</v>
-      </c>
+      <c r="AJ105" s="76"/>
+      <c r="AK105" s="55"/>
       <c r="AL105" s="13"/>
       <c r="AM105" s="13"/>
       <c r="AN105" s="13"/>
@@ -12518,7 +12535,7 @@
       </c>
       <c r="M106" s="83"/>
       <c r="N106" s="84">
-        <f t="shared" si="2"/>
+        <f>V106</f>
         <v>632</v>
       </c>
       <c r="O106" s="83">
@@ -12529,7 +12546,7 @@
         <v>13342095.12</v>
       </c>
       <c r="Q106" s="83">
-        <f t="shared" si="3"/>
+        <f>N106-G106</f>
         <v>632</v>
       </c>
       <c r="R106" s="84">
@@ -12657,13 +12674,13 @@
       </c>
       <c r="M107" s="83"/>
       <c r="N107" s="84">
-        <f t="shared" si="2"/>
+        <f>V107</f>
         <v>3</v>
       </c>
       <c r="O107" s="83"/>
       <c r="P107" s="83"/>
       <c r="Q107" s="83">
-        <f t="shared" si="3"/>
+        <f>N107-G107</f>
         <v>3</v>
       </c>
       <c r="R107" s="84"/>
@@ -12673,7 +12690,7 @@
       <c r="T107" s="113"/>
       <c r="U107" s="87"/>
       <c r="V107" s="106">
-        <f t="shared" ref="V107:V116" si="31">SUM(X107+AA107+AD107+AG107)</f>
+        <f>SUM(X107+AA107+AD107+AG107)</f>
         <v>3</v>
       </c>
       <c r="W107" s="93"/>
@@ -12741,13 +12758,13 @@
       </c>
       <c r="M108" s="83"/>
       <c r="N108" s="84">
-        <f t="shared" si="2"/>
+        <f>V108</f>
         <v>111</v>
       </c>
       <c r="O108" s="83"/>
       <c r="P108" s="83"/>
       <c r="Q108" s="83">
-        <f t="shared" si="3"/>
+        <f>N108-G108</f>
         <v>111</v>
       </c>
       <c r="R108" s="84"/>
@@ -12757,7 +12774,7 @@
       <c r="T108" s="113"/>
       <c r="U108" s="87"/>
       <c r="V108" s="67">
-        <f t="shared" si="31"/>
+        <f>SUM(X108+AA108+AD108+AG108)</f>
         <v>111</v>
       </c>
       <c r="W108" s="93"/>
@@ -12825,13 +12842,13 @@
       </c>
       <c r="M109" s="83"/>
       <c r="N109" s="84">
-        <f t="shared" si="2"/>
+        <f>V109</f>
         <v>105</v>
       </c>
       <c r="O109" s="83"/>
       <c r="P109" s="83"/>
       <c r="Q109" s="83">
-        <f t="shared" si="3"/>
+        <f>N109-G109</f>
         <v>105</v>
       </c>
       <c r="R109" s="84"/>
@@ -12841,7 +12858,7 @@
       <c r="T109" s="113"/>
       <c r="U109" s="87"/>
       <c r="V109" s="67">
-        <f t="shared" si="31"/>
+        <f>SUM(X109+AA109+AD109+AG109)</f>
         <v>105</v>
       </c>
       <c r="W109" s="93"/>
@@ -12907,13 +12924,13 @@
       </c>
       <c r="M110" s="83"/>
       <c r="N110" s="84">
-        <f t="shared" si="2"/>
+        <f>V110</f>
         <v>18</v>
       </c>
       <c r="O110" s="83"/>
       <c r="P110" s="83"/>
       <c r="Q110" s="83">
-        <f t="shared" si="3"/>
+        <f>N110-G110</f>
         <v>18</v>
       </c>
       <c r="R110" s="84"/>
@@ -12923,7 +12940,7 @@
       <c r="T110" s="113"/>
       <c r="U110" s="87"/>
       <c r="V110" s="67">
-        <f t="shared" si="31"/>
+        <f>SUM(X110+AA110+AD110+AG110)</f>
         <v>18</v>
       </c>
       <c r="W110" s="93"/>
@@ -12989,13 +13006,13 @@
       </c>
       <c r="M111" s="83"/>
       <c r="N111" s="84">
-        <f t="shared" si="2"/>
+        <f>V111</f>
         <v>113</v>
       </c>
       <c r="O111" s="83"/>
       <c r="P111" s="83"/>
       <c r="Q111" s="83">
-        <f t="shared" si="3"/>
+        <f>N111-G111</f>
         <v>113</v>
       </c>
       <c r="R111" s="84"/>
@@ -13005,7 +13022,7 @@
       <c r="T111" s="113"/>
       <c r="U111" s="87"/>
       <c r="V111" s="67">
-        <f t="shared" si="31"/>
+        <f>SUM(X111+AA111+AD111+AG111)</f>
         <v>113</v>
       </c>
       <c r="W111" s="93"/>
@@ -13071,13 +13088,13 @@
       </c>
       <c r="M112" s="83"/>
       <c r="N112" s="84">
-        <f t="shared" si="2"/>
+        <f>V112</f>
         <v>111</v>
       </c>
       <c r="O112" s="83"/>
       <c r="P112" s="83"/>
       <c r="Q112" s="83">
-        <f t="shared" si="3"/>
+        <f>N112-G112</f>
         <v>111</v>
       </c>
       <c r="R112" s="84"/>
@@ -13087,7 +13104,7 @@
       <c r="T112" s="113"/>
       <c r="U112" s="87"/>
       <c r="V112" s="67">
-        <f t="shared" si="31"/>
+        <f>SUM(X112+AA112+AD112+AG112)</f>
         <v>111</v>
       </c>
       <c r="W112" s="93"/>
@@ -13158,13 +13175,13 @@
       </c>
       <c r="M113" s="83"/>
       <c r="N113" s="84">
-        <f t="shared" si="2"/>
+        <f>V113</f>
         <v>123</v>
       </c>
       <c r="O113" s="83"/>
       <c r="P113" s="83"/>
       <c r="Q113" s="83">
-        <f t="shared" si="3"/>
+        <f>N113-G113</f>
         <v>123</v>
       </c>
       <c r="R113" s="84"/>
@@ -13174,7 +13191,7 @@
       <c r="T113" s="113"/>
       <c r="U113" s="87"/>
       <c r="V113" s="67">
-        <f t="shared" si="31"/>
+        <f>SUM(X113+AA113+AD113+AG113)</f>
         <v>123</v>
       </c>
       <c r="W113" s="93"/>
@@ -13242,13 +13259,13 @@
       </c>
       <c r="M114" s="83"/>
       <c r="N114" s="84">
-        <f t="shared" si="2"/>
+        <f>V114</f>
         <v>33</v>
       </c>
       <c r="O114" s="83"/>
       <c r="P114" s="83"/>
       <c r="Q114" s="83">
-        <f t="shared" si="3"/>
+        <f>N114-G114</f>
         <v>33</v>
       </c>
       <c r="R114" s="84"/>
@@ -13258,7 +13275,7 @@
       <c r="T114" s="113"/>
       <c r="U114" s="87"/>
       <c r="V114" s="67">
-        <f t="shared" si="31"/>
+        <f>SUM(X114+AA114+AD114+AG114)</f>
         <v>33</v>
       </c>
       <c r="W114" s="93"/>
@@ -13322,13 +13339,13 @@
       <c r="L115" s="83"/>
       <c r="M115" s="83"/>
       <c r="N115" s="84">
-        <f t="shared" si="2"/>
+        <f>V115</f>
         <v>12</v>
       </c>
       <c r="O115" s="83"/>
       <c r="P115" s="83"/>
       <c r="Q115" s="83">
-        <f t="shared" si="3"/>
+        <f>N115-G115</f>
         <v>12</v>
       </c>
       <c r="R115" s="84"/>
@@ -13338,7 +13355,7 @@
       <c r="T115" s="113"/>
       <c r="U115" s="87"/>
       <c r="V115" s="67">
-        <f t="shared" si="31"/>
+        <f>SUM(X115+AA115+AD115+AG115)</f>
         <v>12</v>
       </c>
       <c r="W115" s="93"/>
@@ -13402,13 +13419,13 @@
       <c r="L116" s="83"/>
       <c r="M116" s="83"/>
       <c r="N116" s="84">
-        <f t="shared" si="2"/>
+        <f>V116</f>
         <v>3</v>
       </c>
       <c r="O116" s="83"/>
       <c r="P116" s="83"/>
       <c r="Q116" s="83">
-        <f t="shared" si="3"/>
+        <f>N116-G116</f>
         <v>3</v>
       </c>
       <c r="R116" s="84"/>
@@ -13418,7 +13435,7 @@
       <c r="T116" s="113"/>
       <c r="U116" s="87"/>
       <c r="V116" s="106">
-        <f t="shared" si="31"/>
+        <f>SUM(X116+AA116+AD116+AG116)</f>
         <v>3</v>
       </c>
       <c r="W116" s="93"/>
@@ -13506,7 +13523,7 @@
       </c>
       <c r="M117" s="83"/>
       <c r="N117" s="84">
-        <f t="shared" si="2"/>
+        <f>V117</f>
         <v>136</v>
       </c>
       <c r="O117" s="83">
@@ -13517,7 +13534,7 @@
         <v>14710415.52</v>
       </c>
       <c r="Q117" s="83">
-        <f t="shared" si="3"/>
+        <f>N117-G117</f>
         <v>136</v>
       </c>
       <c r="R117" s="84">
@@ -13591,8 +13608,10 @@
       <c r="AJ117" s="76" t="s">
         <v>238</v>
       </c>
-      <c r="AK117" s="55" t="s">
-        <v>239</v>
+      <c r="AK117" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Расценка новая, расчёт стоимости прикладываем. Основную часть расценки составляет стоимость самого модуля, закупка входит в БЕР №10. Состав работ исправлен под технологию монтажа МПП/МГПП, стоимость в AE округлена до 2 знаков после запятой.</t>
+        </is>
       </c>
       <c r="AL117" s="13"/>
       <c r="AM117" s="13"/>
@@ -13637,13 +13656,13 @@
       </c>
       <c r="M118" s="83"/>
       <c r="N118" s="84">
-        <f t="shared" si="2"/>
+        <f>V118</f>
         <v>71</v>
       </c>
       <c r="O118" s="83"/>
       <c r="P118" s="83"/>
       <c r="Q118" s="83">
-        <f t="shared" si="3"/>
+        <f>N118-G118</f>
         <v>71</v>
       </c>
       <c r="R118" s="84"/>
@@ -13653,7 +13672,7 @@
       <c r="T118" s="113"/>
       <c r="U118" s="87"/>
       <c r="V118" s="106">
-        <f t="shared" ref="V118:V121" si="32">SUM(X118+AA118+AD118+AG118)</f>
+        <f>SUM(X118+AA118+AD118+AG118)</f>
         <v>71</v>
       </c>
       <c r="W118" s="93"/>
@@ -13717,13 +13736,13 @@
       </c>
       <c r="M119" s="83"/>
       <c r="N119" s="84">
-        <f t="shared" si="2"/>
+        <f>V119</f>
         <v>28</v>
       </c>
       <c r="O119" s="83"/>
       <c r="P119" s="83"/>
       <c r="Q119" s="83">
-        <f t="shared" si="3"/>
+        <f>N119-G119</f>
         <v>28</v>
       </c>
       <c r="R119" s="84"/>
@@ -13733,7 +13752,7 @@
       <c r="T119" s="113"/>
       <c r="U119" s="87"/>
       <c r="V119" s="106">
-        <f t="shared" si="32"/>
+        <f>SUM(X119+AA119+AD119+AG119)</f>
         <v>28</v>
       </c>
       <c r="W119" s="93"/>
@@ -13797,13 +13816,13 @@
       </c>
       <c r="M120" s="83"/>
       <c r="N120" s="84">
-        <f t="shared" si="2"/>
+        <f>V120</f>
         <v>35</v>
       </c>
       <c r="O120" s="83"/>
       <c r="P120" s="83"/>
       <c r="Q120" s="83">
-        <f t="shared" si="3"/>
+        <f>N120-G120</f>
         <v>35</v>
       </c>
       <c r="R120" s="84"/>
@@ -13813,7 +13832,7 @@
       <c r="T120" s="113"/>
       <c r="U120" s="87"/>
       <c r="V120" s="106">
-        <f t="shared" si="32"/>
+        <f>SUM(X120+AA120+AD120+AG120)</f>
         <v>35</v>
       </c>
       <c r="W120" s="93"/>
@@ -13875,13 +13894,13 @@
       <c r="L121" s="83"/>
       <c r="M121" s="83"/>
       <c r="N121" s="84">
-        <f t="shared" si="2"/>
+        <f>V121</f>
         <v>2</v>
       </c>
       <c r="O121" s="83"/>
       <c r="P121" s="83"/>
       <c r="Q121" s="83">
-        <f t="shared" si="3"/>
+        <f>N121-G121</f>
         <v>2</v>
       </c>
       <c r="R121" s="84"/>
@@ -13891,7 +13910,7 @@
       <c r="T121" s="113"/>
       <c r="U121" s="87"/>
       <c r="V121" s="106">
-        <f t="shared" si="32"/>
+        <f>SUM(X121+AA121+AD121+AG121)</f>
         <v>2</v>
       </c>
       <c r="W121" s="93"/>
@@ -13980,7 +13999,7 @@
       </c>
       <c r="M122" s="83"/>
       <c r="N122" s="84">
-        <f t="shared" si="2"/>
+        <f>V122</f>
         <v>114</v>
       </c>
       <c r="O122" s="83">
@@ -13991,7 +14010,7 @@
         <v>83029238.1</v>
       </c>
       <c r="Q122" s="83">
-        <f t="shared" si="3"/>
+        <f>N122-G122</f>
         <v>114</v>
       </c>
       <c r="R122" s="84">
@@ -14065,8 +14084,10 @@
       <c r="AJ122" s="76" t="s">
         <v>248</v>
       </c>
-      <c r="AK122" s="55" t="s">
-        <v>249</v>
+      <c r="AK122" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стоимость в AE округлена до 2 знаков после запятой, опечатка в составе работ БЕР №11 исправлена. БЕР №11 — комплектная модульная установка пожаротушения (АУПТ.СО2, поз. 1.1.1, 2.1.1 и т.д.), а не отдельный модуль, как в БЕР №10, поэтому составы работ разные; из состава БЕР №11 исключены насосы и теплообменники. Разница в цене связана со стоимостью оборудования установки, которое входит в расценку, — это видно из расчёта стоимости, который прикладываем.</t>
+        </is>
       </c>
       <c r="AL122" s="13"/>
       <c r="AM122" s="13"/>
@@ -14111,13 +14132,13 @@
       </c>
       <c r="M123" s="83"/>
       <c r="N123" s="84">
-        <f t="shared" si="2"/>
+        <f>V123</f>
         <v>82</v>
       </c>
       <c r="O123" s="83"/>
       <c r="P123" s="83"/>
       <c r="Q123" s="83">
-        <f t="shared" si="3"/>
+        <f>N123-G123</f>
         <v>82</v>
       </c>
       <c r="R123" s="84"/>
@@ -14129,7 +14150,7 @@
       </c>
       <c r="U123" s="87"/>
       <c r="V123" s="106">
-        <f t="shared" ref="V123:V126" si="33">SUM(X123+AA123+AD123+AG123)</f>
+        <f>SUM(X123+AA123+AD123+AG123)</f>
         <v>82</v>
       </c>
       <c r="W123" s="93"/>
@@ -14190,13 +14211,13 @@
       </c>
       <c r="M124" s="83"/>
       <c r="N124" s="84">
-        <f t="shared" si="2"/>
+        <f>V124</f>
         <v>20</v>
       </c>
       <c r="O124" s="83"/>
       <c r="P124" s="83"/>
       <c r="Q124" s="83">
-        <f t="shared" si="3"/>
+        <f>N124-G124</f>
         <v>20</v>
       </c>
       <c r="R124" s="84"/>
@@ -14206,7 +14227,7 @@
       <c r="T124" s="113"/>
       <c r="U124" s="87"/>
       <c r="V124" s="106">
-        <f t="shared" si="33"/>
+        <f>SUM(X124+AA124+AD124+AG124)</f>
         <v>20</v>
       </c>
       <c r="W124" s="93"/>
@@ -14267,13 +14288,13 @@
       </c>
       <c r="M125" s="83"/>
       <c r="N125" s="84">
-        <f t="shared" si="2"/>
+        <f>V125</f>
         <v>6</v>
       </c>
       <c r="O125" s="83"/>
       <c r="P125" s="83"/>
       <c r="Q125" s="83">
-        <f t="shared" si="3"/>
+        <f>N125-G125</f>
         <v>6</v>
       </c>
       <c r="R125" s="84"/>
@@ -14283,7 +14304,7 @@
       <c r="T125" s="113"/>
       <c r="U125" s="87"/>
       <c r="V125" s="106">
-        <f t="shared" si="33"/>
+        <f>SUM(X125+AA125+AD125+AG125)</f>
         <v>6</v>
       </c>
       <c r="W125" s="93"/>
@@ -14342,13 +14363,13 @@
       <c r="L126" s="83"/>
       <c r="M126" s="83"/>
       <c r="N126" s="84">
-        <f t="shared" si="2"/>
+        <f>V126</f>
         <v>6</v>
       </c>
       <c r="O126" s="83"/>
       <c r="P126" s="83"/>
       <c r="Q126" s="83">
-        <f t="shared" si="3"/>
+        <f>N126-G126</f>
         <v>6</v>
       </c>
       <c r="R126" s="84"/>
@@ -14358,7 +14379,7 @@
       <c r="T126" s="113"/>
       <c r="U126" s="87"/>
       <c r="V126" s="106">
-        <f t="shared" si="33"/>
+        <f>SUM(X126+AA126+AD126+AG126)</f>
         <v>6</v>
       </c>
       <c r="W126" s="93"/>
@@ -14448,7 +14469,7 @@
       </c>
       <c r="M127" s="83"/>
       <c r="N127" s="84">
-        <f t="shared" si="2"/>
+        <f>V127</f>
         <v>1732.4</v>
       </c>
       <c r="O127" s="83">
@@ -14459,7 +14480,7 @@
         <v>37878181.07</v>
       </c>
       <c r="Q127" s="83">
-        <f t="shared" si="3"/>
+        <f>N127-G127</f>
         <v>1732.4</v>
       </c>
       <c r="R127" s="84">
@@ -14540,7 +14561,7 @@
       </c>
       <c r="AK127" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Принято. Состав работ БЕР №12 приведён к ранее согласованной редакции: убрано упоминание гуммировки, исправлено наименование расценки.</t>
+          <t xml:space="preserve">Принято. Состав работ БЕР №12 приведён к ранее согласованной редакции: убрано упоминание гуммировки, исправлено наименование расценки (то же — в БЕР №13).</t>
         </is>
       </c>
       <c r="AL127" s="13"/>
@@ -14586,13 +14607,13 @@
       </c>
       <c r="M128" s="83"/>
       <c r="N128" s="84">
-        <f t="shared" si="2"/>
+        <f>V128</f>
         <v>893</v>
       </c>
       <c r="O128" s="83"/>
       <c r="P128" s="83"/>
       <c r="Q128" s="83">
-        <f t="shared" si="3"/>
+        <f>N128-G128</f>
         <v>893</v>
       </c>
       <c r="R128" s="84"/>
@@ -14602,7 +14623,7 @@
       <c r="T128" s="113"/>
       <c r="U128" s="87"/>
       <c r="V128" s="106">
-        <f t="shared" ref="V128:V134" si="34">SUM(X128+AA128+AD128+AG128)</f>
+        <f>SUM(X128+AA128+AD128+AG128)</f>
         <v>893</v>
       </c>
       <c r="W128" s="93"/>
@@ -14665,13 +14686,13 @@
       </c>
       <c r="M129" s="83"/>
       <c r="N129" s="84">
-        <f t="shared" si="2"/>
+        <f>V129</f>
         <v>216</v>
       </c>
       <c r="O129" s="83"/>
       <c r="P129" s="83"/>
       <c r="Q129" s="83">
-        <f t="shared" si="3"/>
+        <f>N129-G129</f>
         <v>216</v>
       </c>
       <c r="R129" s="84"/>
@@ -14681,7 +14702,7 @@
       <c r="T129" s="113"/>
       <c r="U129" s="87"/>
       <c r="V129" s="106">
-        <f t="shared" si="34"/>
+        <f>SUM(X129+AA129+AD129+AG129)</f>
         <v>216</v>
       </c>
       <c r="W129" s="93"/>
@@ -14744,13 +14765,13 @@
       </c>
       <c r="M130" s="83"/>
       <c r="N130" s="84">
-        <f t="shared" si="2"/>
+        <f>V130</f>
         <v>200</v>
       </c>
       <c r="O130" s="83"/>
       <c r="P130" s="83"/>
       <c r="Q130" s="83">
-        <f t="shared" si="3"/>
+        <f>N130-G130</f>
         <v>200</v>
       </c>
       <c r="R130" s="84"/>
@@ -14760,7 +14781,7 @@
       <c r="T130" s="113"/>
       <c r="U130" s="87"/>
       <c r="V130" s="106">
-        <f t="shared" si="34"/>
+        <f>SUM(X130+AA130+AD130+AG130)</f>
         <v>200</v>
       </c>
       <c r="W130" s="93"/>
@@ -14822,13 +14843,13 @@
       </c>
       <c r="M131" s="83"/>
       <c r="N131" s="84">
-        <f t="shared" si="2"/>
+        <f>V131</f>
         <v>181</v>
       </c>
       <c r="O131" s="83"/>
       <c r="P131" s="83"/>
       <c r="Q131" s="83">
-        <f t="shared" si="3"/>
+        <f>N131-G131</f>
         <v>181</v>
       </c>
       <c r="R131" s="84"/>
@@ -14838,7 +14859,7 @@
       <c r="T131" s="113"/>
       <c r="U131" s="87"/>
       <c r="V131" s="106">
-        <f t="shared" si="34"/>
+        <f>SUM(X131+AA131+AD131+AG131)</f>
         <v>181</v>
       </c>
       <c r="W131" s="93"/>
@@ -14901,13 +14922,13 @@
       </c>
       <c r="M132" s="83"/>
       <c r="N132" s="84">
-        <f t="shared" si="2"/>
+        <f>V132</f>
         <v>139.4</v>
       </c>
       <c r="O132" s="83"/>
       <c r="P132" s="83"/>
       <c r="Q132" s="83">
-        <f t="shared" si="3"/>
+        <f>N132-G132</f>
         <v>139.4</v>
       </c>
       <c r="R132" s="84"/>
@@ -14917,7 +14938,7 @@
       <c r="T132" s="113"/>
       <c r="U132" s="87"/>
       <c r="V132" s="106">
-        <f t="shared" si="34"/>
+        <f>SUM(X132+AA132+AD132+AG132)</f>
         <v>139.4</v>
       </c>
       <c r="W132" s="93"/>
@@ -14980,13 +15001,13 @@
       </c>
       <c r="M133" s="83"/>
       <c r="N133" s="84">
-        <f t="shared" si="2"/>
+        <f>V133</f>
         <v>57</v>
       </c>
       <c r="O133" s="83"/>
       <c r="P133" s="83"/>
       <c r="Q133" s="83">
-        <f t="shared" si="3"/>
+        <f>N133-G133</f>
         <v>57</v>
       </c>
       <c r="R133" s="84"/>
@@ -14996,7 +15017,7 @@
       <c r="T133" s="113"/>
       <c r="U133" s="87"/>
       <c r="V133" s="106">
-        <f t="shared" si="34"/>
+        <f>SUM(X133+AA133+AD133+AG133)</f>
         <v>57</v>
       </c>
       <c r="W133" s="93"/>
@@ -15057,13 +15078,13 @@
       <c r="L134" s="83"/>
       <c r="M134" s="83"/>
       <c r="N134" s="84">
-        <f t="shared" si="2"/>
+        <f>V134</f>
         <v>46</v>
       </c>
       <c r="O134" s="83"/>
       <c r="P134" s="83"/>
       <c r="Q134" s="83">
-        <f t="shared" si="3"/>
+        <f>N134-G134</f>
         <v>46</v>
       </c>
       <c r="R134" s="84"/>
@@ -15073,7 +15094,7 @@
       <c r="T134" s="113"/>
       <c r="U134" s="87"/>
       <c r="V134" s="106">
-        <f t="shared" si="34"/>
+        <f>SUM(X134+AA134+AD134+AG134)</f>
         <v>46</v>
       </c>
       <c r="W134" s="93"/>
@@ -15126,8 +15147,10 @@
       <c r="D135" s="94">
         <v>13.0</v>
       </c>
-      <c r="E135" s="94" t="s">
-        <v>271</v>
+      <c r="E135" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поставка стальных трубок (DN 0 - 300) (и / или) труба</t>
+        </is>
       </c>
       <c r="F135" s="96" t="s">
         <v>69</v>
@@ -15163,7 +15186,7 @@
       </c>
       <c r="M135" s="83"/>
       <c r="N135" s="84">
-        <f t="shared" si="2"/>
+        <f>V135</f>
         <v>1732.4</v>
       </c>
       <c r="O135" s="83">
@@ -15174,7 +15197,7 @@
         <v>37878181.07</v>
       </c>
       <c r="Q135" s="83">
-        <f t="shared" si="3"/>
+        <f>N135-G135</f>
         <v>1732.4</v>
       </c>
       <c r="R135" s="84">
@@ -15294,13 +15317,13 @@
       </c>
       <c r="M136" s="83"/>
       <c r="N136" s="84">
-        <f t="shared" si="2"/>
+        <f>V136</f>
         <v>893</v>
       </c>
       <c r="O136" s="83"/>
       <c r="P136" s="83"/>
       <c r="Q136" s="83">
-        <f t="shared" si="3"/>
+        <f>N136-G136</f>
         <v>893</v>
       </c>
       <c r="R136" s="84"/>
@@ -15310,7 +15333,7 @@
       <c r="T136" s="113"/>
       <c r="U136" s="87"/>
       <c r="V136" s="106">
-        <f t="shared" ref="V136:V142" si="35">SUM(X136+AA136+AD136+AG136)</f>
+        <f>SUM(X136+AA136+AD136+AG136)</f>
         <v>893</v>
       </c>
       <c r="W136" s="93"/>
@@ -15373,13 +15396,13 @@
       </c>
       <c r="M137" s="83"/>
       <c r="N137" s="84">
-        <f t="shared" si="2"/>
+        <f>V137</f>
         <v>216</v>
       </c>
       <c r="O137" s="83"/>
       <c r="P137" s="83"/>
       <c r="Q137" s="83">
-        <f t="shared" si="3"/>
+        <f>N137-G137</f>
         <v>216</v>
       </c>
       <c r="R137" s="84"/>
@@ -15389,7 +15412,7 @@
       <c r="T137" s="113"/>
       <c r="U137" s="87"/>
       <c r="V137" s="106">
-        <f t="shared" si="35"/>
+        <f>SUM(X137+AA137+AD137+AG137)</f>
         <v>216</v>
       </c>
       <c r="W137" s="93"/>
@@ -15452,13 +15475,13 @@
       </c>
       <c r="M138" s="83"/>
       <c r="N138" s="84">
-        <f t="shared" si="2"/>
+        <f>V138</f>
         <v>200</v>
       </c>
       <c r="O138" s="83"/>
       <c r="P138" s="83"/>
       <c r="Q138" s="83">
-        <f t="shared" si="3"/>
+        <f>N138-G138</f>
         <v>200</v>
       </c>
       <c r="R138" s="84"/>
@@ -15468,7 +15491,7 @@
       <c r="T138" s="113"/>
       <c r="U138" s="87"/>
       <c r="V138" s="106">
-        <f t="shared" si="35"/>
+        <f>SUM(X138+AA138+AD138+AG138)</f>
         <v>200</v>
       </c>
       <c r="W138" s="93"/>
@@ -15530,13 +15553,13 @@
       </c>
       <c r="M139" s="83"/>
       <c r="N139" s="84">
-        <f t="shared" si="2"/>
+        <f>V139</f>
         <v>181</v>
       </c>
       <c r="O139" s="83"/>
       <c r="P139" s="83"/>
       <c r="Q139" s="83">
-        <f t="shared" si="3"/>
+        <f>N139-G139</f>
         <v>181</v>
       </c>
       <c r="R139" s="84"/>
@@ -15546,7 +15569,7 @@
       <c r="T139" s="113"/>
       <c r="U139" s="87"/>
       <c r="V139" s="106">
-        <f t="shared" si="35"/>
+        <f>SUM(X139+AA139+AD139+AG139)</f>
         <v>181</v>
       </c>
       <c r="W139" s="93"/>
@@ -15609,13 +15632,13 @@
       </c>
       <c r="M140" s="83"/>
       <c r="N140" s="84">
-        <f t="shared" si="2"/>
+        <f>V140</f>
         <v>139.4</v>
       </c>
       <c r="O140" s="83"/>
       <c r="P140" s="83"/>
       <c r="Q140" s="83">
-        <f t="shared" si="3"/>
+        <f>N140-G140</f>
         <v>139.4</v>
       </c>
       <c r="R140" s="84"/>
@@ -15625,7 +15648,7 @@
       <c r="T140" s="113"/>
       <c r="U140" s="87"/>
       <c r="V140" s="106">
-        <f t="shared" si="35"/>
+        <f>SUM(X140+AA140+AD140+AG140)</f>
         <v>139.4</v>
       </c>
       <c r="W140" s="93"/>
@@ -15688,13 +15711,13 @@
       </c>
       <c r="M141" s="83"/>
       <c r="N141" s="84">
-        <f t="shared" si="2"/>
+        <f>V141</f>
         <v>57</v>
       </c>
       <c r="O141" s="83"/>
       <c r="P141" s="83"/>
       <c r="Q141" s="83">
-        <f t="shared" si="3"/>
+        <f>N141-G141</f>
         <v>57</v>
       </c>
       <c r="R141" s="84"/>
@@ -15704,7 +15727,7 @@
       <c r="T141" s="113"/>
       <c r="U141" s="87"/>
       <c r="V141" s="106">
-        <f t="shared" si="35"/>
+        <f>SUM(X141+AA141+AD141+AG141)</f>
         <v>57</v>
       </c>
       <c r="W141" s="93"/>
@@ -15765,13 +15788,13 @@
       <c r="L142" s="83"/>
       <c r="M142" s="83"/>
       <c r="N142" s="84">
-        <f t="shared" si="2"/>
+        <f>V142</f>
         <v>46</v>
       </c>
       <c r="O142" s="83"/>
       <c r="P142" s="83"/>
       <c r="Q142" s="83">
-        <f t="shared" si="3"/>
+        <f>N142-G142</f>
         <v>46</v>
       </c>
       <c r="R142" s="84"/>
@@ -15783,7 +15806,7 @@
       <c r="T142" s="113"/>
       <c r="U142" s="87"/>
       <c r="V142" s="106">
-        <f t="shared" si="35"/>
+        <f>SUM(X142+AA142+AD142+AG142)</f>
         <v>46</v>
       </c>
       <c r="W142" s="93"/>
@@ -15794,21 +15817,22 @@
       <c r="AB142" s="84"/>
       <c r="AC142" s="93"/>
       <c r="AD142" s="110">
-        <v>0.0</v>
+        <f>AD134</f>
       </c>
       <c r="AE142" s="84"/>
       <c r="AF142" s="93"/>
       <c r="AG142" s="110">
-        <f>1+27+12+(6)</f>
-        <v>46</v>
+        <f>AG134</f>
       </c>
       <c r="AH142" s="84"/>
       <c r="AI142" s="93"/>
       <c r="AJ142" s="131" t="s">
         <v>274</v>
       </c>
-      <c r="AK142" s="55" t="s">
-        <v>275</v>
+      <c r="AK142" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Исправлено: в AD142 и AG142 ссылки на AD134 и AG134 (объём поставки равен объёму монтажа).</t>
+        </is>
       </c>
       <c r="AL142" s="13"/>
       <c r="AM142" s="13"/>
@@ -15877,18 +15901,18 @@
       </c>
       <c r="M143" s="83"/>
       <c r="N143" s="84">
-        <f t="shared" si="2"/>
+        <f>V143</f>
         <v>140</v>
       </c>
       <c r="O143" s="83">
-        <v>17499.32</v>
+        <v>15334.14</v>
       </c>
       <c r="P143" s="83">
         <f>N143*AE143</f>
         <v>2449904.8</v>
       </c>
       <c r="Q143" s="83">
-        <f t="shared" si="3"/>
+        <f>N143-G143</f>
         <v>140</v>
       </c>
       <c r="R143" s="84">
@@ -15966,7 +15990,7 @@
       </c>
       <c r="AK143" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">БЕР №133 не включает закупку, а в БЕР №14 закупка арматуры и изделий трубопроводов входит в расценку, поэтому замена на БЕР №133 некорректна. Состав работ БЕР №14 уточнён: убрано «без учета закупки», добавлено «приобретение».</t>
+          <t xml:space="preserve">БЕР №133 не включает закупку, а в БЕР №14 закупка арматуры и изделий трубопроводов входит в расценку. В этом ДВР нет отдельной позиции на поставку клапанов, поэтому при переносе в БЕР №133 закупка клапанов не будет учтена ни в одной расценке. Состав работ БЕР №14 уточнён: «приобретение и доставка материалов».</t>
         </is>
       </c>
       <c r="AL143" s="13"/>
@@ -16012,13 +16036,13 @@
       </c>
       <c r="M144" s="83"/>
       <c r="N144" s="84">
-        <f t="shared" si="2"/>
+        <f>V144</f>
         <v>18</v>
       </c>
       <c r="O144" s="83"/>
       <c r="P144" s="83"/>
       <c r="Q144" s="83">
-        <f t="shared" si="3"/>
+        <f>N144-G144</f>
         <v>18</v>
       </c>
       <c r="R144" s="84"/>
@@ -16030,7 +16054,7 @@
       </c>
       <c r="U144" s="87"/>
       <c r="V144" s="106">
-        <f t="shared" ref="V144:V147" si="36">SUM(X144+AA144+AD144+AG144)</f>
+        <f>SUM(X144+AA144+AD144+AG144)</f>
         <v>18</v>
       </c>
       <c r="W144" s="93"/>
@@ -16092,13 +16116,13 @@
       </c>
       <c r="M145" s="83"/>
       <c r="N145" s="84">
-        <f t="shared" si="2"/>
+        <f>V145</f>
         <v>36</v>
       </c>
       <c r="O145" s="83"/>
       <c r="P145" s="83"/>
       <c r="Q145" s="83">
-        <f t="shared" si="3"/>
+        <f>N145-G145</f>
         <v>36</v>
       </c>
       <c r="R145" s="84"/>
@@ -16108,7 +16132,7 @@
       <c r="T145" s="113"/>
       <c r="U145" s="87"/>
       <c r="V145" s="106">
-        <f t="shared" si="36"/>
+        <f>SUM(X145+AA145+AD145+AG145)</f>
         <v>36</v>
       </c>
       <c r="W145" s="93"/>
@@ -16171,13 +16195,13 @@
       </c>
       <c r="M146" s="83"/>
       <c r="N146" s="84">
-        <f t="shared" si="2"/>
+        <f>V146</f>
         <v>16</v>
       </c>
       <c r="O146" s="83"/>
       <c r="P146" s="83"/>
       <c r="Q146" s="83">
-        <f t="shared" si="3"/>
+        <f>N146-G146</f>
         <v>16</v>
       </c>
       <c r="R146" s="84"/>
@@ -16187,7 +16211,7 @@
       <c r="T146" s="113"/>
       <c r="U146" s="87"/>
       <c r="V146" s="106">
-        <f t="shared" si="36"/>
+        <f>SUM(X146+AA146+AD146+AG146)</f>
         <v>16</v>
       </c>
       <c r="W146" s="93"/>
@@ -16250,13 +16274,13 @@
       </c>
       <c r="M147" s="83"/>
       <c r="N147" s="84">
-        <f t="shared" si="2"/>
+        <f>V147</f>
         <v>70</v>
       </c>
       <c r="O147" s="83"/>
       <c r="P147" s="83"/>
       <c r="Q147" s="83">
-        <f t="shared" si="3"/>
+        <f>N147-G147</f>
         <v>70</v>
       </c>
       <c r="R147" s="84"/>
@@ -16266,7 +16290,7 @@
       <c r="T147" s="113"/>
       <c r="U147" s="87"/>
       <c r="V147" s="106">
-        <f t="shared" si="36"/>
+        <f>SUM(X147+AA147+AD147+AG147)</f>
         <v>70</v>
       </c>
       <c r="W147" s="93"/>
@@ -16344,7 +16368,7 @@
         <v>11398112</v>
       </c>
       <c r="L148" s="83" t="str">
-        <f t="shared" ref="L148:L161" si="37">S148</f>
+        <f>S148</f>
         <v>12002-81-020601-АУПТ. СО1;;л5; поз(8.1;8.2;8.3;) л6; поз(8.4;8.5;) 
 12002-81-020601-АУПТ. СО3;;л10; поз(12.1;12.2;)
 12002-81-020601-АУПТ. СО4;; л6; поз(8.15)
@@ -16358,7 +16382,7 @@
       </c>
       <c r="M148" s="83"/>
       <c r="N148" s="84">
-        <f t="shared" si="2"/>
+        <f>V148</f>
         <v>1188</v>
       </c>
       <c r="O148" s="83">
@@ -16369,7 +16393,7 @@
         <v>11398111.56</v>
       </c>
       <c r="Q148" s="83">
-        <f t="shared" si="3"/>
+        <f>N148-G148</f>
         <v>1188</v>
       </c>
       <c r="R148" s="84">
@@ -16489,7 +16513,7 @@
       <c r="J149" s="84"/>
       <c r="K149" s="84"/>
       <c r="L149" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S149</f>
         <v>12002-81-020601-АУПТ. СО1;;л5; поз(8.1;8.2;8.3;) л6; поз(8.4;8.5;) </v>
       </c>
       <c r="M149" s="83"/>
@@ -16500,7 +16524,7 @@
       <c r="O149" s="83"/>
       <c r="P149" s="83"/>
       <c r="Q149" s="83">
-        <f t="shared" si="3"/>
+        <f>N149-G149</f>
         <v>107</v>
       </c>
       <c r="R149" s="84"/>
@@ -16510,7 +16534,7 @@
       <c r="T149" s="113"/>
       <c r="U149" s="87"/>
       <c r="V149" s="106">
-        <f t="shared" ref="V149:V154" si="38">SUM(X149+AA149+AD149+AG149)</f>
+        <f>SUM(X149+AA149+AD149+AG149)</f>
         <v>107</v>
       </c>
       <c r="W149" s="93"/>
@@ -16569,7 +16593,7 @@
       <c r="J150" s="84"/>
       <c r="K150" s="84"/>
       <c r="L150" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S150</f>
         <v>12002-81-020601-АУПТ. СО3;;л10; поз(12.1;12.2;)</v>
       </c>
       <c r="M150" s="83"/>
@@ -16580,7 +16604,7 @@
       <c r="O150" s="83"/>
       <c r="P150" s="83"/>
       <c r="Q150" s="83">
-        <f t="shared" si="3"/>
+        <f>N150-G150</f>
         <v>128</v>
       </c>
       <c r="R150" s="84"/>
@@ -16590,7 +16614,7 @@
       <c r="T150" s="113"/>
       <c r="U150" s="87"/>
       <c r="V150" s="106">
-        <f t="shared" si="38"/>
+        <f>SUM(X150+AA150+AD150+AG150)</f>
         <v>128</v>
       </c>
       <c r="W150" s="93"/>
@@ -16649,7 +16673,7 @@
       <c r="J151" s="84"/>
       <c r="K151" s="84"/>
       <c r="L151" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S151</f>
         <v>12002-81-020601-АУПТ. СО4;; л6; поз(8.15)</v>
       </c>
       <c r="M151" s="83"/>
@@ -16660,7 +16684,7 @@
       <c r="O151" s="83"/>
       <c r="P151" s="83"/>
       <c r="Q151" s="83">
-        <f t="shared" si="3"/>
+        <f>N151-G151</f>
         <v>40</v>
       </c>
       <c r="R151" s="84"/>
@@ -16670,7 +16694,7 @@
       <c r="T151" s="113"/>
       <c r="U151" s="87"/>
       <c r="V151" s="106">
-        <f t="shared" si="38"/>
+        <f>SUM(X151+AA151+AD151+AG151)</f>
         <v>40</v>
       </c>
       <c r="W151" s="93"/>
@@ -16729,7 +16753,7 @@
       <c r="J152" s="84"/>
       <c r="K152" s="84"/>
       <c r="L152" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S152</f>
         <v>12002-81-020602-АУПТ.СО1;Изм.0;л6; поз(10.2.1;10.2.2;10.2.3;)</v>
       </c>
       <c r="M152" s="83"/>
@@ -16740,7 +16764,7 @@
       <c r="O152" s="83"/>
       <c r="P152" s="83"/>
       <c r="Q152" s="83">
-        <f t="shared" si="3"/>
+        <f>N152-G152</f>
         <v>27</v>
       </c>
       <c r="R152" s="84"/>
@@ -16752,7 +16776,7 @@
       </c>
       <c r="U152" s="87"/>
       <c r="V152" s="106">
-        <f t="shared" si="38"/>
+        <f>SUM(X152+AA152+AD152+AG152)</f>
         <v>27</v>
       </c>
       <c r="W152" s="93"/>
@@ -16811,18 +16835,18 @@
       <c r="J153" s="84"/>
       <c r="K153" s="84"/>
       <c r="L153" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S153</f>
         <v>12002-81-020601-АУПТ1.1 СО1 Изм.0  л4 поз(7.1-7.4) </v>
       </c>
       <c r="M153" s="83"/>
       <c r="N153" s="84">
-        <f t="shared" ref="N153:N159" si="39">V153</f>
+        <f>V153</f>
         <v>24</v>
       </c>
       <c r="O153" s="83"/>
       <c r="P153" s="83"/>
       <c r="Q153" s="83">
-        <f t="shared" si="3"/>
+        <f>N153-G153</f>
         <v>24</v>
       </c>
       <c r="R153" s="84"/>
@@ -16836,7 +16860,7 @@
         <v>203</v>
       </c>
       <c r="V153" s="106">
-        <f t="shared" si="38"/>
+        <f>SUM(X153+AA153+AD153+AG153)</f>
         <v>24</v>
       </c>
       <c r="W153" s="93"/>
@@ -16895,18 +16919,18 @@
       <c r="J154" s="84"/>
       <c r="K154" s="84"/>
       <c r="L154" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S154</f>
         <v>12002-81-020601-АУПТ1.1 СО3 Изм.0  л6 поз(9.1-9.2) </v>
       </c>
       <c r="M154" s="83"/>
       <c r="N154" s="84">
-        <f t="shared" si="39"/>
+        <f>V154</f>
         <v>27</v>
       </c>
       <c r="O154" s="83"/>
       <c r="P154" s="83"/>
       <c r="Q154" s="83">
-        <f t="shared" si="3"/>
+        <f>N154-G154</f>
         <v>27</v>
       </c>
       <c r="R154" s="84"/>
@@ -16920,7 +16944,7 @@
         <v>203</v>
       </c>
       <c r="V154" s="106">
-        <f t="shared" si="38"/>
+        <f>SUM(X154+AA154+AD154+AG154)</f>
         <v>27</v>
       </c>
       <c r="W154" s="93"/>
@@ -16979,18 +17003,18 @@
       <c r="J155" s="84"/>
       <c r="K155" s="84"/>
       <c r="L155" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S155</f>
         <v>12002-81-020601-СПА. СО; Изм.1; 6л; поз(9.1,9.2,9.3)</v>
       </c>
       <c r="M155" s="83"/>
       <c r="N155" s="84">
-        <f t="shared" si="39"/>
+        <f>V155</f>
         <v>396</v>
       </c>
       <c r="O155" s="83"/>
       <c r="P155" s="83"/>
       <c r="Q155" s="83">
-        <f t="shared" si="3"/>
+        <f>N155-G155</f>
         <v>396</v>
       </c>
       <c r="R155" s="84"/>
@@ -17063,18 +17087,18 @@
       <c r="J156" s="84"/>
       <c r="K156" s="84"/>
       <c r="L156" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S156</f>
         <v>12002-81-020602-СПА.СО л.6 (2.2.1-2.2.4)</v>
       </c>
       <c r="M156" s="83"/>
       <c r="N156" s="84">
-        <f t="shared" si="39"/>
+        <f>V156</f>
         <v>387</v>
       </c>
       <c r="O156" s="83"/>
       <c r="P156" s="83"/>
       <c r="Q156" s="83">
-        <f t="shared" si="3"/>
+        <f>N156-G156</f>
         <v>387</v>
       </c>
       <c r="R156" s="84"/>
@@ -17147,18 +17171,18 @@
       <c r="J157" s="84"/>
       <c r="K157" s="84"/>
       <c r="L157" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S157</f>
         <v>12002-81-020603-СПА.СО л.5 ( п.2.2.1-2.2.4; 2.5.2)</v>
       </c>
       <c r="M157" s="83"/>
       <c r="N157" s="84">
-        <f t="shared" si="39"/>
+        <f>V157</f>
         <v>42</v>
       </c>
       <c r="O157" s="83"/>
       <c r="P157" s="83"/>
       <c r="Q157" s="83">
-        <f t="shared" si="3"/>
+        <f>N157-G157</f>
         <v>42</v>
       </c>
       <c r="R157" s="84"/>
@@ -17172,7 +17196,7 @@
         <v>203</v>
       </c>
       <c r="V157" s="106">
-        <f t="shared" ref="V157:V158" si="40">SUM(X157+AA157+AD157+AG157)</f>
+        <f>SUM(X157+AA157+AD157+AG157)</f>
         <v>42</v>
       </c>
       <c r="W157" s="93"/>
@@ -17231,18 +17255,18 @@
       <c r="J158" s="84"/>
       <c r="K158" s="84"/>
       <c r="L158" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S158</f>
         <v>12002-81-0220-СПА.СО Изм2_, л.2  (поз 2.9)</v>
       </c>
       <c r="M158" s="83"/>
       <c r="N158" s="84">
-        <f t="shared" si="39"/>
+        <f>V158</f>
         <v>10</v>
       </c>
       <c r="O158" s="83"/>
       <c r="P158" s="83"/>
       <c r="Q158" s="83">
-        <f t="shared" si="3"/>
+        <f>N158-G158</f>
         <v>10</v>
       </c>
       <c r="R158" s="84"/>
@@ -17256,7 +17280,7 @@
         <v>203</v>
       </c>
       <c r="V158" s="106">
-        <f t="shared" si="40"/>
+        <f>SUM(X158+AA158+AD158+AG158)</f>
         <v>10</v>
       </c>
       <c r="W158" s="93"/>
@@ -17325,7 +17349,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="84">
-        <f t="shared" ref="J159:J161" si="41">V159-G159</f>
+        <f>V159-G159</f>
         <v>292</v>
       </c>
       <c r="K159" s="84">
@@ -17333,7 +17357,7 @@
         <v>13397018</v>
       </c>
       <c r="L159" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S159</f>
         <v>12002-81-020601-СПА. СО; Изм.1; 1л; поз(2.8)
 12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.5; 2.6) л.2(поз 4.6)
 12002-81-020602-СПА.СО.Изм.1 1л(1.2.8)
@@ -17341,7 +17365,7 @@
       </c>
       <c r="M159" s="83"/>
       <c r="N159" s="84">
-        <f t="shared" si="39"/>
+        <f>V159</f>
         <v>292</v>
       </c>
       <c r="O159" s="83">
@@ -17352,7 +17376,7 @@
         <v>13397018.4</v>
       </c>
       <c r="Q159" s="83">
-        <f t="shared" si="3"/>
+        <f>N159-G159</f>
         <v>292</v>
       </c>
       <c r="R159" s="84">
@@ -17464,12 +17488,12 @@
       <c r="H160" s="83"/>
       <c r="I160" s="83"/>
       <c r="J160" s="84">
-        <f t="shared" si="41"/>
+        <f>V160-G160</f>
         <v>52</v>
       </c>
       <c r="K160" s="84"/>
       <c r="L160" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S160</f>
         <v>12002-81-020601-АУПТ.СО3 ; Изм.0; 1л; поз(2.3; 2.4)</v>
       </c>
       <c r="M160" s="83"/>
@@ -17480,7 +17504,7 @@
       <c r="O160" s="83"/>
       <c r="P160" s="83"/>
       <c r="Q160" s="83">
-        <f t="shared" si="3"/>
+        <f>N160-G160</f>
         <v>28</v>
       </c>
       <c r="R160" s="84"/>
@@ -17494,7 +17518,7 @@
         <v>306</v>
       </c>
       <c r="V160" s="106">
-        <f t="shared" ref="V160:V166" si="42">SUM(X160+AA160+AD160+AG160)</f>
+        <f>SUM(X160+AA160+AD160+AG160)</f>
         <v>52</v>
       </c>
       <c r="W160" s="93"/>
@@ -17551,12 +17575,12 @@
       <c r="H161" s="83"/>
       <c r="I161" s="83"/>
       <c r="J161" s="84">
-        <f t="shared" si="41"/>
+        <f>V161-G161</f>
         <v>40</v>
       </c>
       <c r="K161" s="84"/>
       <c r="L161" s="83" t="str">
-        <f t="shared" si="37"/>
+        <f>S161</f>
         <v>12002-81-020601-АУПТ.СО4 ; Изм.0; 1л; поз(1.2)</v>
       </c>
       <c r="M161" s="83"/>
@@ -17567,7 +17591,7 @@
       <c r="O161" s="83"/>
       <c r="P161" s="83"/>
       <c r="Q161" s="83">
-        <f t="shared" si="3"/>
+        <f>N161-G161</f>
         <v>40</v>
       </c>
       <c r="R161" s="84"/>
@@ -17577,7 +17601,7 @@
       <c r="T161" s="113"/>
       <c r="U161" s="87"/>
       <c r="V161" s="106">
-        <f t="shared" si="42"/>
+        <f>SUM(X161+AA161+AD161+AG161)</f>
         <v>40</v>
       </c>
       <c r="W161" s="93"/>
@@ -17643,7 +17667,7 @@
       <c r="O162" s="83"/>
       <c r="P162" s="83"/>
       <c r="Q162" s="83">
-        <f t="shared" si="3"/>
+        <f>N162-G162</f>
         <v>6</v>
       </c>
       <c r="R162" s="84"/>
@@ -17653,7 +17677,7 @@
       <c r="T162" s="113"/>
       <c r="U162" s="87"/>
       <c r="V162" s="106">
-        <f t="shared" si="42"/>
+        <f>SUM(X162+AA162+AD162+AG162)</f>
         <v>6</v>
       </c>
       <c r="W162" s="93"/>
@@ -17709,12 +17733,12 @@
       <c r="H163" s="83"/>
       <c r="I163" s="83"/>
       <c r="J163" s="84">
-        <f t="shared" ref="J163:J167" si="43">V163-G163</f>
+        <f>V163-G163</f>
         <v>69</v>
       </c>
       <c r="K163" s="84"/>
       <c r="L163" s="83" t="str">
-        <f t="shared" ref="L163:L167" si="44">S163</f>
+        <f>S163</f>
         <v>12002-81-020601-СПА. СО; Изм.1; 1л; поз(2.8)</v>
       </c>
       <c r="M163" s="83"/>
@@ -17724,7 +17748,7 @@
       <c r="O163" s="83"/>
       <c r="P163" s="83"/>
       <c r="Q163" s="83">
-        <f t="shared" si="3"/>
+        <f>N163-G163</f>
         <v>69</v>
       </c>
       <c r="R163" s="84"/>
@@ -17734,7 +17758,7 @@
       <c r="T163" s="113"/>
       <c r="U163" s="87"/>
       <c r="V163" s="106">
-        <f t="shared" si="42"/>
+        <f>SUM(X163+AA163+AD163+AG163)</f>
         <v>69</v>
       </c>
       <c r="W163" s="93"/>
@@ -17790,12 +17814,12 @@
       <c r="H164" s="83"/>
       <c r="I164" s="83"/>
       <c r="J164" s="84">
-        <f t="shared" si="43"/>
+        <f>V164-G164</f>
         <v>42</v>
       </c>
       <c r="K164" s="84"/>
       <c r="L164" s="83" t="str">
-        <f t="shared" si="44"/>
+        <f>S164</f>
         <v>12002-81-020602-АУПТ.СО1 ; Изм.0; 1л; поз(2.5; 2.6) л.2(поз 4.6)</v>
       </c>
       <c r="M164" s="83"/>
@@ -17806,7 +17830,7 @@
       <c r="O164" s="83"/>
       <c r="P164" s="83"/>
       <c r="Q164" s="83">
-        <f t="shared" si="3"/>
+        <f>N164-G164</f>
         <v>42</v>
       </c>
       <c r="R164" s="84"/>
@@ -17816,7 +17840,7 @@
       <c r="T164" s="113"/>
       <c r="U164" s="87"/>
       <c r="V164" s="106">
-        <f t="shared" si="42"/>
+        <f>SUM(X164+AA164+AD164+AG164)</f>
         <v>42</v>
       </c>
       <c r="W164" s="93"/>
@@ -17875,12 +17899,12 @@
         <v>311</v>
       </c>
       <c r="J165" s="84">
-        <f t="shared" si="43"/>
+        <f>V165-G165</f>
         <v>62</v>
       </c>
       <c r="K165" s="84"/>
       <c r="L165" s="83" t="str">
-        <f t="shared" si="44"/>
+        <f>S165</f>
         <v>12002-81-020602-СПА.СО.Изм.1 1л(1.2.8)</v>
       </c>
       <c r="M165" s="83"/>
@@ -17890,7 +17914,7 @@
       <c r="O165" s="83"/>
       <c r="P165" s="83"/>
       <c r="Q165" s="83">
-        <f t="shared" si="3"/>
+        <f>N165-G165</f>
         <v>62</v>
       </c>
       <c r="R165" s="84"/>
@@ -17900,7 +17924,7 @@
       <c r="T165" s="113"/>
       <c r="U165" s="87"/>
       <c r="V165" s="106">
-        <f t="shared" si="42"/>
+        <f>SUM(X165+AA165+AD165+AG165)</f>
         <v>62</v>
       </c>
       <c r="W165" s="93"/>
@@ -17958,12 +17982,12 @@
       <c r="H166" s="83"/>
       <c r="I166" s="83"/>
       <c r="J166" s="84">
-        <f t="shared" si="43"/>
+        <f>V166-G166</f>
         <v>21</v>
       </c>
       <c r="K166" s="84"/>
       <c r="L166" s="83" t="str">
-        <f t="shared" si="44"/>
+        <f>S166</f>
         <v>12002-81-020603-СПА.СО л.1 ( п.1.2.6)</v>
       </c>
       <c r="M166" s="83"/>
@@ -17973,7 +17997,7 @@
       <c r="O166" s="83"/>
       <c r="P166" s="83"/>
       <c r="Q166" s="83">
-        <f t="shared" si="3"/>
+        <f>N166-G166</f>
         <v>21</v>
       </c>
       <c r="R166" s="84"/>
@@ -17983,7 +18007,7 @@
       <c r="T166" s="113"/>
       <c r="U166" s="87"/>
       <c r="V166" s="106">
-        <f t="shared" si="42"/>
+        <f>SUM(X166+AA166+AD166+AG166)</f>
         <v>21</v>
       </c>
       <c r="W166" s="93"/>
@@ -18033,7 +18057,7 @@
         <v>302</v>
       </c>
       <c r="D167" s="134">
-        <v>18.0</v>
+        <v>17</v>
       </c>
       <c r="E167" s="132" t="s">
         <v>314</v>
@@ -18052,7 +18076,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="138">
-        <f t="shared" si="43"/>
+        <f>V167-G167</f>
         <v>38</v>
       </c>
       <c r="K167" s="138">
@@ -18060,7 +18084,7 @@
         <v>15670171</v>
       </c>
       <c r="L167" s="137" t="str">
-        <f t="shared" si="44"/>
+        <f>S167</f>
         <v>12002-81-020601-СПА. СО; Изм.1; 2л; поз(5.1)
 12002-81-020602-АУПТ.СО1 ; Изм.0; 2л; поз(5.1)
 12002-81-020602-СПА.СО:Изм.1, л3 (1.5.1)</v>
@@ -18071,14 +18095,14 @@
         <v>38</v>
       </c>
       <c r="O167" s="137">
-        <v>7748.64</v>
+        <v>333038.02</v>
       </c>
       <c r="P167" s="137">
         <f>N167*AE167</f>
         <v>15670170.58</v>
       </c>
       <c r="Q167" s="137">
-        <f t="shared" si="3"/>
+        <f>N167-G167</f>
         <v>38</v>
       </c>
       <c r="R167" s="138">
@@ -18153,8 +18177,10 @@
       <c r="AJ167" s="76" t="s">
         <v>316</v>
       </c>
-      <c r="AK167" s="55" t="s">
-        <v>317</v>
+      <c r="AK167" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Расчёт стоимости прикладываем (расценки направлены на согласование 09.07.2026). Наименование и состав работ БЕР №17 приведены в соответствие с расценкой: «Аспирационные извещатели ИП 212-1 «ОПТИСЕНС» ИПДА». Нумерация БЕР приведена к сплошной (ранее — №18).</t>
+        </is>
       </c>
       <c r="AL167" s="13"/>
       <c r="AM167" s="13"/>
@@ -18202,7 +18228,7 @@
       <c r="O168" s="150"/>
       <c r="P168" s="150"/>
       <c r="Q168" s="150">
-        <f t="shared" si="3"/>
+        <f>N168-G168</f>
         <v>12</v>
       </c>
       <c r="R168" s="151"/>
@@ -18212,7 +18238,7 @@
       <c r="T168" s="153"/>
       <c r="U168" s="154"/>
       <c r="V168" s="155">
-        <f t="shared" ref="V168:V170" si="45">SUM(X168+AA168+AD168+AG168)</f>
+        <f>SUM(X168+AA168+AD168+AG168)</f>
         <v>12</v>
       </c>
       <c r="W168" s="156"/>
@@ -18270,7 +18296,7 @@
       <c r="J169" s="84"/>
       <c r="K169" s="84"/>
       <c r="L169" s="83" t="str">
-        <f t="shared" ref="L169:L170" si="46">S169</f>
+        <f>S169</f>
         <v>12002-81-020602-АУПТ.СО1 ; Изм.0; 2л; поз(5.1)</v>
       </c>
       <c r="M169" s="83"/>
@@ -18280,7 +18306,7 @@
       <c r="O169" s="83"/>
       <c r="P169" s="83"/>
       <c r="Q169" s="83">
-        <f t="shared" si="3"/>
+        <f>N169-G169</f>
         <v>6</v>
       </c>
       <c r="R169" s="84"/>
@@ -18290,7 +18316,7 @@
       <c r="T169" s="113"/>
       <c r="U169" s="89"/>
       <c r="V169" s="158">
-        <f t="shared" si="45"/>
+        <f>SUM(X169+AA169+AD169+AG169)</f>
         <v>6</v>
       </c>
       <c r="W169" s="93"/>
@@ -18348,7 +18374,7 @@
       <c r="J170" s="138"/>
       <c r="K170" s="138"/>
       <c r="L170" s="137" t="str">
-        <f t="shared" si="46"/>
+        <f>S170</f>
         <v>12002-81-020602-СПА.СО:Изм.1, л3 (1.5.1)</v>
       </c>
       <c r="M170" s="137"/>
@@ -18358,7 +18384,7 @@
       <c r="O170" s="137"/>
       <c r="P170" s="137"/>
       <c r="Q170" s="138">
-        <f t="shared" si="3"/>
+        <f>N170-G170</f>
         <v>20</v>
       </c>
       <c r="R170" s="162"/>
@@ -18368,7 +18394,7 @@
       <c r="T170" s="164"/>
       <c r="U170" s="165"/>
       <c r="V170" s="166">
-        <f t="shared" si="45"/>
+        <f>SUM(X170+AA170+AD170+AG170)</f>
         <v>20</v>
       </c>
       <c r="W170" s="165"/>
@@ -19151,8 +19177,15 @@
       <c r="B183" s="13"/>
       <c r="C183" s="13"/>
       <c r="D183" s="13"/>
-      <c r="E183" s="172" t="s">
-        <v>331</v>
+      <c r="E183" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*БЕР №9. Установка аккумуляторных батарей включает:
+- приобретение и доставка аккумуляторных батарей и боксов резервного питания к месту производства работ
+- монтаж боксов резервного питания, установка в них аккумуляторных батарей
+- расключение устройств
+- проверка подключения, не относящаяся к ПНР
+- прочие сопутствующие работы</t>
+        </is>
       </c>
       <c r="F183" s="13"/>
       <c r="G183" s="13"/>
@@ -19273,8 +19306,17 @@
       <c r="B185" s="13"/>
       <c r="C185" s="13"/>
       <c r="D185" s="13"/>
-      <c r="E185" s="174" t="s">
-        <v>333</v>
+      <c r="E185" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*БЕР №11. Установка модульная пожаротушения включает:
+- приобретение и доставка оборудования/материалов к месту производства работ
+- разметка мест установки, монтаж рам, кронштейнов и креплений
+- установка модулей установки в проектное положение и их соединение по проекту (коллектор, распределительные устройства — при наличии в комплекте установки)
+- монтаж запорно-пусковых устройств и арматуры установки
+- прокладка и подключение кабелей питания и цепей пуска
+- проверка цепей пуска, не относящаяся к ПНР
+- прочие сопутствующие работы</t>
+        </is>
       </c>
       <c r="F185" s="13"/>
       <c r="G185" s="13"/>
@@ -19334,8 +19376,19 @@
       <c r="B186" s="13"/>
       <c r="C186" s="13"/>
       <c r="D186" s="13"/>
-      <c r="E186" s="175" t="s">
-        <v>334</v>
+      <c r="E186" s="175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*БЕР №12. Монтаж стальных трубок (DN 0 - 300) (и / или) труба включает:
+ - Устройство песчанного основания
+- Прокладка трубопровода (кроме теплоизоляции),  опускание и укладка плетей труб в траншею и сварка труб
+- Установку фланцев, устройство запорной арматуры и СКУ
+- Устройство бетонных фундаментов, лотков, футляров и эстакад, гидроизоляции бетонных элементов
+- Подбивка трубопровода песчанным грунтом вручную
+- Проведение  неразрушающего контроля сварных стыков- Огрунтовка и окраска стальных трубопроводов, защитное покрытие из оцинкованной стали
+- Промывка трубопровода
+- Обратная засыпка (обваловка трубопровода)
+-Прочие сопутствующие работы.</t>
+        </is>
       </c>
       <c r="F186" s="13"/>
       <c r="G186" s="13"/>
@@ -19395,8 +19448,11 @@
       <c r="B187" s="13"/>
       <c r="C187" s="13"/>
       <c r="D187" s="13"/>
-      <c r="E187" s="171" t="s">
-        <v>335</v>
+      <c r="E187" s="171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*БЕР №13. Поставка стальных трубок (DN 0 - 300) (и / или) труба включает:
+- Доставка материалов к месту производства работ</t>
+        </is>
       </c>
       <c r="F187" s="13"/>
       <c r="G187" s="13"/>
@@ -19456,8 +19512,15 @@
       <c r="B188" s="13"/>
       <c r="C188" s="13"/>
       <c r="D188" s="13"/>
-      <c r="E188" s="171" t="s">
-        <v>336</v>
+      <c r="E188" s="171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*БЕР №14. Монтаж арматуры и изделий трубопроводов ВК (душ, мойка, унитаз, фланец, отвод, крепеж, втулка) включает:
+- приобретение и доставка материалов к месту производства работ
+- подготовка оснований
+- монтаж арматуры и изделий
+- опробование изделий
+- прочие сопутствующие работы</t>
+        </is>
       </c>
       <c r="F188" s="13"/>
       <c r="G188" s="13"/>
@@ -19472,9 +19535,7 @@
       <c r="P188" s="13"/>
       <c r="Q188" s="13"/>
       <c r="R188" s="13"/>
-      <c r="S188" s="176" t="s">
-        <v>337</v>
-      </c>
+      <c r="S188" s="176"/>
       <c r="T188" s="13"/>
       <c r="U188" s="13"/>
       <c r="V188" s="13"/>
@@ -19535,9 +19596,7 @@
       <c r="P189" s="13"/>
       <c r="Q189" s="13"/>
       <c r="R189" s="13"/>
-      <c r="S189" s="177" t="s">
-        <v>339</v>
-      </c>
+      <c r="S189" s="177"/>
       <c r="T189" s="13"/>
       <c r="U189" s="13"/>
       <c r="V189" s="13"/>
@@ -19582,8 +19641,15 @@
       <c r="B190" s="13"/>
       <c r="C190" s="13"/>
       <c r="D190" s="13"/>
-      <c r="E190" s="178" t="s">
-        <v>340</v>
+      <c r="E190" s="178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*БЕР №16. Установка адресного пожарного извещателя пламени включает:
+- Приобретение и доставка  оборудования/материалов к месту производства работ;
+- Установка  в проектное положение, соединение.
+- Прокладку и подключение соединительных линий;
+- Проверку правильности подключения;
+- Настройку и адресацию извещателя.</t>
+        </is>
       </c>
       <c r="F190" s="13"/>
       <c r="G190" s="13"/>
@@ -19643,8 +19709,16 @@
       <c r="B191" s="13"/>
       <c r="C191" s="13"/>
       <c r="D191" s="13"/>
-      <c r="E191" s="178" t="s">
-        <v>341</v>
+      <c r="E191" s="178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*БЕР №17. Аспирационные извещатели ИП 212-1 «ОПТИСЕНС» ИПДА включает:
+- приобретение и доставка извещателей к месту производства работ
+- установка извещателя в проектное положение
+- расключение (подключение к линиям связи и питания)
+- настройка и адресация извещателя
+- испытания, не относящиеся к ПНР (прозвонка кабелей, опробование цепей, проверка работоспособности после монтажа)
+- прочие сопутствующие работы</t>
+        </is>
       </c>
       <c r="F191" s="13"/>
       <c r="G191" s="13"/>
